--- a/data/question-bank.xlsx
+++ b/data/question-bank.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsun/Documents/Codex/2026-08-19/referenced-chatgpt-conversation-this-is-an/outputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsun/Documents/Codex/2026-08-19/referenced-chatgpt-conversation-this-is-an/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B22365E-24DA-644B-9BFB-FF4F659B7573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{890B0292-0C67-B44B-A489-F56554744CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="600" windowWidth="28200" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="600" windowWidth="28200" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Question Bank" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="726">
   <si>
     <t>id</t>
   </si>
@@ -1384,9 +1384,6 @@
     <t>Same functional group</t>
   </si>
   <si>
-    <t>Differ from one member to the next by -CH2-</t>
-  </si>
-  <si>
     <t>Similar chemical properties</t>
   </si>
   <si>
@@ -1475,9 +1472,6 @@
   </si>
   <si>
     <t>High temperature</t>
-  </si>
-  <si>
-    <t>Al2O3 catalyst</t>
   </si>
   <si>
     <t>CIE135</t>
@@ -2029,6 +2023,241 @@
   </si>
   <si>
     <t>4 Improvements</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Al₂O₃ catalyst</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Differ from one member to the next by -CH₂-</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CIE184</t>
+  </si>
+  <si>
+    <t>CIE185</t>
+  </si>
+  <si>
+    <t>CIE186</t>
+  </si>
+  <si>
+    <t>CIE187</t>
+  </si>
+  <si>
+    <t>CIE188</t>
+  </si>
+  <si>
+    <t>CIE189</t>
+  </si>
+  <si>
+    <t>CIE190</t>
+  </si>
+  <si>
+    <t>CIE191</t>
+  </si>
+  <si>
+    <t>CIE192</t>
+  </si>
+  <si>
+    <t>CIE193</t>
+  </si>
+  <si>
+    <t>CIE194</t>
+  </si>
+  <si>
+    <t>CIE195</t>
+  </si>
+  <si>
+    <t>CIE196</t>
+  </si>
+  <si>
+    <t>CIE197</t>
+  </si>
+  <si>
+    <t>5 Lab apparatus</t>
+  </si>
+  <si>
+    <t>5 Lab apparatus</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: conical flask</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: measuring cylinder</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: volumetric pipette</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: burette</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: beaker</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: test tube</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: boiling tube</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: water bath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: glass rod</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: condenser</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: funnel</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: gas syringe</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: pestle and mortar</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: Bunsen burner</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CIE198</t>
+  </si>
+  <si>
+    <t>CIE199</t>
+  </si>
+  <si>
+    <t>Translate: crucible</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Translate: delivery tube</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>锥形瓶</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>量筒</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>容量移液管</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>滴定管</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>烧杯</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>试管</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>沸腾试管</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>水浴盆</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>玻璃棒</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷凝器</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>漏斗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>气体注射器</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>研钵和研杵</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>本生燃烧器</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>坩埚</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>输送管</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not accurate, but fast</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Very accurate, only fixed volume</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Very accurate, variable volumes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>More suitable for heating</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>To keep temperature constant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>To stir, evenly mix</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Used for filtration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Used for gas collection</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>To grind into small pieces or powder</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Used for heating</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>To deliver gas</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2176,6 +2405,12 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <color rgb="FFB3261E"/>
@@ -2185,12 +2420,6 @@
           <bgColor rgb="FFFCE8E6"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2206,11 +2435,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuestionBank" displayName="QuestionBank" ref="A1:J184" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuestionBank" displayName="QuestionBank" ref="A1:J200" totalsRowShown="0">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="paper" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="topic" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="paper" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="topic" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="question"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="answer_1"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="answer_2"/>
@@ -2418,7 +2647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J184"/>
+  <dimension ref="A1:J200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2468,7 +2697,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>
@@ -2494,7 +2723,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>16</v>
@@ -2520,7 +2749,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>20</v>
@@ -2544,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>23</v>
@@ -2568,7 +2797,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>26</v>
@@ -2592,7 +2821,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>29</v>
@@ -2616,7 +2845,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>32</v>
@@ -2640,7 +2869,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>35</v>
@@ -2664,7 +2893,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>38</v>
@@ -2688,7 +2917,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>41</v>
@@ -2714,7 +2943,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>45</v>
@@ -2742,7 +2971,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>50</v>
@@ -2766,7 +2995,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>53</v>
@@ -2790,7 +3019,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>56</v>
@@ -2814,7 +3043,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>59</v>
@@ -2840,7 +3069,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>63</v>
@@ -2868,7 +3097,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>68</v>
@@ -2894,7 +3123,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>72</v>
@@ -2920,7 +3149,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>75</v>
@@ -2946,7 +3175,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>79</v>
@@ -2970,7 +3199,7 @@
         <v>4</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>82</v>
@@ -2994,7 +3223,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>85</v>
@@ -3018,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>87</v>
@@ -3046,7 +3275,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>92</v>
@@ -3070,7 +3299,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>95</v>
@@ -3096,7 +3325,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>99</v>
@@ -3120,7 +3349,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>102</v>
@@ -3144,7 +3373,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>105</v>
@@ -3168,7 +3397,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>108</v>
@@ -3192,7 +3421,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>111</v>
@@ -3218,7 +3447,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>115</v>
@@ -3242,7 +3471,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>118</v>
@@ -3270,7 +3499,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>123</v>
@@ -3296,7 +3525,7 @@
         <v>4</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>127</v>
@@ -3322,7 +3551,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>131</v>
@@ -3348,7 +3577,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>135</v>
@@ -3372,7 +3601,7 @@
         <v>4</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>138</v>
@@ -3396,7 +3625,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>141</v>
@@ -3420,7 +3649,7 @@
         <v>4</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>144</v>
@@ -3444,7 +3673,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>147</v>
@@ -3468,7 +3697,7 @@
         <v>4</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>150</v>
@@ -3492,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>153</v>
@@ -3520,7 +3749,7 @@
         <v>4</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>158</v>
@@ -3546,7 +3775,7 @@
         <v>4</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>162</v>
@@ -3572,7 +3801,7 @@
         <v>4</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>165</v>
@@ -3600,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>170</v>
@@ -3628,7 +3857,7 @@
         <v>4</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>175</v>
@@ -3652,7 +3881,7 @@
         <v>4</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>178</v>
@@ -3678,7 +3907,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>182</v>
@@ -3702,7 +3931,7 @@
         <v>4</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>185</v>
@@ -3728,7 +3957,7 @@
         <v>4</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>188</v>
@@ -3756,7 +3985,7 @@
         <v>4</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>193</v>
@@ -3782,7 +4011,7 @@
         <v>4</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>197</v>
@@ -3810,7 +4039,7 @@
         <v>4</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>202</v>
@@ -3836,7 +4065,7 @@
         <v>4</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>206</v>
@@ -3864,7 +4093,7 @@
         <v>4</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>210</v>
@@ -3888,7 +4117,7 @@
         <v>4</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>213</v>
@@ -3912,7 +4141,7 @@
         <v>4</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>216</v>
@@ -3938,7 +4167,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>220</v>
@@ -3964,7 +4193,7 @@
         <v>4</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>222</v>
@@ -3988,7 +4217,7 @@
         <v>4</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>225</v>
@@ -4012,7 +4241,7 @@
         <v>4</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>228</v>
@@ -4036,7 +4265,7 @@
         <v>4</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>231</v>
@@ -4060,7 +4289,7 @@
         <v>4</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>234</v>
@@ -4084,7 +4313,7 @@
         <v>4</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>237</v>
@@ -4108,7 +4337,7 @@
         <v>4</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>240</v>
@@ -4134,7 +4363,7 @@
         <v>4</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>244</v>
@@ -4158,7 +4387,7 @@
         <v>4</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>247</v>
@@ -4182,7 +4411,7 @@
         <v>4</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>250</v>
@@ -4206,7 +4435,7 @@
         <v>4</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>253</v>
@@ -4230,7 +4459,7 @@
         <v>4</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>256</v>
@@ -4254,7 +4483,7 @@
         <v>4</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>259</v>
@@ -4278,7 +4507,7 @@
         <v>4</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>262</v>
@@ -4302,7 +4531,7 @@
         <v>4</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>265</v>
@@ -4326,7 +4555,7 @@
         <v>4</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>268</v>
@@ -4350,7 +4579,7 @@
         <v>4</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>271</v>
@@ -4374,7 +4603,7 @@
         <v>4</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>274</v>
@@ -4406,7 +4635,7 @@
         <v>4</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>281</v>
@@ -4432,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>285</v>
@@ -4456,7 +4685,7 @@
         <v>4</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>288</v>
@@ -4484,7 +4713,7 @@
         <v>4</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>292</v>
@@ -4508,7 +4737,7 @@
         <v>4</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>295</v>
@@ -4532,7 +4761,7 @@
         <v>4</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>298</v>
@@ -4556,7 +4785,7 @@
         <v>4</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>300</v>
@@ -4580,7 +4809,7 @@
         <v>4</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>303</v>
@@ -4610,7 +4839,7 @@
         <v>4</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>309</v>
@@ -4638,7 +4867,7 @@
         <v>4</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>314</v>
@@ -4666,7 +4895,7 @@
         <v>4</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>319</v>
@@ -4690,7 +4919,7 @@
         <v>4</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>322</v>
@@ -4714,7 +4943,7 @@
         <v>4</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>325</v>
@@ -4744,7 +4973,7 @@
         <v>4</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>331</v>
@@ -4768,7 +4997,7 @@
         <v>4</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>334</v>
@@ -4794,7 +5023,7 @@
         <v>4</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>338</v>
@@ -4820,7 +5049,7 @@
         <v>4</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>342</v>
@@ -4844,7 +5073,7 @@
         <v>4</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>345</v>
@@ -4868,7 +5097,7 @@
         <v>4</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>348</v>
@@ -4894,7 +5123,7 @@
         <v>4</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>352</v>
@@ -4918,7 +5147,7 @@
         <v>4</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>355</v>
@@ -4942,7 +5171,7 @@
         <v>4</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>358</v>
@@ -4968,7 +5197,7 @@
         <v>4</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>362</v>
@@ -4992,7 +5221,7 @@
         <v>4</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>365</v>
@@ -5018,7 +5247,7 @@
         <v>4</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>369</v>
@@ -5042,7 +5271,7 @@
         <v>4</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>372</v>
@@ -5066,7 +5295,7 @@
         <v>4</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>375</v>
@@ -5094,7 +5323,7 @@
         <v>4</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D106" s="5" t="s">
         <v>380</v>
@@ -5118,7 +5347,7 @@
         <v>4</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>383</v>
@@ -5142,7 +5371,7 @@
         <v>4</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>386</v>
@@ -5166,7 +5395,7 @@
         <v>4</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>389</v>
@@ -5190,7 +5419,7 @@
         <v>4</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>392</v>
@@ -5218,7 +5447,7 @@
         <v>4</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>397</v>
@@ -5242,7 +5471,7 @@
         <v>4</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>400</v>
@@ -5266,7 +5495,7 @@
         <v>4</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>403</v>
@@ -5294,7 +5523,7 @@
         <v>4</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>408</v>
@@ -5318,7 +5547,7 @@
         <v>4</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>411</v>
@@ -5344,7 +5573,7 @@
         <v>4</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>415</v>
@@ -5368,7 +5597,7 @@
         <v>4</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>418</v>
@@ -5392,7 +5621,7 @@
         <v>4</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>421</v>
@@ -5422,7 +5651,7 @@
         <v>4</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>427</v>
@@ -5446,7 +5675,7 @@
         <v>4</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>430</v>
@@ -5470,7 +5699,7 @@
         <v>4</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>433</v>
@@ -5500,7 +5729,7 @@
         <v>4</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>438</v>
@@ -5526,7 +5755,7 @@
         <v>4</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>442</v>
@@ -5550,7 +5779,7 @@
         <v>4</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>445</v>
@@ -5574,7 +5803,7 @@
         <v>4</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>448</v>
@@ -5598,7 +5827,7 @@
         <v>4</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>451</v>
@@ -5610,13 +5839,13 @@
         <v>453</v>
       </c>
       <c r="G126" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="H126" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="H126" s="5" t="s">
+      <c r="I126" s="5" t="s">
         <v>455</v>
-      </c>
-      <c r="I126" s="5" t="s">
-        <v>456</v>
       </c>
       <c r="J126" s="5" t="s">
         <v>14</v>
@@ -5624,19 +5853,19 @@
     </row>
     <row r="127" spans="1:10" ht="42" customHeight="1">
       <c r="A127" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="B127" s="8">
+        <v>4</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D127" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="B127" s="8">
-        <v>4</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D127" s="5" t="s">
+      <c r="E127" s="5" t="s">
         <v>458</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>459</v>
       </c>
       <c r="F127" s="5"/>
       <c r="G127" s="5"/>
@@ -5648,19 +5877,19 @@
     </row>
     <row r="128" spans="1:10" ht="42" customHeight="1">
       <c r="A128" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B128" s="8">
+        <v>4</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D128" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="B128" s="8">
-        <v>4</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D128" s="5" t="s">
+      <c r="E128" s="5" t="s">
         <v>461</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>462</v>
       </c>
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
@@ -5672,22 +5901,22 @@
     </row>
     <row r="129" spans="1:10" ht="42" customHeight="1">
       <c r="A129" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B129" s="8">
+        <v>4</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D129" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B129" s="8">
-        <v>4</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D129" s="5" t="s">
+      <c r="E129" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="E129" s="5" t="s">
+      <c r="F129" s="5" t="s">
         <v>465</v>
-      </c>
-      <c r="F129" s="5" t="s">
-        <v>466</v>
       </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
@@ -5698,19 +5927,19 @@
     </row>
     <row r="130" spans="1:10" ht="42" customHeight="1">
       <c r="A130" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B130" s="7">
+        <v>4</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="B130" s="7">
-        <v>4</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D130" s="5" t="s">
+      <c r="E130" s="5" t="s">
         <v>468</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>469</v>
       </c>
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
@@ -5722,19 +5951,19 @@
     </row>
     <row r="131" spans="1:10" ht="42" customHeight="1">
       <c r="A131" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B131" s="8">
+        <v>4</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D131" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="B131" s="8">
-        <v>4</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D131" s="5" t="s">
+      <c r="E131" s="5" t="s">
         <v>471</v>
-      </c>
-      <c r="E131" s="5" t="s">
-        <v>472</v>
       </c>
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
@@ -5746,19 +5975,19 @@
     </row>
     <row r="132" spans="1:10" ht="42" customHeight="1">
       <c r="A132" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B132" s="8">
+        <v>4</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="B132" s="8">
-        <v>4</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D132" s="5" t="s">
+      <c r="E132" s="5" t="s">
         <v>474</v>
-      </c>
-      <c r="E132" s="5" t="s">
-        <v>475</v>
       </c>
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
@@ -5770,19 +5999,19 @@
     </row>
     <row r="133" spans="1:10" ht="42" customHeight="1">
       <c r="A133" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B133" s="8">
+        <v>4</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D133" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="B133" s="8">
-        <v>4</v>
-      </c>
-      <c r="C133" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D133" s="5" t="s">
+      <c r="E133" s="5" t="s">
         <v>477</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>478</v>
       </c>
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
@@ -5794,19 +6023,19 @@
     </row>
     <row r="134" spans="1:10" ht="42" customHeight="1">
       <c r="A134" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B134" s="7">
+        <v>4</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="B134" s="7">
-        <v>4</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D134" s="5" t="s">
+      <c r="E134" s="5" t="s">
         <v>480</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>481</v>
       </c>
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
@@ -5818,22 +6047,22 @@
     </row>
     <row r="135" spans="1:10" ht="42" customHeight="1">
       <c r="A135" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B135" s="8">
+        <v>4</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D135" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="B135" s="8">
-        <v>4</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D135" s="5" t="s">
+      <c r="E135" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="E135" s="5" t="s">
-        <v>484</v>
-      </c>
       <c r="F135" s="5" t="s">
-        <v>485</v>
+        <v>663</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
@@ -5844,19 +6073,19 @@
     </row>
     <row r="136" spans="1:10" ht="42" customHeight="1">
       <c r="A136" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B136" s="8">
+        <v>4</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="E136" s="5" t="s">
         <v>486</v>
-      </c>
-      <c r="B136" s="8">
-        <v>4</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>488</v>
       </c>
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
@@ -5868,19 +6097,19 @@
     </row>
     <row r="137" spans="1:10" ht="42" customHeight="1">
       <c r="A137" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B137" s="8">
+        <v>4</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="E137" s="5" t="s">
         <v>489</v>
-      </c>
-      <c r="B137" s="8">
-        <v>4</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>491</v>
       </c>
       <c r="F137" s="5"/>
       <c r="G137" s="5"/>
@@ -5892,25 +6121,25 @@
     </row>
     <row r="138" spans="1:10" ht="42" customHeight="1">
       <c r="A138" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B138" s="7">
+        <v>4</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="E138" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="B138" s="7">
-        <v>4</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D138" s="5" t="s">
+      <c r="F138" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="G138" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="G138" s="5" t="s">
-        <v>496</v>
       </c>
       <c r="H138" s="5"/>
       <c r="I138" s="5"/>
@@ -5920,22 +6149,22 @@
     </row>
     <row r="139" spans="1:10" ht="42" customHeight="1">
       <c r="A139" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B139" s="8">
+        <v>4</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="E139" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="B139" s="8">
-        <v>4</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D139" s="5" t="s">
+      <c r="F139" s="5" t="s">
         <v>498</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="F139" s="5" t="s">
-        <v>500</v>
       </c>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -5946,22 +6175,22 @@
     </row>
     <row r="140" spans="1:10" ht="42" customHeight="1">
       <c r="A140" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B140" s="8">
+        <v>4</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="E140" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B140" s="8">
-        <v>4</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D140" s="5" t="s">
+      <c r="F140" s="5" t="s">
         <v>502</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>503</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>504</v>
       </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
@@ -5972,25 +6201,25 @@
     </row>
     <row r="141" spans="1:10" ht="42" customHeight="1">
       <c r="A141" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B141" s="8">
+        <v>4</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="E141" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="B141" s="8">
-        <v>4</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D141" s="5" t="s">
+      <c r="F141" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="E141" s="5" t="s">
+      <c r="G141" s="5" t="s">
         <v>507</v>
-      </c>
-      <c r="F141" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>509</v>
       </c>
       <c r="H141" s="5"/>
       <c r="I141" s="5"/>
@@ -6000,22 +6229,22 @@
     </row>
     <row r="142" spans="1:10" ht="42" customHeight="1">
       <c r="A142" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B142" s="7">
+        <v>4</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="E142" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="B142" s="7">
-        <v>4</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D142" s="5" t="s">
+      <c r="F142" s="5" t="s">
         <v>511</v>
-      </c>
-      <c r="E142" s="5" t="s">
-        <v>512</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>513</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -6026,22 +6255,22 @@
     </row>
     <row r="143" spans="1:10" ht="42" customHeight="1">
       <c r="A143" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B143" s="8">
+        <v>4</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="E143" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="B143" s="8">
-        <v>4</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D143" s="5" t="s">
+      <c r="F143" s="5" t="s">
         <v>515</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>517</v>
       </c>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -6052,19 +6281,19 @@
     </row>
     <row r="144" spans="1:10" ht="42" customHeight="1">
       <c r="A144" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="B144" s="8">
+        <v>4</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="E144" s="5" t="s">
         <v>518</v>
-      </c>
-      <c r="B144" s="8">
-        <v>4</v>
-      </c>
-      <c r="C144" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>520</v>
       </c>
       <c r="F144" s="5"/>
       <c r="G144" s="5"/>
@@ -6076,19 +6305,19 @@
     </row>
     <row r="145" spans="1:10" ht="42" customHeight="1">
       <c r="A145" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="B145" s="8">
+        <v>4</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="E145" s="5" t="s">
         <v>521</v>
-      </c>
-      <c r="B145" s="8">
-        <v>4</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>523</v>
       </c>
       <c r="F145" s="5"/>
       <c r="G145" s="5"/>
@@ -6100,19 +6329,19 @@
     </row>
     <row r="146" spans="1:10" ht="42" customHeight="1">
       <c r="A146" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="B146" s="7">
+        <v>4</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="E146" s="5" t="s">
         <v>524</v>
-      </c>
-      <c r="B146" s="7">
-        <v>4</v>
-      </c>
-      <c r="C146" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D146" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>526</v>
       </c>
       <c r="F146" s="5"/>
       <c r="G146" s="5"/>
@@ -6124,19 +6353,19 @@
     </row>
     <row r="147" spans="1:10" ht="42" customHeight="1">
       <c r="A147" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B147" s="8">
+        <v>4</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="E147" s="5" t="s">
         <v>527</v>
-      </c>
-      <c r="B147" s="8">
-        <v>4</v>
-      </c>
-      <c r="C147" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>529</v>
       </c>
       <c r="F147" s="5"/>
       <c r="G147" s="5"/>
@@ -6148,19 +6377,19 @@
     </row>
     <row r="148" spans="1:10" ht="42" customHeight="1">
       <c r="A148" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="B148" s="8">
+        <v>4</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="E148" s="5" t="s">
         <v>530</v>
-      </c>
-      <c r="B148" s="8">
-        <v>4</v>
-      </c>
-      <c r="C148" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>532</v>
       </c>
       <c r="F148" s="5"/>
       <c r="G148" s="5"/>
@@ -6172,19 +6401,19 @@
     </row>
     <row r="149" spans="1:10" ht="42" customHeight="1">
       <c r="A149" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B149" s="8">
+        <v>4</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="E149" s="5" t="s">
         <v>533</v>
-      </c>
-      <c r="B149" s="8">
-        <v>4</v>
-      </c>
-      <c r="C149" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>535</v>
       </c>
       <c r="F149" s="5"/>
       <c r="G149" s="5"/>
@@ -6196,19 +6425,19 @@
     </row>
     <row r="150" spans="1:10" ht="42" customHeight="1">
       <c r="A150" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="B150" s="7">
+        <v>4</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="E150" s="5" t="s">
         <v>536</v>
-      </c>
-      <c r="B150" s="7">
-        <v>4</v>
-      </c>
-      <c r="C150" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>538</v>
       </c>
       <c r="F150" s="5"/>
       <c r="G150" s="5"/>
@@ -6220,19 +6449,19 @@
     </row>
     <row r="151" spans="1:10" ht="42" customHeight="1">
       <c r="A151" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="B151" s="8">
+        <v>4</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="E151" s="5" t="s">
         <v>539</v>
-      </c>
-      <c r="B151" s="8">
-        <v>4</v>
-      </c>
-      <c r="C151" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="E151" s="5" t="s">
-        <v>541</v>
       </c>
       <c r="F151" s="5"/>
       <c r="G151" s="5"/>
@@ -6244,19 +6473,19 @@
     </row>
     <row r="152" spans="1:10" ht="42" customHeight="1">
       <c r="A152" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="B152" s="8">
+        <v>4</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="E152" s="5" t="s">
         <v>542</v>
-      </c>
-      <c r="B152" s="8">
-        <v>4</v>
-      </c>
-      <c r="C152" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="E152" s="5" t="s">
-        <v>544</v>
       </c>
       <c r="F152" s="5"/>
       <c r="G152" s="5"/>
@@ -6268,22 +6497,22 @@
     </row>
     <row r="153" spans="1:10" ht="42" customHeight="1">
       <c r="A153" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B153" s="8">
+        <v>4</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="E153" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="B153" s="8">
-        <v>4</v>
-      </c>
-      <c r="C153" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D153" s="5" t="s">
+      <c r="F153" s="5" t="s">
         <v>546</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>548</v>
       </c>
       <c r="G153" s="5" t="s">
         <v>279</v>
@@ -6296,19 +6525,19 @@
     </row>
     <row r="154" spans="1:10" ht="42" customHeight="1">
       <c r="A154" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="B154" s="7">
+        <v>4</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="E154" s="5" t="s">
         <v>549</v>
-      </c>
-      <c r="B154" s="7">
-        <v>4</v>
-      </c>
-      <c r="C154" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>550</v>
-      </c>
-      <c r="E154" s="5" t="s">
-        <v>551</v>
       </c>
       <c r="F154" s="5"/>
       <c r="G154" s="5"/>
@@ -6320,19 +6549,19 @@
     </row>
     <row r="155" spans="1:10" ht="42" customHeight="1">
       <c r="A155" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="B155" s="8">
+        <v>4</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="E155" s="5" t="s">
         <v>552</v>
-      </c>
-      <c r="B155" s="8">
-        <v>4</v>
-      </c>
-      <c r="C155" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="E155" s="5" t="s">
-        <v>554</v>
       </c>
       <c r="F155" s="5"/>
       <c r="G155" s="5"/>
@@ -6344,19 +6573,19 @@
     </row>
     <row r="156" spans="1:10" ht="42" customHeight="1">
       <c r="A156" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="B156" s="8">
+        <v>4</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E156" s="5" t="s">
         <v>555</v>
-      </c>
-      <c r="B156" s="8">
-        <v>4</v>
-      </c>
-      <c r="C156" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D156" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="E156" s="5" t="s">
-        <v>557</v>
       </c>
       <c r="F156" s="5"/>
       <c r="G156" s="5"/>
@@ -6368,19 +6597,19 @@
     </row>
     <row r="157" spans="1:10" ht="42" customHeight="1">
       <c r="A157" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="B157" s="8">
+        <v>4</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="E157" s="5" t="s">
         <v>558</v>
-      </c>
-      <c r="B157" s="8">
-        <v>4</v>
-      </c>
-      <c r="C157" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="E157" s="5" t="s">
-        <v>560</v>
       </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
@@ -6392,19 +6621,19 @@
     </row>
     <row r="158" spans="1:10" ht="42" customHeight="1">
       <c r="A158" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="B158" s="7">
+        <v>4</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="E158" s="5" t="s">
         <v>561</v>
-      </c>
-      <c r="B158" s="7">
-        <v>4</v>
-      </c>
-      <c r="C158" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="D158" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="E158" s="5" t="s">
-        <v>563</v>
       </c>
       <c r="F158" s="5"/>
       <c r="G158" s="5"/>
@@ -6416,19 +6645,19 @@
     </row>
     <row r="159" spans="1:10" ht="42" customHeight="1">
       <c r="A159" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B159" s="8">
         <v>6</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F159" s="5"/>
       <c r="G159" s="5"/>
@@ -6440,19 +6669,19 @@
     </row>
     <row r="160" spans="1:10" ht="42" customHeight="1">
       <c r="A160" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B160" s="8">
         <v>6</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F160" s="5"/>
       <c r="G160" s="5"/>
@@ -6464,22 +6693,22 @@
     </row>
     <row r="161" spans="1:10" ht="42" customHeight="1">
       <c r="A161" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B161" s="8">
         <v>6</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D161" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="F161" s="5" t="s">
         <v>571</v>
-      </c>
-      <c r="E161" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>573</v>
       </c>
       <c r="G161" s="5"/>
       <c r="H161" s="5"/>
@@ -6490,19 +6719,19 @@
     </row>
     <row r="162" spans="1:10" ht="42" customHeight="1">
       <c r="A162" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B162" s="8">
         <v>6</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F162" s="5"/>
       <c r="G162" s="5"/>
@@ -6514,19 +6743,19 @@
     </row>
     <row r="163" spans="1:10" ht="42" customHeight="1">
       <c r="A163" s="4" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B163" s="8">
         <v>6</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F163" s="5"/>
       <c r="G163" s="5"/>
@@ -6538,19 +6767,19 @@
     </row>
     <row r="164" spans="1:10" ht="42" customHeight="1">
       <c r="A164" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B164" s="8">
         <v>6</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F164" s="5"/>
       <c r="G164" s="5"/>
@@ -6562,19 +6791,19 @@
     </row>
     <row r="165" spans="1:10" ht="42" customHeight="1">
       <c r="A165" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B165" s="8">
         <v>6</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F165" s="5"/>
       <c r="G165" s="5"/>
@@ -6586,19 +6815,19 @@
     </row>
     <row r="166" spans="1:10" ht="42" customHeight="1">
       <c r="A166" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B166" s="8">
         <v>6</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F166" s="5"/>
       <c r="G166" s="5"/>
@@ -6610,22 +6839,22 @@
     </row>
     <row r="167" spans="1:10" ht="42" customHeight="1">
       <c r="A167" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B167" s="8">
         <v>6</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D167" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="F167" s="5" t="s">
         <v>590</v>
-      </c>
-      <c r="E167" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="F167" s="5" t="s">
-        <v>592</v>
       </c>
       <c r="G167" s="5"/>
       <c r="H167" s="5"/>
@@ -6636,19 +6865,19 @@
     </row>
     <row r="168" spans="1:10" ht="42" customHeight="1">
       <c r="A168" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B168" s="8">
         <v>6</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F168" s="5"/>
       <c r="G168" s="5"/>
@@ -6660,22 +6889,22 @@
     </row>
     <row r="169" spans="1:10" ht="42" customHeight="1">
       <c r="A169" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B169" s="8">
         <v>6</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D169" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="F169" s="5" t="s">
         <v>597</v>
-      </c>
-      <c r="E169" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>599</v>
       </c>
       <c r="G169" s="5"/>
       <c r="H169" s="5"/>
@@ -6686,22 +6915,22 @@
     </row>
     <row r="170" spans="1:10" ht="42" customHeight="1">
       <c r="A170" s="4" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B170" s="8">
         <v>6</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E170" s="5" t="s">
         <v>189</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="G170" s="5"/>
       <c r="H170" s="5"/>
@@ -6712,22 +6941,22 @@
     </row>
     <row r="171" spans="1:10" ht="42" customHeight="1">
       <c r="A171" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B171" s="8">
         <v>6</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D171" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="F171" s="5" t="s">
         <v>604</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>606</v>
       </c>
       <c r="G171" s="5"/>
       <c r="H171" s="5"/>
@@ -6738,22 +6967,22 @@
     </row>
     <row r="172" spans="1:10" ht="42" customHeight="1">
       <c r="A172" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B172" s="8">
         <v>6</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D172" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="F172" s="5" t="s">
         <v>608</v>
-      </c>
-      <c r="E172" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>610</v>
       </c>
       <c r="G172" s="5"/>
       <c r="H172" s="5"/>
@@ -6764,22 +6993,22 @@
     </row>
     <row r="173" spans="1:10" ht="42" customHeight="1">
       <c r="A173" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B173" s="8">
         <v>6</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D173" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="F173" s="5" t="s">
         <v>612</v>
-      </c>
-      <c r="E173" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>614</v>
       </c>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
@@ -6790,22 +7019,22 @@
     </row>
     <row r="174" spans="1:10" ht="42" customHeight="1">
       <c r="A174" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B174" s="8">
         <v>6</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D174" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F174" s="5" t="s">
         <v>616</v>
-      </c>
-      <c r="E174" s="5" t="s">
-        <v>617</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>618</v>
       </c>
       <c r="G174" s="5"/>
       <c r="H174" s="5"/>
@@ -6816,19 +7045,19 @@
     </row>
     <row r="175" spans="1:10" ht="42" customHeight="1">
       <c r="A175" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B175" s="8">
         <v>6</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F175" s="5"/>
       <c r="G175" s="5"/>
@@ -6840,19 +7069,19 @@
     </row>
     <row r="176" spans="1:10" ht="42" customHeight="1">
       <c r="A176" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B176" s="8">
         <v>6</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F176" s="5"/>
       <c r="G176" s="5"/>
@@ -6864,19 +7093,19 @@
     </row>
     <row r="177" spans="1:10" ht="42" customHeight="1">
       <c r="A177" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B177" s="8">
         <v>6</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F177" s="5"/>
       <c r="G177" s="5"/>
@@ -6888,19 +7117,19 @@
     </row>
     <row r="178" spans="1:10" ht="42" customHeight="1">
       <c r="A178" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B178" s="8">
         <v>6</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F178" s="5"/>
       <c r="G178" s="5"/>
@@ -6912,19 +7141,19 @@
     </row>
     <row r="179" spans="1:10" ht="42" customHeight="1">
       <c r="A179" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B179" s="8">
         <v>6</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F179" s="5"/>
       <c r="G179" s="5"/>
@@ -6936,19 +7165,19 @@
     </row>
     <row r="180" spans="1:10" ht="42" customHeight="1">
       <c r="A180" s="4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B180" s="8">
         <v>6</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F180" s="5"/>
       <c r="G180" s="5"/>
@@ -6960,19 +7189,19 @@
     </row>
     <row r="181" spans="1:10" ht="42" customHeight="1">
       <c r="A181" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B181" s="8">
         <v>6</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F181" s="5"/>
       <c r="G181" s="5"/>
@@ -6984,22 +7213,22 @@
     </row>
     <row r="182" spans="1:10" ht="42" customHeight="1">
       <c r="A182" s="4" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B182" s="8">
         <v>6</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D182" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="F182" s="5" t="s">
         <v>641</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="F182" s="5" t="s">
-        <v>643</v>
       </c>
       <c r="G182" s="5"/>
       <c r="H182" s="5"/>
@@ -7010,19 +7239,19 @@
     </row>
     <row r="183" spans="1:10" ht="42" customHeight="1">
       <c r="A183" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B183" s="8">
         <v>6</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F183" s="5"/>
       <c r="G183" s="5"/>
@@ -7034,19 +7263,19 @@
     </row>
     <row r="184" spans="1:10" ht="42" customHeight="1">
       <c r="A184" s="4" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B184" s="8">
         <v>6</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F184" s="5"/>
       <c r="G184" s="5"/>
@@ -7056,10 +7285,322 @@
         <v>14</v>
       </c>
     </row>
+    <row r="185" spans="1:10" ht="42" customHeight="1">
+      <c r="A185" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="B185" s="8">
+        <v>6</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="F185" s="5"/>
+    </row>
+    <row r="186" spans="1:10" ht="42" customHeight="1">
+      <c r="A186" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="B186" s="8">
+        <v>6</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="42" customHeight="1">
+      <c r="A187" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="B187" s="8">
+        <v>6</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="42" customHeight="1">
+      <c r="A188" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="B188" s="8">
+        <v>6</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="42" customHeight="1">
+      <c r="A189" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="B189" s="8">
+        <v>6</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="F189" s="5"/>
+    </row>
+    <row r="190" spans="1:10" ht="42" customHeight="1">
+      <c r="A190" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="B190" s="8">
+        <v>6</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="F190" s="5"/>
+    </row>
+    <row r="191" spans="1:10" ht="42" customHeight="1">
+      <c r="A191" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="B191" s="8">
+        <v>6</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" ht="42" customHeight="1">
+      <c r="A192" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="B192" s="8">
+        <v>6</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="F192" s="5" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="42" customHeight="1">
+      <c r="A193" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="B193" s="8">
+        <v>6</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>689</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="42" customHeight="1">
+      <c r="A194" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="B194" s="8">
+        <v>6</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="F194" s="5"/>
+    </row>
+    <row r="195" spans="1:6" ht="42" customHeight="1">
+      <c r="A195" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="B195" s="8">
+        <v>6</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="E195" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="42" customHeight="1">
+      <c r="A196" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="B196" s="8">
+        <v>6</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="42" customHeight="1">
+      <c r="A197" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="B197" s="8">
+        <v>6</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="42" customHeight="1">
+      <c r="A198" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="B198" s="8">
+        <v>6</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="42" customHeight="1">
+      <c r="A199" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="B199" s="8">
+        <v>6</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="42" customHeight="1">
+      <c r="A200" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="B200" s="8">
+        <v>6</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>679</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>725</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="I2:I158">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="yes"/>
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="yes"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/question-bank.xlsx
+++ b/data/question-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsun/Documents/Codex/2026-08-19/referenced-chatgpt-conversation-this-is-an/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F42FF6C-10F0-B64C-8822-6677648FBE71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8F8F07-AF14-354C-8D34-8D645F2B843A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="600" windowWidth="28200" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,9 +370,6 @@
     <t>Explain why mass of anode decreases when using copper electrodes</t>
   </si>
   <si>
-    <t>Cu forms Cu2+, which goes into the solution</t>
-  </si>
-  <si>
     <t>CIE032</t>
   </si>
   <si>
@@ -3848,6 +3845,27 @@
         <rFont val="Aptos"/>
       </rPr>
       <t xml:space="preserve"> → Cu</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Cu forms Cu</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>, which goes into the solution</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -4311,7 +4329,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>11</v>
@@ -4337,7 +4355,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>16</v>
@@ -4363,7 +4381,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>20</v>
@@ -4387,7 +4405,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>23</v>
@@ -4411,7 +4429,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>26</v>
@@ -4435,7 +4453,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>29</v>
@@ -4459,7 +4477,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>32</v>
@@ -4483,7 +4501,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>35</v>
@@ -4507,7 +4525,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>38</v>
@@ -4531,7 +4549,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>41</v>
@@ -4557,7 +4575,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>45</v>
@@ -4585,7 +4603,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>50</v>
@@ -4609,7 +4627,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>53</v>
@@ -4633,7 +4651,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>56</v>
@@ -4657,7 +4675,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>59</v>
@@ -4683,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>63</v>
@@ -4711,7 +4729,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>68</v>
@@ -4737,7 +4755,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>72</v>
@@ -4763,7 +4781,7 @@
         <v>4</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>75</v>
@@ -4789,7 +4807,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>79</v>
@@ -4813,7 +4831,7 @@
         <v>4</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>82</v>
@@ -4837,7 +4855,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>85</v>
@@ -4861,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>87</v>
@@ -4889,7 +4907,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>92</v>
@@ -4913,7 +4931,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>95</v>
@@ -4939,7 +4957,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>99</v>
@@ -4963,7 +4981,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>102</v>
@@ -4987,7 +5005,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>105</v>
@@ -5011,7 +5029,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>108</v>
@@ -5035,7 +5053,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>111</v>
@@ -5061,13 +5079,13 @@
         <v>4</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>115</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>116</v>
+        <v>832</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -5079,25 +5097,25 @@
     </row>
     <row r="33" spans="1:10" ht="42" customHeight="1">
       <c r="A33" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B33" s="8">
+        <v>4</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="8">
-        <v>4</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -5107,22 +5125,22 @@
     </row>
     <row r="34" spans="1:10" ht="42" customHeight="1">
       <c r="A34" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="7">
+        <v>4</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B34" s="7">
-        <v>4</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="F34" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -5133,22 +5151,22 @@
     </row>
     <row r="35" spans="1:10" ht="42" customHeight="1">
       <c r="A35" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="8">
+        <v>4</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B35" s="8">
-        <v>4</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -5159,22 +5177,22 @@
     </row>
     <row r="36" spans="1:10" ht="42" customHeight="1">
       <c r="A36" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="8">
+        <v>4</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B36" s="8">
-        <v>4</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>649</v>
-      </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -5185,22 +5203,22 @@
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1">
       <c r="A37" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B37" s="7">
         <v>4</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E37" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>831</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>832</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
@@ -5209,22 +5227,22 @@
     </row>
     <row r="38" spans="1:10" ht="42" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B38" s="8">
         <v>4</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>727</v>
-      </c>
       <c r="F38" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -5233,19 +5251,19 @@
     </row>
     <row r="39" spans="1:10" ht="42" customHeight="1">
       <c r="A39" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B39" s="8">
         <v>4</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -5255,19 +5273,19 @@
     </row>
     <row r="40" spans="1:10" ht="42" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B40" s="8">
         <v>4</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D40" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -5279,19 +5297,19 @@
     </row>
     <row r="41" spans="1:10" ht="42" customHeight="1">
       <c r="A41" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B41" s="7">
         <v>4</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D41" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>138</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -5303,19 +5321,19 @@
     </row>
     <row r="42" spans="1:10" ht="42" customHeight="1">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B42" s="8">
         <v>4</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -5327,19 +5345,19 @@
     </row>
     <row r="43" spans="1:10" ht="42" customHeight="1">
       <c r="A43" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B43" s="8">
         <v>4</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D43" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -5351,19 +5369,19 @@
     </row>
     <row r="44" spans="1:10" ht="42" customHeight="1">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="8">
         <v>4</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D44" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -5375,19 +5393,19 @@
     </row>
     <row r="45" spans="1:10" ht="42" customHeight="1">
       <c r="A45" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B45" s="7">
         <v>4</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>151</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -5399,25 +5417,25 @@
     </row>
     <row r="46" spans="1:10" ht="42" customHeight="1">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B46" s="8">
         <v>4</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D46" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="F46" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="G46" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -5427,22 +5445,22 @@
     </row>
     <row r="47" spans="1:10" ht="42" customHeight="1">
       <c r="A47" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>4</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="F47" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
@@ -5453,22 +5471,22 @@
     </row>
     <row r="48" spans="1:10" ht="42" customHeight="1">
       <c r="A48" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B48" s="8">
         <v>4</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D48" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>163</v>
-      </c>
       <c r="F48" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
@@ -5479,25 +5497,25 @@
     </row>
     <row r="49" spans="1:10" ht="42" customHeight="1">
       <c r="A49" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B49" s="7">
         <v>4</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D49" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="F49" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="G49" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="G49" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -5507,25 +5525,25 @@
     </row>
     <row r="50" spans="1:10" ht="42" customHeight="1">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B50" s="8">
         <v>4</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D50" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="F50" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="G50" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -5535,19 +5553,19 @@
     </row>
     <row r="51" spans="1:10" ht="42" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B51" s="8">
         <v>4</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D51" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>176</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -5559,22 +5577,22 @@
     </row>
     <row r="52" spans="1:10" ht="42" customHeight="1">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B52" s="8">
         <v>4</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D52" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="F52" s="5" t="s">
         <v>179</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>180</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
@@ -5585,19 +5603,19 @@
     </row>
     <row r="53" spans="1:10" ht="42" customHeight="1">
       <c r="A53" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B53" s="7">
         <v>4</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D53" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -5609,22 +5627,22 @@
     </row>
     <row r="54" spans="1:10" ht="42" customHeight="1">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B54" s="8">
         <v>4</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D54" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
@@ -5635,25 +5653,25 @@
     </row>
     <row r="55" spans="1:10" ht="42" customHeight="1">
       <c r="A55" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B55" s="8">
         <v>4</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D55" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="F55" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="G55" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>191</v>
       </c>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -5663,22 +5681,22 @@
     </row>
     <row r="56" spans="1:10" ht="42" customHeight="1">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B56" s="8">
         <v>4</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D56" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="F56" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="F56" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
@@ -5689,25 +5707,25 @@
     </row>
     <row r="57" spans="1:10" ht="42" customHeight="1">
       <c r="A57" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B57" s="7">
         <v>4</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D57" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="F57" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="G57" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
@@ -5717,22 +5735,22 @@
     </row>
     <row r="58" spans="1:10" ht="42" customHeight="1">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B58" s="8">
         <v>4</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D58" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="F58" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -5743,25 +5761,25 @@
     </row>
     <row r="59" spans="1:10" ht="42" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B59" s="8">
         <v>4</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D59" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>208</v>
       </c>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
@@ -5771,19 +5789,19 @@
     </row>
     <row r="60" spans="1:10" ht="42" customHeight="1">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B60" s="8">
         <v>4</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D60" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -5795,19 +5813,19 @@
     </row>
     <row r="61" spans="1:10" ht="42" customHeight="1">
       <c r="A61" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B61" s="7">
         <v>4</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -5819,22 +5837,22 @@
     </row>
     <row r="62" spans="1:10" ht="42" customHeight="1">
       <c r="A62" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B62" s="8">
         <v>4</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D62" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="F62" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5845,22 +5863,22 @@
     </row>
     <row r="63" spans="1:10" ht="42" customHeight="1">
       <c r="A63" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B63" s="8">
         <v>4</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
@@ -5871,19 +5889,19 @@
     </row>
     <row r="64" spans="1:10" ht="42" customHeight="1">
       <c r="A64" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B64" s="8">
         <v>4</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D64" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>223</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -5895,19 +5913,19 @@
     </row>
     <row r="65" spans="1:10" ht="42" customHeight="1">
       <c r="A65" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B65" s="7">
         <v>4</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -5919,19 +5937,19 @@
     </row>
     <row r="66" spans="1:10" ht="42" customHeight="1">
       <c r="A66" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B66" s="8">
         <v>4</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D66" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>229</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -5943,19 +5961,19 @@
     </row>
     <row r="67" spans="1:10" ht="42" customHeight="1">
       <c r="A67" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B67" s="8">
         <v>4</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D67" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>231</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>232</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -5967,19 +5985,19 @@
     </row>
     <row r="68" spans="1:10" ht="42" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B68" s="8">
         <v>4</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D68" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>235</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -5991,19 +6009,19 @@
     </row>
     <row r="69" spans="1:10" ht="42" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B69" s="7">
         <v>4</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -6015,19 +6033,19 @@
     </row>
     <row r="70" spans="1:10" ht="42" customHeight="1">
       <c r="A70" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B70" s="7">
         <v>4</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -6037,19 +6055,19 @@
     </row>
     <row r="71" spans="1:10" ht="42" customHeight="1">
       <c r="A71" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B71" s="7">
         <v>4</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -6059,19 +6077,19 @@
     </row>
     <row r="72" spans="1:10" ht="42" customHeight="1">
       <c r="A72" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B72" s="7">
         <v>4</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -6081,19 +6099,19 @@
     </row>
     <row r="73" spans="1:10" ht="42" customHeight="1">
       <c r="A73" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B73" s="7">
         <v>4</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -6103,22 +6121,22 @@
     </row>
     <row r="74" spans="1:10" ht="42" customHeight="1">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B74" s="8">
         <v>4</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D74" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E74" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="F74" s="5" t="s">
         <v>240</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>241</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -6129,19 +6147,19 @@
     </row>
     <row r="75" spans="1:10" ht="42" customHeight="1">
       <c r="A75" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B75" s="8">
         <v>4</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D75" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>244</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -6153,19 +6171,19 @@
     </row>
     <row r="76" spans="1:10" ht="42" customHeight="1">
       <c r="A76" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B76" s="8">
         <v>4</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D76" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="E76" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>247</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -6177,19 +6195,19 @@
     </row>
     <row r="77" spans="1:10" ht="42" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B77" s="7">
         <v>4</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D77" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>250</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -6201,19 +6219,19 @@
     </row>
     <row r="78" spans="1:10" ht="42" customHeight="1">
       <c r="A78" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B78" s="8">
         <v>4</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D78" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -6225,19 +6243,19 @@
     </row>
     <row r="79" spans="1:10" ht="42" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B79" s="8">
         <v>4</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D79" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -6249,19 +6267,19 @@
     </row>
     <row r="80" spans="1:10" ht="42" customHeight="1">
       <c r="A80" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B80" s="8">
         <v>4</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>258</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>259</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -6273,19 +6291,19 @@
     </row>
     <row r="81" spans="1:10" ht="42" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B81" s="7">
         <v>4</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D81" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>261</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>262</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -6297,19 +6315,19 @@
     </row>
     <row r="82" spans="1:10" ht="42" customHeight="1">
       <c r="A82" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B82" s="8">
         <v>4</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D82" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E82" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -6321,19 +6339,19 @@
     </row>
     <row r="83" spans="1:10" ht="42" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B83" s="8">
         <v>4</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D83" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -6345,19 +6363,19 @@
     </row>
     <row r="84" spans="1:10" ht="42" customHeight="1">
       <c r="A84" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B84" s="8">
         <v>4</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D84" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E84" s="5" t="s">
         <v>270</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
@@ -6369,31 +6387,31 @@
     </row>
     <row r="85" spans="1:10" ht="42" customHeight="1">
       <c r="A85" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B85" s="7">
         <v>4</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D85" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="E85" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="F85" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="G85" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="G85" s="5" t="s">
+      <c r="H85" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="H85" s="5" t="s">
+      <c r="I85" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="I85" s="5" t="s">
-        <v>278</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>14</v>
@@ -6401,22 +6419,22 @@
     </row>
     <row r="86" spans="1:10" ht="42" customHeight="1">
       <c r="A86" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B86" s="8">
         <v>4</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D86" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="F86" s="5" t="s">
         <v>281</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>282</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
@@ -6427,19 +6445,19 @@
     </row>
     <row r="87" spans="1:10" ht="42" customHeight="1">
       <c r="A87" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B87" s="8">
         <v>4</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D87" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="E87" s="5" t="s">
         <v>284</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>285</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
@@ -6451,25 +6469,25 @@
     </row>
     <row r="88" spans="1:10" ht="42" customHeight="1">
       <c r="A88" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B88" s="8">
         <v>4</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D88" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="F88" s="5" t="s">
+      <c r="G88" s="5" t="s">
         <v>288</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>289</v>
       </c>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
@@ -6479,19 +6497,19 @@
     </row>
     <row r="89" spans="1:10" ht="42" customHeight="1">
       <c r="A89" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B89" s="8">
         <v>4</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D89" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>740</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>741</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
@@ -6501,19 +6519,19 @@
     </row>
     <row r="90" spans="1:10" ht="42" customHeight="1">
       <c r="A90" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B90" s="8">
         <v>4</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D90" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="E90" s="5" t="s">
         <v>742</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>743</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
@@ -6523,19 +6541,19 @@
     </row>
     <row r="91" spans="1:10" ht="42" customHeight="1">
       <c r="A91" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B91" s="7">
         <v>4</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D91" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E91" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>292</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
@@ -6547,19 +6565,19 @@
     </row>
     <row r="92" spans="1:10" ht="42" customHeight="1">
       <c r="A92" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B92" s="8">
         <v>4</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D92" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E92" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>295</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
@@ -6571,19 +6589,19 @@
     </row>
     <row r="93" spans="1:10" ht="42" customHeight="1">
       <c r="A93" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B93" s="8">
         <v>4</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
@@ -6595,19 +6613,19 @@
     </row>
     <row r="94" spans="1:10" ht="42" customHeight="1">
       <c r="A94" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B94" s="8">
         <v>4</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D94" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="E94" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>300</v>
       </c>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
@@ -6619,28 +6637,28 @@
     </row>
     <row r="95" spans="1:10" ht="42" customHeight="1">
       <c r="A95" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B95" s="7">
         <v>4</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D95" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="E95" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="E95" s="5" t="s">
+      <c r="F95" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="F95" s="5" t="s">
+      <c r="G95" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G95" s="5" t="s">
+      <c r="H95" s="5" t="s">
         <v>305</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>306</v>
       </c>
       <c r="I95" s="5"/>
       <c r="J95" s="5" t="s">
@@ -6649,25 +6667,25 @@
     </row>
     <row r="96" spans="1:10" ht="42" customHeight="1">
       <c r="A96" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B96" s="8">
         <v>4</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D96" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E96" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="E96" s="5" t="s">
+      <c r="F96" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F96" s="5" t="s">
+      <c r="G96" s="5" t="s">
         <v>310</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>311</v>
       </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
@@ -6677,25 +6695,25 @@
     </row>
     <row r="97" spans="1:10" ht="42" customHeight="1">
       <c r="A97" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B97" s="8">
         <v>4</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D97" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="E97" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="E97" s="5" t="s">
+      <c r="F97" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="F97" s="5" t="s">
+      <c r="G97" s="5" t="s">
         <v>315</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>316</v>
       </c>
       <c r="H97" s="5"/>
       <c r="I97" s="5"/>
@@ -6705,19 +6723,19 @@
     </row>
     <row r="98" spans="1:10" ht="42" customHeight="1">
       <c r="A98" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B98" s="8">
         <v>4</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D98" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="E98" s="5" t="s">
         <v>318</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>319</v>
       </c>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
@@ -6729,19 +6747,19 @@
     </row>
     <row r="99" spans="1:10" ht="42" customHeight="1">
       <c r="A99" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B99" s="7">
         <v>4</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D99" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E99" s="5" t="s">
         <v>321</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>322</v>
       </c>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
@@ -6753,28 +6771,28 @@
     </row>
     <row r="100" spans="1:10" ht="42" customHeight="1">
       <c r="A100" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B100" s="8">
         <v>4</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D100" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="E100" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="E100" s="5" t="s">
+      <c r="F100" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="F100" s="5" t="s">
+      <c r="G100" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="H100" s="5" t="s">
         <v>327</v>
-      </c>
-      <c r="H100" s="5" t="s">
-        <v>328</v>
       </c>
       <c r="I100" s="5"/>
       <c r="J100" s="5" t="s">
@@ -6783,19 +6801,19 @@
     </row>
     <row r="101" spans="1:10" ht="42" customHeight="1">
       <c r="A101" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B101" s="8">
         <v>4</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D101" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="E101" s="5" t="s">
         <v>330</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>331</v>
       </c>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
@@ -6807,19 +6825,19 @@
     </row>
     <row r="102" spans="1:10" ht="42" customHeight="1">
       <c r="A102" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B102" s="8">
         <v>4</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D102" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="E102" s="5" t="s">
         <v>744</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>745</v>
       </c>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
@@ -6829,19 +6847,19 @@
     </row>
     <row r="103" spans="1:10" ht="42" customHeight="1">
       <c r="A103" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B103" s="8">
         <v>4</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D103" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="E103" s="5" t="s">
         <v>746</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>747</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
@@ -6851,19 +6869,19 @@
     </row>
     <row r="104" spans="1:10" ht="42" customHeight="1">
       <c r="A104" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B104" s="8">
         <v>4</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D104" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="E104" s="5" t="s">
         <v>748</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>749</v>
       </c>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
@@ -6873,19 +6891,19 @@
     </row>
     <row r="105" spans="1:10" ht="42" customHeight="1">
       <c r="A105" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B105" s="8">
         <v>4</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D105" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="E105" s="5" t="s">
         <v>750</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>751</v>
       </c>
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
@@ -6895,19 +6913,19 @@
     </row>
     <row r="106" spans="1:10" ht="42" customHeight="1">
       <c r="A106" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B106" s="8">
         <v>4</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D106" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="E106" s="5" t="s">
         <v>752</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>753</v>
       </c>
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
@@ -6917,22 +6935,22 @@
     </row>
     <row r="107" spans="1:10" ht="42" customHeight="1">
       <c r="A107" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B107" s="8">
         <v>4</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D107" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="E107" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="E107" s="5" t="s">
+      <c r="F107" s="5" t="s">
         <v>334</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>335</v>
       </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
@@ -6943,22 +6961,22 @@
     </row>
     <row r="108" spans="1:10" ht="42" customHeight="1">
       <c r="A108" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B108" s="7">
         <v>4</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D108" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="E108" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="E108" s="5" t="s">
+      <c r="F108" s="5" t="s">
         <v>338</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>339</v>
       </c>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -6969,19 +6987,19 @@
     </row>
     <row r="109" spans="1:10" ht="42" customHeight="1">
       <c r="A109" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B109" s="8">
         <v>4</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D109" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="E109" s="5" t="s">
         <v>341</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>342</v>
       </c>
       <c r="F109" s="5"/>
       <c r="G109" s="5"/>
@@ -6993,19 +7011,19 @@
     </row>
     <row r="110" spans="1:10" ht="42" customHeight="1">
       <c r="A110" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B110" s="8">
         <v>4</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D110" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E110" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="E110" s="5" t="s">
-        <v>345</v>
       </c>
       <c r="F110" s="5"/>
       <c r="G110" s="5"/>
@@ -7017,22 +7035,22 @@
     </row>
     <row r="111" spans="1:10" ht="42" customHeight="1">
       <c r="A111" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B111" s="8">
         <v>4</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D111" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E111" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="E111" s="5" t="s">
+      <c r="F111" s="5" t="s">
         <v>348</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>349</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
@@ -7043,19 +7061,19 @@
     </row>
     <row r="112" spans="1:10" ht="42" customHeight="1">
       <c r="A112" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B112" s="7">
         <v>4</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D112" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="E112" s="5" t="s">
         <v>351</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>352</v>
       </c>
       <c r="F112" s="5"/>
       <c r="G112" s="5"/>
@@ -7067,19 +7085,19 @@
     </row>
     <row r="113" spans="1:10" ht="42" customHeight="1">
       <c r="A113" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B113" s="8">
         <v>4</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D113" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E113" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>355</v>
       </c>
       <c r="F113" s="5"/>
       <c r="G113" s="5"/>
@@ -7091,22 +7109,22 @@
     </row>
     <row r="114" spans="1:10" ht="42" customHeight="1">
       <c r="A114" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B114" s="8">
         <v>4</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D114" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E114" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="E114" s="5" t="s">
+      <c r="F114" s="5" t="s">
         <v>358</v>
-      </c>
-      <c r="F114" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -7117,19 +7135,19 @@
     </row>
     <row r="115" spans="1:10" ht="42" customHeight="1">
       <c r="A115" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B115" s="8">
         <v>4</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D115" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E115" s="5" t="s">
         <v>361</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>362</v>
       </c>
       <c r="F115" s="5"/>
       <c r="G115" s="5"/>
@@ -7141,22 +7159,22 @@
     </row>
     <row r="116" spans="1:10" ht="42" customHeight="1">
       <c r="A116" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B116" s="7">
         <v>4</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D116" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="E116" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="E116" s="5" t="s">
+      <c r="F116" s="5" t="s">
         <v>365</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>366</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
@@ -7167,19 +7185,19 @@
     </row>
     <row r="117" spans="1:10" ht="42" customHeight="1">
       <c r="A117" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B117" s="8">
         <v>4</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D117" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E117" s="5" t="s">
         <v>368</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>369</v>
       </c>
       <c r="F117" s="5"/>
       <c r="G117" s="5"/>
@@ -7191,19 +7209,19 @@
     </row>
     <row r="118" spans="1:10" ht="42" customHeight="1">
       <c r="A118" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B118" s="8">
         <v>4</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D118" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="E118" s="5" t="s">
         <v>371</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>372</v>
       </c>
       <c r="F118" s="5"/>
       <c r="G118" s="5"/>
@@ -7215,25 +7233,25 @@
     </row>
     <row r="119" spans="1:10" ht="42" customHeight="1">
       <c r="A119" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B119" s="8">
         <v>4</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D119" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="E119" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="E119" s="5" t="s">
+      <c r="F119" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="F119" s="5" t="s">
+      <c r="G119" s="5" t="s">
         <v>376</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>377</v>
       </c>
       <c r="H119" s="5"/>
       <c r="I119" s="5"/>
@@ -7243,19 +7261,19 @@
     </row>
     <row r="120" spans="1:10" ht="42" customHeight="1">
       <c r="A120" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B120" s="7">
         <v>4</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D120" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E120" s="5" t="s">
         <v>379</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>380</v>
       </c>
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
@@ -7267,19 +7285,19 @@
     </row>
     <row r="121" spans="1:10" ht="42" customHeight="1">
       <c r="A121" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B121" s="8">
         <v>4</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D121" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E121" s="5" t="s">
         <v>382</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>383</v>
       </c>
       <c r="F121" s="5"/>
       <c r="G121" s="5"/>
@@ -7291,19 +7309,19 @@
     </row>
     <row r="122" spans="1:10" ht="42" customHeight="1">
       <c r="A122" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B122" s="8">
         <v>4</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D122" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="E122" s="5" t="s">
         <v>385</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>386</v>
       </c>
       <c r="F122" s="5"/>
       <c r="G122" s="5"/>
@@ -7315,19 +7333,19 @@
     </row>
     <row r="123" spans="1:10" ht="42" customHeight="1">
       <c r="A123" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B123" s="8">
         <v>4</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D123" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="E123" s="5" t="s">
         <v>388</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>389</v>
       </c>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
@@ -7339,25 +7357,25 @@
     </row>
     <row r="124" spans="1:10" ht="42" customHeight="1">
       <c r="A124" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B124" s="7">
         <v>4</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D124" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E124" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="E124" s="5" t="s">
+      <c r="F124" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="F124" s="5" t="s">
+      <c r="G124" s="5" t="s">
         <v>393</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>394</v>
       </c>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
@@ -7367,19 +7385,19 @@
     </row>
     <row r="125" spans="1:10" ht="42" customHeight="1">
       <c r="A125" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B125" s="8">
         <v>4</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D125" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="E125" s="5" t="s">
         <v>396</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>397</v>
       </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
@@ -7391,19 +7409,19 @@
     </row>
     <row r="126" spans="1:10" ht="42" customHeight="1">
       <c r="A126" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B126" s="8">
         <v>4</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D126" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="E126" s="5" t="s">
         <v>399</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>400</v>
       </c>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
@@ -7415,25 +7433,25 @@
     </row>
     <row r="127" spans="1:10" ht="42" customHeight="1">
       <c r="A127" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B127" s="8">
         <v>4</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D127" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="E127" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="E127" s="5" t="s">
+      <c r="F127" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="F127" s="5" t="s">
+      <c r="G127" s="5" t="s">
         <v>404</v>
-      </c>
-      <c r="G127" s="5" t="s">
-        <v>405</v>
       </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
@@ -7443,19 +7461,19 @@
     </row>
     <row r="128" spans="1:10" ht="42" customHeight="1">
       <c r="A128" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B128" s="7">
         <v>4</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D128" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E128" s="5" t="s">
         <v>407</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>408</v>
       </c>
       <c r="F128" s="5"/>
       <c r="G128" s="5"/>
@@ -7467,19 +7485,19 @@
     </row>
     <row r="129" spans="1:10" ht="42" customHeight="1">
       <c r="A129" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B129" s="7">
         <v>4</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D129" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="E129" s="5" t="s">
         <v>754</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>755</v>
       </c>
       <c r="F129" s="5"/>
       <c r="G129" s="5"/>
@@ -7489,19 +7507,19 @@
     </row>
     <row r="130" spans="1:10" ht="42" customHeight="1">
       <c r="A130" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B130" s="8">
         <v>4</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="F130" s="5"/>
       <c r="G130" s="5"/>
@@ -7511,19 +7529,19 @@
     </row>
     <row r="131" spans="1:10" ht="42" customHeight="1">
       <c r="A131" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B131" s="8">
         <v>4</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
@@ -7533,19 +7551,19 @@
     </row>
     <row r="132" spans="1:10" ht="42" customHeight="1">
       <c r="A132" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B132" s="7">
         <v>4</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
@@ -7555,52 +7573,52 @@
     </row>
     <row r="133" spans="1:10" ht="42" customHeight="1">
       <c r="A133" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B133" s="7">
         <v>4</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E133" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="F133" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="F133" s="5" t="s">
+      <c r="G133" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="G133" s="5" t="s">
+      <c r="H133" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="H133" s="5" t="s">
+      <c r="I133" s="5" t="s">
         <v>765</v>
-      </c>
-      <c r="I133" s="5" t="s">
-        <v>766</v>
       </c>
       <c r="J133" s="5"/>
     </row>
     <row r="134" spans="1:10" ht="42" customHeight="1">
       <c r="A134" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B134" s="7">
         <v>4</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D134" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="E134" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="E134" s="5" t="s">
+      <c r="F134" s="5" t="s">
         <v>768</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>769</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
@@ -7609,22 +7627,22 @@
     </row>
     <row r="135" spans="1:10" ht="42" customHeight="1">
       <c r="A135" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B135" s="8">
         <v>4</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D135" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="E135" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="E135" s="5" t="s">
+      <c r="F135" s="5" t="s">
         <v>411</v>
-      </c>
-      <c r="F135" s="5" t="s">
-        <v>412</v>
       </c>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
@@ -7635,19 +7653,19 @@
     </row>
     <row r="136" spans="1:10" ht="42" customHeight="1">
       <c r="A136" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B136" s="8">
         <v>4</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D136" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E136" s="5" t="s">
         <v>414</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>415</v>
       </c>
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
@@ -7659,19 +7677,19 @@
     </row>
     <row r="137" spans="1:10" ht="42" customHeight="1">
       <c r="A137" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B137" s="8">
         <v>4</v>
       </c>
       <c r="C137" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D137" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="E137" s="5" t="s">
         <v>417</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>418</v>
       </c>
       <c r="F137" s="5"/>
       <c r="G137" s="5"/>
@@ -7683,28 +7701,28 @@
     </row>
     <row r="138" spans="1:10" ht="42" customHeight="1">
       <c r="A138" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B138" s="7">
         <v>4</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D138" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="E138" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="E138" s="5" t="s">
+      <c r="F138" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="F138" s="5" t="s">
+      <c r="G138" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="G138" s="5" t="s">
+      <c r="H138" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="H138" s="5" t="s">
-        <v>424</v>
       </c>
       <c r="I138" s="5"/>
       <c r="J138" s="5" t="s">
@@ -7713,19 +7731,19 @@
     </row>
     <row r="139" spans="1:10" ht="42" customHeight="1">
       <c r="A139" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B139" s="8">
         <v>4</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D139" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="E139" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>427</v>
       </c>
       <c r="F139" s="5"/>
       <c r="G139" s="5"/>
@@ -7737,19 +7755,19 @@
     </row>
     <row r="140" spans="1:10" ht="42" customHeight="1">
       <c r="A140" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B140" s="8">
         <v>4</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D140" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="E140" s="5" t="s">
         <v>429</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>430</v>
       </c>
       <c r="F140" s="5"/>
       <c r="G140" s="5"/>
@@ -7761,28 +7779,28 @@
     </row>
     <row r="141" spans="1:10" ht="42" customHeight="1">
       <c r="A141" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B141" s="8">
         <v>4</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D141" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F141" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="E141" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="F141" s="5" t="s">
+      <c r="G141" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="G141" s="5" t="s">
+      <c r="H141" s="5" t="s">
         <v>434</v>
-      </c>
-      <c r="H141" s="5" t="s">
-        <v>435</v>
       </c>
       <c r="I141" s="5"/>
       <c r="J141" s="5" t="s">
@@ -7791,22 +7809,22 @@
     </row>
     <row r="142" spans="1:10" ht="42" customHeight="1">
       <c r="A142" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B142" s="7">
         <v>4</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D142" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E142" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="E142" s="5" t="s">
+      <c r="F142" s="5" t="s">
         <v>438</v>
-      </c>
-      <c r="F142" s="5" t="s">
-        <v>439</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -7817,19 +7835,19 @@
     </row>
     <row r="143" spans="1:10" ht="42" customHeight="1">
       <c r="A143" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B143" s="8">
         <v>4</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D143" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E143" s="5" t="s">
         <v>441</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>442</v>
       </c>
       <c r="F143" s="5"/>
       <c r="G143" s="5"/>
@@ -7841,19 +7859,19 @@
     </row>
     <row r="144" spans="1:10" ht="42" customHeight="1">
       <c r="A144" s="4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B144" s="7">
         <v>4</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D144" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="E144" s="5" t="s">
         <v>771</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>772</v>
       </c>
       <c r="F144" s="5"/>
       <c r="G144" s="5"/>
@@ -7863,19 +7881,19 @@
     </row>
     <row r="145" spans="1:10" ht="42" customHeight="1">
       <c r="A145" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B145" s="8">
         <v>4</v>
       </c>
       <c r="C145" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D145" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="E145" s="5" t="s">
         <v>773</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>774</v>
       </c>
       <c r="F145" s="5"/>
       <c r="G145" s="5"/>
@@ -7885,19 +7903,19 @@
     </row>
     <row r="146" spans="1:10" ht="42" customHeight="1">
       <c r="A146" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B146" s="8">
         <v>4</v>
       </c>
       <c r="C146" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D146" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E146" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>445</v>
       </c>
       <c r="F146" s="5"/>
       <c r="G146" s="5"/>
@@ -7909,19 +7927,19 @@
     </row>
     <row r="147" spans="1:10" ht="42" customHeight="1">
       <c r="A147" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B147" s="8">
         <v>4</v>
       </c>
       <c r="C147" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D147" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E147" s="5" t="s">
         <v>447</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>448</v>
       </c>
       <c r="F147" s="5"/>
       <c r="G147" s="5"/>
@@ -7933,31 +7951,31 @@
     </row>
     <row r="148" spans="1:10" ht="42" customHeight="1">
       <c r="A148" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B148" s="7">
         <v>4</v>
       </c>
       <c r="C148" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D148" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="E148" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="E148" s="5" t="s">
+      <c r="F148" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="F148" s="5" t="s">
+      <c r="G148" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="H148" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="G148" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="H148" s="5" t="s">
+      <c r="I148" s="5" t="s">
         <v>453</v>
-      </c>
-      <c r="I148" s="5" t="s">
-        <v>454</v>
       </c>
       <c r="J148" s="5" t="s">
         <v>14</v>
@@ -7965,19 +7983,19 @@
     </row>
     <row r="149" spans="1:10" ht="42" customHeight="1">
       <c r="A149" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B149" s="8">
         <v>4</v>
       </c>
       <c r="C149" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D149" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="E149" s="5" t="s">
         <v>456</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="F149" s="5"/>
       <c r="G149" s="5"/>
@@ -7989,19 +8007,19 @@
     </row>
     <row r="150" spans="1:10" ht="42" customHeight="1">
       <c r="A150" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B150" s="8">
         <v>4</v>
       </c>
       <c r="C150" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D150" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="E150" s="5" t="s">
         <v>459</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>460</v>
       </c>
       <c r="F150" s="5"/>
       <c r="G150" s="5"/>
@@ -8013,22 +8031,22 @@
     </row>
     <row r="151" spans="1:10" ht="42" customHeight="1">
       <c r="A151" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B151" s="8">
         <v>4</v>
       </c>
       <c r="C151" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D151" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="E151" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="E151" s="5" t="s">
+      <c r="F151" s="5" t="s">
         <v>463</v>
-      </c>
-      <c r="F151" s="5" t="s">
-        <v>464</v>
       </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
@@ -8039,19 +8057,19 @@
     </row>
     <row r="152" spans="1:10" ht="42" customHeight="1">
       <c r="A152" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B152" s="7">
         <v>4</v>
       </c>
       <c r="C152" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D152" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="E152" s="5" t="s">
         <v>466</v>
-      </c>
-      <c r="E152" s="5" t="s">
-        <v>467</v>
       </c>
       <c r="F152" s="5"/>
       <c r="G152" s="5"/>
@@ -8063,19 +8081,19 @@
     </row>
     <row r="153" spans="1:10" ht="42" customHeight="1">
       <c r="A153" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B153" s="8">
         <v>4</v>
       </c>
       <c r="C153" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D153" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="E153" s="5" t="s">
         <v>469</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>470</v>
       </c>
       <c r="F153" s="5"/>
       <c r="G153" s="5"/>
@@ -8087,49 +8105,49 @@
     </row>
     <row r="154" spans="1:10" ht="42" customHeight="1">
       <c r="A154" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B154" s="8">
         <v>4</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D154" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="E154" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="E154" s="5" t="s">
+      <c r="F154" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="F154" s="5" t="s">
+      <c r="G154" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="G154" s="5" t="s">
+      <c r="H154" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="H154" s="5" t="s">
+      <c r="I154" s="5" t="s">
         <v>797</v>
-      </c>
-      <c r="I154" s="5" t="s">
-        <v>798</v>
       </c>
       <c r="J154" s="5"/>
     </row>
     <row r="155" spans="1:10" ht="42" customHeight="1">
       <c r="A155" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B155" s="8">
         <v>4</v>
       </c>
       <c r="C155" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F155" s="5"/>
       <c r="G155" s="5"/>
@@ -8139,19 +8157,19 @@
     </row>
     <row r="156" spans="1:10" ht="42" customHeight="1">
       <c r="A156" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B156" s="8">
         <v>4</v>
       </c>
       <c r="C156" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F156" s="5"/>
       <c r="G156" s="5"/>
@@ -8161,19 +8179,19 @@
     </row>
     <row r="157" spans="1:10" ht="42" customHeight="1">
       <c r="A157" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B157" s="8">
         <v>4</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5"/>
@@ -8183,19 +8201,19 @@
     </row>
     <row r="158" spans="1:10" ht="42" customHeight="1">
       <c r="A158" s="4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B158" s="8">
         <v>4</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D158" s="10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F158" s="5"/>
       <c r="G158" s="5"/>
@@ -8205,19 +8223,19 @@
     </row>
     <row r="159" spans="1:10" ht="42" customHeight="1">
       <c r="A159" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B159" s="8">
         <v>4</v>
       </c>
       <c r="C159" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D159" s="10" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F159" s="5"/>
       <c r="G159" s="5"/>
@@ -8227,19 +8245,19 @@
     </row>
     <row r="160" spans="1:10" ht="42" customHeight="1">
       <c r="A160" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B160" s="8">
         <v>4</v>
       </c>
       <c r="C160" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D160" s="10" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="F160" s="5"/>
       <c r="G160" s="5"/>
@@ -8249,19 +8267,19 @@
     </row>
     <row r="161" spans="1:10" ht="42" customHeight="1">
       <c r="A161" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B161" s="8">
         <v>4</v>
       </c>
       <c r="C161" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D161" s="10" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F161" s="5"/>
       <c r="G161" s="5"/>
@@ -8271,19 +8289,19 @@
     </row>
     <row r="162" spans="1:10" ht="42" customHeight="1">
       <c r="A162" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B162" s="8">
         <v>4</v>
       </c>
       <c r="C162" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D162" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="E162" s="5" t="s">
         <v>784</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>785</v>
       </c>
       <c r="F162" s="5"/>
       <c r="G162" s="5"/>
@@ -8293,19 +8311,19 @@
     </row>
     <row r="163" spans="1:10" ht="42" customHeight="1">
       <c r="A163" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B163" s="8">
         <v>4</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D163" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="E163" s="5" t="s">
         <v>472</v>
-      </c>
-      <c r="E163" s="5" t="s">
-        <v>473</v>
       </c>
       <c r="F163" s="5"/>
       <c r="G163" s="5"/>
@@ -8317,19 +8335,19 @@
     </row>
     <row r="164" spans="1:10" ht="42" customHeight="1">
       <c r="A164" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B164" s="8">
         <v>4</v>
       </c>
       <c r="C164" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D164" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="E164" s="5" t="s">
         <v>475</v>
-      </c>
-      <c r="E164" s="5" t="s">
-        <v>476</v>
       </c>
       <c r="F164" s="5"/>
       <c r="G164" s="5"/>
@@ -8341,19 +8359,19 @@
     </row>
     <row r="165" spans="1:10" ht="42" customHeight="1">
       <c r="A165" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B165" s="7">
         <v>4</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D165" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E165" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="E165" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="F165" s="5"/>
       <c r="G165" s="5"/>
@@ -8365,22 +8383,22 @@
     </row>
     <row r="166" spans="1:10" ht="42" customHeight="1">
       <c r="A166" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B166" s="8">
         <v>4</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D166" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="E166" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="E166" s="5" t="s">
-        <v>482</v>
-      </c>
       <c r="F166" s="5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="5"/>
@@ -8391,19 +8409,19 @@
     </row>
     <row r="167" spans="1:10" ht="42" customHeight="1">
       <c r="A167" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B167" s="8">
         <v>4</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D167" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="E167" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="E167" s="5" t="s">
-        <v>485</v>
       </c>
       <c r="F167" s="5"/>
       <c r="G167" s="5"/>
@@ -8415,19 +8433,19 @@
     </row>
     <row r="168" spans="1:10" ht="42" customHeight="1">
       <c r="A168" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B168" s="8">
         <v>4</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D168" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="E168" s="5" t="s">
         <v>487</v>
-      </c>
-      <c r="E168" s="5" t="s">
-        <v>488</v>
       </c>
       <c r="F168" s="5"/>
       <c r="G168" s="5"/>
@@ -8439,25 +8457,25 @@
     </row>
     <row r="169" spans="1:10" ht="42" customHeight="1">
       <c r="A169" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B169" s="7">
         <v>4</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D169" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="E169" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="E169" s="5" t="s">
+      <c r="F169" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="F169" s="5" t="s">
+      <c r="G169" s="5" t="s">
         <v>492</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>493</v>
       </c>
       <c r="H169" s="5"/>
       <c r="I169" s="5"/>
@@ -8467,22 +8485,22 @@
     </row>
     <row r="170" spans="1:10" ht="42" customHeight="1">
       <c r="A170" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B170" s="8">
         <v>4</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D170" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="E170" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="E170" s="5" t="s">
+      <c r="F170" s="5" t="s">
         <v>496</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>497</v>
       </c>
       <c r="G170" s="5"/>
       <c r="H170" s="5"/>
@@ -8493,22 +8511,22 @@
     </row>
     <row r="171" spans="1:10" ht="42" customHeight="1">
       <c r="A171" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B171" s="8">
         <v>4</v>
       </c>
       <c r="C171" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D171" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="E171" s="5" t="s">
+      <c r="F171" s="5" t="s">
         <v>500</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>501</v>
       </c>
       <c r="G171" s="5"/>
       <c r="H171" s="5"/>
@@ -8519,25 +8537,25 @@
     </row>
     <row r="172" spans="1:10" ht="42" customHeight="1">
       <c r="A172" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B172" s="8">
         <v>4</v>
       </c>
       <c r="C172" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D172" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="E172" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="E172" s="5" t="s">
+      <c r="F172" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="F172" s="5" t="s">
+      <c r="G172" s="5" t="s">
         <v>505</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>506</v>
       </c>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
@@ -8547,22 +8565,22 @@
     </row>
     <row r="173" spans="1:10" ht="42" customHeight="1">
       <c r="A173" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B173" s="7">
         <v>4</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D173" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="E173" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="E173" s="5" t="s">
+      <c r="F173" s="5" t="s">
         <v>509</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>510</v>
       </c>
       <c r="G173" s="5"/>
       <c r="H173" s="5"/>
@@ -8573,22 +8591,22 @@
     </row>
     <row r="174" spans="1:10" ht="42" customHeight="1">
       <c r="A174" s="4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B174" s="8">
         <v>4</v>
       </c>
       <c r="C174" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D174" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="E174" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="E174" s="5" t="s">
+      <c r="F174" s="5" t="s">
         <v>513</v>
-      </c>
-      <c r="F174" s="5" t="s">
-        <v>514</v>
       </c>
       <c r="G174" s="5"/>
       <c r="H174" s="5"/>
@@ -8599,19 +8617,19 @@
     </row>
     <row r="175" spans="1:10" ht="42" customHeight="1">
       <c r="A175" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B175" s="8">
         <v>4</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D175" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>516</v>
-      </c>
-      <c r="E175" s="5" t="s">
-        <v>517</v>
       </c>
       <c r="F175" s="5"/>
       <c r="G175" s="5"/>
@@ -8623,19 +8641,19 @@
     </row>
     <row r="176" spans="1:10" ht="42" customHeight="1">
       <c r="A176" s="4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B176" s="8">
         <v>4</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D176" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="E176" s="5" t="s">
         <v>519</v>
-      </c>
-      <c r="E176" s="5" t="s">
-        <v>520</v>
       </c>
       <c r="F176" s="5"/>
       <c r="G176" s="5"/>
@@ -8647,19 +8665,19 @@
     </row>
     <row r="177" spans="1:10" ht="42" customHeight="1">
       <c r="A177" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B177" s="7">
         <v>4</v>
       </c>
       <c r="C177" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D177" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="E177" s="5" t="s">
         <v>522</v>
-      </c>
-      <c r="E177" s="5" t="s">
-        <v>523</v>
       </c>
       <c r="F177" s="5"/>
       <c r="G177" s="5"/>
@@ -8671,19 +8689,19 @@
     </row>
     <row r="178" spans="1:10" ht="42" customHeight="1">
       <c r="A178" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B178" s="7">
         <v>4</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D178" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="E178" s="5" t="s">
         <v>775</v>
-      </c>
-      <c r="E178" s="5" t="s">
-        <v>776</v>
       </c>
       <c r="F178" s="5"/>
       <c r="G178" s="5"/>
@@ -8693,19 +8711,19 @@
     </row>
     <row r="179" spans="1:10" ht="42" customHeight="1">
       <c r="A179" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B179" s="8">
         <v>4</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D179" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="E179" s="5" t="s">
         <v>525</v>
-      </c>
-      <c r="E179" s="5" t="s">
-        <v>526</v>
       </c>
       <c r="F179" s="5"/>
       <c r="G179" s="5"/>
@@ -8717,19 +8735,19 @@
     </row>
     <row r="180" spans="1:10" ht="42" customHeight="1">
       <c r="A180" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B180" s="8">
         <v>4</v>
       </c>
       <c r="C180" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D180" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="E180" s="5" t="s">
         <v>528</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>529</v>
       </c>
       <c r="F180" s="5"/>
       <c r="G180" s="5"/>
@@ -8741,19 +8759,19 @@
     </row>
     <row r="181" spans="1:10" ht="42" customHeight="1">
       <c r="A181" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B181" s="8">
         <v>4</v>
       </c>
       <c r="C181" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D181" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="E181" s="5" t="s">
         <v>531</v>
-      </c>
-      <c r="E181" s="5" t="s">
-        <v>532</v>
       </c>
       <c r="F181" s="5"/>
       <c r="G181" s="5"/>
@@ -8765,19 +8783,19 @@
     </row>
     <row r="182" spans="1:10" ht="42" customHeight="1">
       <c r="A182" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B182" s="7">
         <v>4</v>
       </c>
       <c r="C182" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D182" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="E182" s="5" t="s">
         <v>534</v>
-      </c>
-      <c r="E182" s="5" t="s">
-        <v>535</v>
       </c>
       <c r="F182" s="5"/>
       <c r="G182" s="5"/>
@@ -8789,19 +8807,19 @@
     </row>
     <row r="183" spans="1:10" ht="42" customHeight="1">
       <c r="A183" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B183" s="8">
         <v>4</v>
       </c>
       <c r="C183" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D183" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="E183" s="5" t="s">
         <v>537</v>
-      </c>
-      <c r="E183" s="5" t="s">
-        <v>538</v>
       </c>
       <c r="F183" s="5"/>
       <c r="G183" s="5"/>
@@ -8813,19 +8831,19 @@
     </row>
     <row r="184" spans="1:10" ht="42" customHeight="1">
       <c r="A184" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B184" s="8">
         <v>4</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D184" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="E184" s="5" t="s">
         <v>540</v>
-      </c>
-      <c r="E184" s="5" t="s">
-        <v>541</v>
       </c>
       <c r="F184" s="5"/>
       <c r="G184" s="5"/>
@@ -8837,25 +8855,25 @@
     </row>
     <row r="185" spans="1:10" ht="42" customHeight="1">
       <c r="A185" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B185" s="8">
         <v>4</v>
       </c>
       <c r="C185" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D185" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="E185" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="E185" s="5" t="s">
+      <c r="F185" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="F185" s="5" t="s">
-        <v>545</v>
-      </c>
       <c r="G185" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H185" s="5"/>
       <c r="I185" s="5"/>
@@ -8865,19 +8883,19 @@
     </row>
     <row r="186" spans="1:10" ht="42" customHeight="1">
       <c r="A186" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B186" s="7">
         <v>4</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D186" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="E186" s="5" t="s">
         <v>547</v>
-      </c>
-      <c r="E186" s="5" t="s">
-        <v>548</v>
       </c>
       <c r="F186" s="5"/>
       <c r="G186" s="5"/>
@@ -8889,19 +8907,19 @@
     </row>
     <row r="187" spans="1:10" ht="42" customHeight="1">
       <c r="A187" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B187" s="8">
         <v>4</v>
       </c>
       <c r="C187" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D187" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="E187" s="5" t="s">
         <v>550</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>551</v>
       </c>
       <c r="F187" s="5"/>
       <c r="G187" s="5"/>
@@ -8913,19 +8931,19 @@
     </row>
     <row r="188" spans="1:10" ht="42" customHeight="1">
       <c r="A188" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B188" s="8">
         <v>4</v>
       </c>
       <c r="C188" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D188" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="E188" s="5" t="s">
         <v>553</v>
-      </c>
-      <c r="E188" s="5" t="s">
-        <v>554</v>
       </c>
       <c r="F188" s="5"/>
       <c r="G188" s="5"/>
@@ -8937,19 +8955,19 @@
     </row>
     <row r="189" spans="1:10" ht="42" customHeight="1">
       <c r="A189" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B189" s="8">
         <v>4</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D189" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="E189" s="5" t="s">
         <v>556</v>
-      </c>
-      <c r="E189" s="5" t="s">
-        <v>557</v>
       </c>
       <c r="F189" s="5"/>
       <c r="G189" s="5"/>
@@ -8961,19 +8979,19 @@
     </row>
     <row r="190" spans="1:10" ht="42" customHeight="1">
       <c r="A190" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B190" s="7">
         <v>4</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D190" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="E190" s="5" t="s">
         <v>559</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>560</v>
       </c>
       <c r="F190" s="5"/>
       <c r="G190" s="5"/>
@@ -8985,19 +9003,19 @@
     </row>
     <row r="191" spans="1:10" ht="42" customHeight="1">
       <c r="A191" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B191" s="8">
         <v>6</v>
       </c>
       <c r="C191" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D191" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="E191" s="5" t="s">
         <v>562</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>563</v>
       </c>
       <c r="F191" s="5"/>
       <c r="G191" s="5"/>
@@ -9009,19 +9027,19 @@
     </row>
     <row r="192" spans="1:10" ht="42" customHeight="1">
       <c r="A192" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B192" s="8">
         <v>6</v>
       </c>
       <c r="C192" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D192" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="E192" s="5" t="s">
         <v>565</v>
-      </c>
-      <c r="E192" s="5" t="s">
-        <v>566</v>
       </c>
       <c r="F192" s="5"/>
       <c r="G192" s="5"/>
@@ -9033,22 +9051,22 @@
     </row>
     <row r="193" spans="1:10" ht="42" customHeight="1">
       <c r="A193" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B193" s="8">
         <v>6</v>
       </c>
       <c r="C193" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D193" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="E193" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="E193" s="5" t="s">
+      <c r="F193" s="5" t="s">
         <v>569</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>570</v>
       </c>
       <c r="G193" s="5"/>
       <c r="H193" s="5"/>
@@ -9059,19 +9077,19 @@
     </row>
     <row r="194" spans="1:10" ht="42" customHeight="1">
       <c r="A194" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B194" s="8">
         <v>6</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D194" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="E194" s="5" t="s">
         <v>572</v>
-      </c>
-      <c r="E194" s="5" t="s">
-        <v>573</v>
       </c>
       <c r="F194" s="5"/>
       <c r="G194" s="5"/>
@@ -9083,19 +9101,19 @@
     </row>
     <row r="195" spans="1:10" ht="42" customHeight="1">
       <c r="A195" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B195" s="8">
         <v>6</v>
       </c>
       <c r="C195" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D195" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="E195" s="5" t="s">
         <v>575</v>
-      </c>
-      <c r="E195" s="5" t="s">
-        <v>576</v>
       </c>
       <c r="F195" s="5"/>
       <c r="G195" s="5"/>
@@ -9107,19 +9125,19 @@
     </row>
     <row r="196" spans="1:10" ht="42" customHeight="1">
       <c r="A196" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B196" s="8">
         <v>6</v>
       </c>
       <c r="C196" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D196" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="E196" s="5" t="s">
         <v>578</v>
-      </c>
-      <c r="E196" s="5" t="s">
-        <v>579</v>
       </c>
       <c r="F196" s="5"/>
       <c r="G196" s="5"/>
@@ -9131,19 +9149,19 @@
     </row>
     <row r="197" spans="1:10" ht="42" customHeight="1">
       <c r="A197" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B197" s="8">
         <v>6</v>
       </c>
       <c r="C197" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D197" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="E197" s="5" t="s">
         <v>581</v>
-      </c>
-      <c r="E197" s="5" t="s">
-        <v>582</v>
       </c>
       <c r="F197" s="5"/>
       <c r="G197" s="5"/>
@@ -9155,19 +9173,19 @@
     </row>
     <row r="198" spans="1:10" ht="42" customHeight="1">
       <c r="A198" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B198" s="8">
         <v>6</v>
       </c>
       <c r="C198" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D198" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="E198" s="5" t="s">
         <v>584</v>
-      </c>
-      <c r="E198" s="5" t="s">
-        <v>585</v>
       </c>
       <c r="F198" s="5"/>
       <c r="G198" s="5"/>
@@ -9179,22 +9197,22 @@
     </row>
     <row r="199" spans="1:10" ht="42" customHeight="1">
       <c r="A199" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B199" s="8">
         <v>6</v>
       </c>
       <c r="C199" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D199" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="E199" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="E199" s="5" t="s">
+      <c r="F199" s="5" t="s">
         <v>588</v>
-      </c>
-      <c r="F199" s="5" t="s">
-        <v>589</v>
       </c>
       <c r="G199" s="5"/>
       <c r="H199" s="5"/>
@@ -9205,19 +9223,19 @@
     </row>
     <row r="200" spans="1:10" ht="42" customHeight="1">
       <c r="A200" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B200" s="8">
         <v>6</v>
       </c>
       <c r="C200" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D200" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="E200" s="5" t="s">
         <v>591</v>
-      </c>
-      <c r="E200" s="5" t="s">
-        <v>592</v>
       </c>
       <c r="F200" s="5"/>
       <c r="G200" s="5"/>
@@ -9229,22 +9247,22 @@
     </row>
     <row r="201" spans="1:10" ht="42" customHeight="1">
       <c r="A201" s="4" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B201" s="8">
         <v>6</v>
       </c>
       <c r="C201" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D201" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="E201" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="E201" s="5" t="s">
+      <c r="F201" s="5" t="s">
         <v>595</v>
-      </c>
-      <c r="F201" s="5" t="s">
-        <v>596</v>
       </c>
       <c r="G201" s="5"/>
       <c r="H201" s="5"/>
@@ -9255,22 +9273,22 @@
     </row>
     <row r="202" spans="1:10" ht="42" customHeight="1">
       <c r="A202" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B202" s="8">
         <v>6</v>
       </c>
       <c r="C202" s="8" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D202" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F202" s="5" t="s">
         <v>598</v>
-      </c>
-      <c r="E202" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="F202" s="5" t="s">
-        <v>599</v>
       </c>
       <c r="G202" s="5"/>
       <c r="H202" s="5"/>
@@ -9281,22 +9299,22 @@
     </row>
     <row r="203" spans="1:10" ht="42" customHeight="1">
       <c r="A203" s="4" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B203" s="8">
         <v>6</v>
       </c>
       <c r="C203" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D203" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="E203" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="E203" s="5" t="s">
+      <c r="F203" s="5" t="s">
         <v>602</v>
-      </c>
-      <c r="F203" s="5" t="s">
-        <v>603</v>
       </c>
       <c r="G203" s="5"/>
       <c r="H203" s="5"/>
@@ -9307,22 +9325,22 @@
     </row>
     <row r="204" spans="1:10" ht="42" customHeight="1">
       <c r="A204" s="4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B204" s="8">
         <v>6</v>
       </c>
       <c r="C204" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D204" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="E204" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="E204" s="5" t="s">
+      <c r="F204" s="5" t="s">
         <v>606</v>
-      </c>
-      <c r="F204" s="5" t="s">
-        <v>607</v>
       </c>
       <c r="G204" s="5"/>
       <c r="H204" s="5"/>
@@ -9333,22 +9351,22 @@
     </row>
     <row r="205" spans="1:10" ht="42" customHeight="1">
       <c r="A205" s="4" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B205" s="8">
         <v>6</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D205" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="E205" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="E205" s="5" t="s">
+      <c r="F205" s="5" t="s">
         <v>610</v>
-      </c>
-      <c r="F205" s="5" t="s">
-        <v>611</v>
       </c>
       <c r="G205" s="5"/>
       <c r="H205" s="5"/>
@@ -9359,22 +9377,22 @@
     </row>
     <row r="206" spans="1:10" ht="42" customHeight="1">
       <c r="A206" s="4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B206" s="8">
         <v>6</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D206" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="E206" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="E206" s="5" t="s">
+      <c r="F206" s="5" t="s">
         <v>614</v>
-      </c>
-      <c r="F206" s="5" t="s">
-        <v>615</v>
       </c>
       <c r="G206" s="5"/>
       <c r="H206" s="5"/>
@@ -9385,19 +9403,19 @@
     </row>
     <row r="207" spans="1:10" ht="42" customHeight="1">
       <c r="A207" s="4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B207" s="8">
         <v>6</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D207" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="E207" s="5" t="s">
         <v>617</v>
-      </c>
-      <c r="E207" s="5" t="s">
-        <v>618</v>
       </c>
       <c r="F207" s="5"/>
       <c r="G207" s="5"/>
@@ -9409,19 +9427,19 @@
     </row>
     <row r="208" spans="1:10" ht="42" customHeight="1">
       <c r="A208" s="4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B208" s="8">
         <v>6</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D208" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="E208" s="5" t="s">
         <v>620</v>
-      </c>
-      <c r="E208" s="5" t="s">
-        <v>621</v>
       </c>
       <c r="F208" s="5"/>
       <c r="G208" s="5"/>
@@ -9433,19 +9451,19 @@
     </row>
     <row r="209" spans="1:10" ht="42" customHeight="1">
       <c r="A209" s="4" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B209" s="8">
         <v>6</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D209" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="E209" s="5" t="s">
         <v>623</v>
-      </c>
-      <c r="E209" s="5" t="s">
-        <v>624</v>
       </c>
       <c r="F209" s="5"/>
       <c r="G209" s="5"/>
@@ -9457,19 +9475,19 @@
     </row>
     <row r="210" spans="1:10" ht="42" customHeight="1">
       <c r="A210" s="4" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B210" s="8">
         <v>6</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D210" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="E210" s="5" t="s">
         <v>626</v>
-      </c>
-      <c r="E210" s="5" t="s">
-        <v>627</v>
       </c>
       <c r="F210" s="5"/>
       <c r="G210" s="5"/>
@@ -9481,19 +9499,19 @@
     </row>
     <row r="211" spans="1:10" ht="42" customHeight="1">
       <c r="A211" s="4" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B211" s="8">
         <v>6</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D211" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="E211" s="5" t="s">
         <v>629</v>
-      </c>
-      <c r="E211" s="5" t="s">
-        <v>630</v>
       </c>
       <c r="F211" s="5"/>
       <c r="G211" s="5"/>
@@ -9505,19 +9523,19 @@
     </row>
     <row r="212" spans="1:10" ht="42" customHeight="1">
       <c r="A212" s="4" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B212" s="8">
         <v>6</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D212" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="E212" s="5" t="s">
         <v>632</v>
-      </c>
-      <c r="E212" s="5" t="s">
-        <v>633</v>
       </c>
       <c r="F212" s="5"/>
       <c r="G212" s="5"/>
@@ -9529,19 +9547,19 @@
     </row>
     <row r="213" spans="1:10" ht="42" customHeight="1">
       <c r="A213" s="4" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B213" s="8">
         <v>6</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D213" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="E213" s="5" t="s">
         <v>635</v>
-      </c>
-      <c r="E213" s="5" t="s">
-        <v>636</v>
       </c>
       <c r="F213" s="5"/>
       <c r="G213" s="5"/>
@@ -9553,22 +9571,22 @@
     </row>
     <row r="214" spans="1:10" ht="42" customHeight="1">
       <c r="A214" s="4" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B214" s="8">
         <v>6</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D214" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="E214" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="E214" s="5" t="s">
+      <c r="F214" s="5" t="s">
         <v>639</v>
-      </c>
-      <c r="F214" s="5" t="s">
-        <v>640</v>
       </c>
       <c r="G214" s="5"/>
       <c r="H214" s="5"/>
@@ -9579,19 +9597,19 @@
     </row>
     <row r="215" spans="1:10" ht="42" customHeight="1">
       <c r="A215" s="4" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B215" s="8">
         <v>6</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D215" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="E215" s="5" t="s">
         <v>642</v>
-      </c>
-      <c r="E215" s="5" t="s">
-        <v>643</v>
       </c>
       <c r="F215" s="5"/>
       <c r="G215" s="5"/>
@@ -9603,19 +9621,19 @@
     </row>
     <row r="216" spans="1:10" ht="42" customHeight="1">
       <c r="A216" s="4" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B216" s="8">
         <v>6</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D216" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="E216" s="5" t="s">
         <v>645</v>
-      </c>
-      <c r="E216" s="5" t="s">
-        <v>646</v>
       </c>
       <c r="F216" s="5"/>
       <c r="G216" s="5"/>
@@ -9627,314 +9645,314 @@
     </row>
     <row r="217" spans="1:10" ht="42" customHeight="1">
       <c r="A217" s="4" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B217" s="8">
         <v>6</v>
       </c>
       <c r="C217" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="D217" s="5" t="s">
         <v>679</v>
       </c>
-      <c r="D217" s="5" t="s">
-        <v>680</v>
-      </c>
       <c r="E217" s="5" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F217" s="5"/>
     </row>
     <row r="218" spans="1:10" ht="42" customHeight="1">
       <c r="A218" s="4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B218" s="8">
         <v>6</v>
       </c>
       <c r="C218" s="8" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="219" spans="1:10" ht="42" customHeight="1">
       <c r="A219" s="4" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B219" s="8">
         <v>6</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="220" spans="1:10" ht="42" customHeight="1">
       <c r="A220" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B220" s="8">
         <v>6</v>
       </c>
       <c r="C220" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F220" s="5" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="221" spans="1:10" ht="42" customHeight="1">
       <c r="A221" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B221" s="8">
         <v>6</v>
       </c>
       <c r="C221" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F221" s="5"/>
     </row>
     <row r="222" spans="1:10" ht="42" customHeight="1">
       <c r="A222" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B222" s="8">
         <v>6</v>
       </c>
       <c r="C222" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F222" s="5"/>
     </row>
     <row r="223" spans="1:10" ht="42" customHeight="1">
       <c r="A223" s="4" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B223" s="8">
         <v>6</v>
       </c>
       <c r="C223" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="224" spans="1:10" ht="42" customHeight="1">
       <c r="A224" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B224" s="8">
         <v>6</v>
       </c>
       <c r="C224" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="225" spans="1:6" ht="42" customHeight="1">
       <c r="A225" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B225" s="8">
         <v>6</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="42" customHeight="1">
       <c r="A226" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B226" s="8">
         <v>6</v>
       </c>
       <c r="C226" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F226" s="5"/>
     </row>
     <row r="227" spans="1:6" ht="42" customHeight="1">
       <c r="A227" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B227" s="8">
         <v>6</v>
       </c>
       <c r="C227" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="42" customHeight="1">
       <c r="A228" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B228" s="8">
         <v>6</v>
       </c>
       <c r="C228" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="42" customHeight="1">
       <c r="A229" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B229" s="8">
         <v>6</v>
       </c>
       <c r="C229" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="42" customHeight="1">
       <c r="A230" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B230" s="8">
         <v>6</v>
       </c>
       <c r="C230" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="42" customHeight="1">
       <c r="A231" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B231" s="8">
         <v>6</v>
       </c>
       <c r="C231" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F231" s="5" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="42" customHeight="1">
       <c r="A232" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B232" s="8">
         <v>6</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F232" s="5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>

--- a/data/question-bank.xlsx
+++ b/data/question-bank.xlsx
@@ -5,22 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsun/Documents/Codex/2026-08-19/referenced-chatgpt-conversation-this-is-an/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsun/Documents/Codex/exam-recall-trainer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8F8F07-AF14-354C-8D34-8D645F2B843A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9900D2CD-37B6-F742-AD4D-432D0CD721C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="600" windowWidth="28200" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="920" yWindow="600" windowWidth="27140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Question Bank" sheetId="1" r:id="rId1"/>
+    <sheet name="CIE_IGCSE_CHEM" sheetId="1" r:id="rId1"/>
+    <sheet name="IB_CHEM_HL" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="1190">
   <si>
     <t>id</t>
   </si>
@@ -3867,6 +3868,1658 @@
       </rPr>
       <t>, which goes into the solution</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 Models of the Particulate Nature of Matter</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2 Models of Bonding and Structure</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 Classification of Matter</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 How Much, How Fast, and How Far</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 What Are the Mechanisms of Chemical Change</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why the first ionization energy decreases when going down the group</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>More shielding, lower attraction between nucleus and outer electrons</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electrons removed from further away from nucleus</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why (a simple covalent compound) has low melting point</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simple molecular covalent compound</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intermolecular forces (or LDF, DPDP) are weak</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe what the circle in benzene ring represents in terms of bonding</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State a physical reason delocalized structure is a better representation of benzene than Kekule structure</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State a chemical reason delocalized structure is a better representation of benzene than Kekule structure</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>All bond lengths are the same</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>All bond angles are the same / Molecule is planar</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Does not easily undergo addition, but will undergo substitution</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>All C-C bond energies are the same</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>enthalpy of hydrogenation is less exothermic than 3x that of cyclohexene</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how modern chemists have improved communication when naming chemical substances</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IUPAC naming system</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Naming rules based on their structure</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain the action of a catalyst</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increases rate of reaction</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Providing an alternative pathway, with lower activation energy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater number of particles have energy greater than activation energy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bond enthalpy values are averages, not specific to this reaction</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bond enthalpies apply to gases but this reaction involves liquids (only apply when there is ACTUAL non-gas species)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain the effect on the spontaneity of the reaction if the temperature was increased / decreased</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>The −TΔS expression becomes more negative / less negative</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>So ΔG becomes more negative / less negative</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increase / decrease in spontaneity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline a reason why NO is a pollutant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forms nitric acid, contributes to acid rain</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contributes to ozone depletion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Respiratory irritant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why A deviates more than B from the ideal gas model</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A has (type of IMF) and B has (type of IMF)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stronger intermolecular forces in A</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State the reason why the nitrate ion contains three identical N-O bonds</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resonance structure / Delocalization of π electrons</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delocalized π electrons</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline, in terms of formal charge, why Lewis formula X is preferred</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Formal charges zero / closest to zero and hence preferred</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Suggest the role of KMnO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> / K</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>Cr</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oxidizing agent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how a buffer solution could be made from (weak acid) and (strong alkali)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Partially neutralize the (weak acid) with (strong alkali)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amount of (strong alkali) added is smaller than the amount of (weak acid) added</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how a buffer solution could be made from (weak alkali) and (strong acid)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Partially neutralize the (weak alkali) with (strong acid)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Amount of (strong acid) added is smaller than the amount of (weak alkali) added</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Predict how adding a small quantity of water would affect the pH of the buffer</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why alkene is susceptible to attack by molecules such as HBr</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>High electron density of C=C bond</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why the entropy change of the reaction is positive / negative</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fewer (more) moles of gaseous reactants form more (fewer) moles of gaseous products</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Outline why the reaction takes place by S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>1 mechanism</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Outline why the reaction takes place by S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2 mechanism</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Primary halogenoalkane</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tertiary halogenoalkane</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Predict, with a reason, a halogenoethane that would react more quickly than bromoethane</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iodoethane</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>C–I bond weaker, easier to break</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remains constant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>As [A−] : [HA] ratio is unchanged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe the difference between an element and a compound</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elements contain only one type of atom / cannot be chemically broken down into simpler substances</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Compounds contain different types of atoms chemically bonded together, in fixed ratios</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how the solutions can produce the most effective buffer</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>High concentration of both acid AND conjugate base</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>n(acid):n(conjugate base) = 1:1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why the complex is colored</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ligand causes d-orbitals to split, creating ΔE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Light is absorbed as electrons transit to a higher energy level in d-d transition</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ΔE corresponds to light in visible region of the spectrum</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Color seen is complementary to the color of light absorbed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe ionic bonding</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe covalent bonding</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electrostatic attraction between oppositely charged ions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electrostatic attraction between shared electron pair and positively charged nuclei</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe one chemical property that makes addition polymer a useful material</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chemically inert</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain, in terms of the intermolecular forces present, the trend in the boiling points of the first few alkanes / alkenes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stronger forces of attraction with increasing chain length / larger number of electrons</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>London dispersion forces</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dipole moments do not cancel out / non-symmetrical molecule</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why ... is polar</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why ... is non-polar</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dipole moments can cancel out / symmetrical molecule</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Explain how ΔH calculation based on bond enthalpy data can have different result from calculation based on ΔH</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> data</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain the molecular geometry of ...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>... bonding pairs and ... lone pairs of electrons around the central atom</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Takes up the orientation where there is least electrostatic repulsion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline ways to distinguish between strong acid and weak acid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure pH: WA has higher pH</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure electrical conductivity: WA has lower electrical conductivity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>React with a metal/metal carbonate: WA reacts more slowly</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Explain how you might experimentally conclude whether the mechanism of a reaction is S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>1 or S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry out the reaction with different concentrations of the nucleophile with all other conditions unchanged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Rate varies with [nucleophile] then S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Rate does not vary with [nucleophile] then S</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contrast covalent and ionic bonds based on the valence electron interactions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Covalent bonding has shared electrons between atoms</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ionic bonding involves electron transfer between atoms</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State the enthalpy term that characterises the strength of the bonding between the ions in an ionic solid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lattice enthalpy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State the feature of the atomic emission spectrum that may be used to find the ionization energy of the element</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Convergence limit</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why the first ionization energy increases when going across the period</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shielding effect stays the same</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Increased positive nuclear charge, greater attraction between nucleus and outer electrons</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why some collisions between reactant molecules do not result in a reaction occurring</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Incorrect orientation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Collision energy is less than activation energy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why the rate of reaction increases as the temperature is increased</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Greater proportion of particles with E&gt;E</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Area under curve when E&gt;E</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> increases at higher temperature</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater frequency of collision</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe observations which confirm that a solid, added to the reaction mixture, is acting as a catalyst</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Solid not consumed in reaction</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reaction rate increased under same conditions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why there are peaks at m/z values less than that of the molecular ion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fragmentation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline what is meant by chiral carbon atom</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A carbon atom bonded to four different atoms or groups</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain how the indicator HInd, that is a weak acid, shows changes in pH using an equation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HInd (aq) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>⇌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> (aq) + Ind</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> (aq)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>HInd and Ind</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> have different colors</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>HInd color in low pH, Ind</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> color in high pH</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State and explain properties of a solid using the kinetic molecular theory model</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State and explain properties of a liquid using the kinetic molecular theory model</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State and explain properties of a gas using the kinetic molecular theory model</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Does not have a fixed shape because particles are free to move</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cannot be compressed because particles are close to each other</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Has a fixed shape because particles are not free to move, can only vibrate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cannot be compressed because particles are touching each other</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can be compressed because particles are far away from each other</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how ... acts as a Lewis base</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how ... acts as a Lewis acid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Donates an electron pair</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accepts an electron pair</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why iodoalkanes react faster than bromoalkanes / chloroalkanes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Due to large atomic radius of I</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>C-I bond weaker than C-Br bond, easier to break</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain what homolytic fission means</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain what heterolytic fission means</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Each atom receives one bonding electron when bond breaks</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Generates free radicals</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Generates charged ions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>One atom receives both bonding electrons when bond breaks</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how a hydrogen bond is formed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>H that is covalently bonded to a N/O/F atom</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Is attracted to the N/O/F atom of neighboring molecule</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater kinetic energy of particles</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline advantages of using ethanol as a fuel instead of gasoline</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ethanol is renewable / sustainable resource</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ethanol has low carbon footprint</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less sulfur dioxide produced than fossil fuels</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less incomplete combustion than fossil fuels</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bonds are polar due to electronegativity differences</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t>1B</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBHL001</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBHL002</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBHL003</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBHL004</t>
+  </si>
+  <si>
+    <t>IBHL005</t>
+  </si>
+  <si>
+    <t>IBHL006</t>
+  </si>
+  <si>
+    <t>IBHL007</t>
+  </si>
+  <si>
+    <t>IBHL008</t>
+  </si>
+  <si>
+    <t>IBHL009</t>
+  </si>
+  <si>
+    <t>IBHL010</t>
+  </si>
+  <si>
+    <t>IBHL011</t>
+  </si>
+  <si>
+    <t>IBHL012</t>
+  </si>
+  <si>
+    <t>IBHL013</t>
+  </si>
+  <si>
+    <t>IBHL014</t>
+  </si>
+  <si>
+    <t>IBHL015</t>
+  </si>
+  <si>
+    <t>IBHL016</t>
+  </si>
+  <si>
+    <t>IBHL017</t>
+  </si>
+  <si>
+    <t>IBHL018</t>
+  </si>
+  <si>
+    <t>IBHL019</t>
+  </si>
+  <si>
+    <t>IBHL020</t>
+  </si>
+  <si>
+    <t>IBHL021</t>
+  </si>
+  <si>
+    <t>IBHL022</t>
+  </si>
+  <si>
+    <t>IBHL023</t>
+  </si>
+  <si>
+    <t>IBHL024</t>
+  </si>
+  <si>
+    <t>IBHL025</t>
+  </si>
+  <si>
+    <t>IBHL026</t>
+  </si>
+  <si>
+    <t>IBHL027</t>
+  </si>
+  <si>
+    <t>IBHL028</t>
+  </si>
+  <si>
+    <t>IBHL029</t>
+  </si>
+  <si>
+    <t>IBHL030</t>
+  </si>
+  <si>
+    <t>IBHL031</t>
+  </si>
+  <si>
+    <t>IBHL032</t>
+  </si>
+  <si>
+    <t>IBHL033</t>
+  </si>
+  <si>
+    <t>IBHL034</t>
+  </si>
+  <si>
+    <t>IBHL035</t>
+  </si>
+  <si>
+    <t>IBHL036</t>
+  </si>
+  <si>
+    <t>IBHL037</t>
+  </si>
+  <si>
+    <t>IBHL038</t>
+  </si>
+  <si>
+    <t>IBHL039</t>
+  </si>
+  <si>
+    <t>IBHL040</t>
+  </si>
+  <si>
+    <t>IBHL041</t>
+  </si>
+  <si>
+    <t>IBHL042</t>
+  </si>
+  <si>
+    <t>IBHL043</t>
+  </si>
+  <si>
+    <t>IBHL044</t>
+  </si>
+  <si>
+    <t>IBHL045</t>
+  </si>
+  <si>
+    <t>IBHL046</t>
+  </si>
+  <si>
+    <t>IBHL047</t>
+  </si>
+  <si>
+    <t>IBHL048</t>
+  </si>
+  <si>
+    <t>IBHL049</t>
+  </si>
+  <si>
+    <t>IBHL050</t>
+  </si>
+  <si>
+    <t>IBHL051</t>
+  </si>
+  <si>
+    <t>IBHL052</t>
+  </si>
+  <si>
+    <t>IBHL053</t>
+  </si>
+  <si>
+    <t>IBHL054</t>
+  </si>
+  <si>
+    <t>IBHL055</t>
+  </si>
+  <si>
+    <t>IBHL056</t>
+  </si>
+  <si>
+    <t>IBHL057</t>
+  </si>
+  <si>
+    <t>IBHL058</t>
+  </si>
+  <si>
+    <t>IBHL059</t>
+  </si>
+  <si>
+    <t>IBHL060</t>
+  </si>
+  <si>
+    <t>IBHL061</t>
+  </si>
+  <si>
+    <t>IBHL062</t>
+  </si>
+  <si>
+    <t>IBHL063</t>
+  </si>
+  <si>
+    <t>IBHL064</t>
+  </si>
+  <si>
+    <t>IBHL065</t>
+  </si>
+  <si>
+    <t>IBHL066</t>
+  </si>
+  <si>
+    <t>IBHL067</t>
+  </si>
+  <si>
+    <t>IBHL068</t>
+  </si>
+  <si>
+    <t>IBHL069</t>
+  </si>
+  <si>
+    <t>IBHL070</t>
+  </si>
+  <si>
+    <t>IBHL071</t>
+  </si>
+  <si>
+    <t>IBHL072</t>
+  </si>
+  <si>
+    <t>1 General Terms</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how recrystallization is carried out</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dissolved in minimum volume hot solvent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Solution allowed to cool slowly</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crystals filtered off</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crystals rinsed with small quantity of cold solvent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State the most important factor to be considered when choosing a solvent for recrystallization</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Solid very soluble in hot solvent AND not very soluble in cold solvent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how impurities with differing solubilities are separated from the desired product</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less soluble impurity removed: filtering hot solution from solids</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deduce how using too much solvent would affect the product of recrystallization</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deduce how using too little solvent would affect the product of recrystallization</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low / decreased yield</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low / decreased purity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how you would separate iron from other substances</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use a magnet to remove iron</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how you would separate sand and sodium chloride</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add excess water to dissolve NaCl</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Filter the sand, and produce saltwater filtrate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heat the sand to dry</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boil off / evaporate water from salt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fractional distillation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>They have different boiling points</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe, with reason, how you would separate methanol and butan-1-ol</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why it is important to seal the chamber for chromatography</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturate chamber with solvent vapor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prevents evaporation of solvent before completion of experiment</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why it is important to keep the start line horizontal when running the chromatograph</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why it is important to keep the start line above the solvent level when running the chromatograph</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prevent angled solvent front for improved separation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Solvent moves straight up paper at same rate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prevent the sample dissolving in the solvent with unpredictable movement</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain how the separation of inks is achieved using paper chromatography</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Continuous cycle of adsorption and desorption</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sample moves when in solvent AND does not move when on paper</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Samples have different attractions / affinities to mobile phase and stationary phase</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Separations based on polarities</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>The student hypothesized there were more than four coloured inks in the mixture. Suggest how the student could modify this chromatography experiment to evaluate the hypothesis</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try different solvent/solvent system</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Run chromatogram on longer paper for longer time</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Run thin layer chromatography / TLC</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Corrosive / skin burn</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage to respiratory tract</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eye damage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poisoning</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline common safety precautions in labs</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline common health and safety risks in lab experiments</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fume hood / respirators</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use of gloves</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Safety goggles</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keep away from flames / use explosive-free container</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline common green chemistry perspectives in labs</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use less reagent - reduce chemical waste</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry out reactions with less effects on global warming</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry out reactions with less effects on depletion of ozone layer</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 Separating Mixtures</t>
+  </si>
+  <si>
+    <t>3 Separating Mixtures</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 Key Experiments</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2 Lab Apparatus</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest how the constant temperature could be easily maintained in a school laboratory</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thermostatic water bath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temperature controlled hot plate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temperature controlled incubator</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State assumptions that are made to calculate the enthalpy of neutralization</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Specific heat capacity of solution is equal to that of water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Density of solution is equal to that of water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest a change to the apparatus that would reduce heat loss for calorimetry</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Replace glass flask with a polystyrene cup</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add a lid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deduce sources of systematic errors for calorimetry experiments</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heat loss to surroundings</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water evaporating from beaker</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not accounting for the heat absorbed by beakers / cups</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce heat loss to surroundings, better insulator</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polystyrene cup has a lower specific heat</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest advantages of replacing glass cup with a polystyrene cup for calorimetry experiments</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>For colorimetry experiment, a student started the experiment and recorded the absorbance value immediately. Suggest why this may not give a reliable result</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equilibrium not reached, reaction still occurring</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>For colorimetry experiment, describe how the solution can be used to construct a calibration curve</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dilute solution to make multiple concentrations</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure the absorbance of these solutions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plot graph of absorbance against concentration with a straight line of best fit</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>For colorimetry experiment, explain how calibration curve can be used to determine the unknown concentration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure the absorbance of the unknown</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use the calibrated graph to determine concentration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe the process of preparing a standard solution from a solid using a volumetric flask</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fully dissolve solid in deionized water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transfer the solution with washings</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fill up to line</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stopper the flask and turn over several times to homogenize the solution</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest how to make a (known c &amp; v solution) from the original (known c &amp; v solution)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry out calculation to find out volume required</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Use ... cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> volumetric pipette / burette to transfer to ... cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> volumetric flask</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fill up to line with deionized water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evaluate the use of an indicator versus a pH probe to determine the end point of the titration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probe more precise</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probe no personal judgement of color change involved</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probes must be calibrated before use</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probes provide continuous monitoring</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probe not chemically adding to system</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest a reason why trial 1 should not be included when finding the mean volume for titration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value not concordant with other values</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mean volume would be too high</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBHL073</t>
+  </si>
+  <si>
+    <t>IBHL074</t>
+  </si>
+  <si>
+    <t>IBHL075</t>
+  </si>
+  <si>
+    <t>IBHL076</t>
+  </si>
+  <si>
+    <t>IBHL077</t>
+  </si>
+  <si>
+    <t>IBHL078</t>
+  </si>
+  <si>
+    <t>IBHL079</t>
+  </si>
+  <si>
+    <t>IBHL080</t>
+  </si>
+  <si>
+    <t>IBHL081</t>
+  </si>
+  <si>
+    <t>IBHL082</t>
+  </si>
+  <si>
+    <t>IBHL083</t>
+  </si>
+  <si>
+    <t>IBHL084</t>
+  </si>
+  <si>
+    <t>IBHL085</t>
+  </si>
+  <si>
+    <t>IBHL086</t>
+  </si>
+  <si>
+    <t>IBHL087</t>
+  </si>
+  <si>
+    <t>IBHL088</t>
+  </si>
+  <si>
+    <t>4 What Drives Chemical Reactions</t>
+  </si>
+  <si>
+    <t>Hot solution filtered</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>More soluble impurity removed: removing / filtering crystals from cold solution</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3874,7 +5527,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -3919,6 +5572,11 @@
       <color rgb="FF000000"/>
       <name val="Aptos"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cambria Math"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3933,7 +5591,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -3993,12 +5651,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF44B3E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4030,12 +5703,21 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
       <font>
         <b/>
@@ -4046,6 +5728,23 @@
           <bgColor rgb="FFFCE8E6"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFB3261E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE8E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4070,8 +5769,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuestionBank" displayName="QuestionBank" ref="A1:J232" totalsRowShown="0">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="paper" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="topic" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="paper" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="topic" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="question"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="answer_1"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="answer_2"/>
@@ -4079,6 +5778,24 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="answer_4"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="answer_5"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="needs_review"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3341C51B-6098-4C4D-86EB-AB33DCEB7697}" name="QuestionBank3" displayName="QuestionBank3" ref="A1:J289" totalsRowShown="0">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{D80898F7-B13A-514A-83F3-0623537EEFE1}" name="id"/>
+    <tableColumn id="2" xr3:uid="{44BE18D2-8686-7F4B-AEEB-F2DB1EFD3E35}" name="paper" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{8A76BF9B-63DC-8842-AFDA-D0EC4C6B5807}" name="topic" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{FB260016-AA57-4F4D-82B5-62D98E8EF2DD}" name="question"/>
+    <tableColumn id="5" xr3:uid="{69EC7B80-4CE5-6245-B62D-04F08F91D7E0}" name="answer_1"/>
+    <tableColumn id="6" xr3:uid="{68DB80DC-776F-6041-B6D0-80D8A6D7B646}" name="answer_2"/>
+    <tableColumn id="7" xr3:uid="{5629F604-FB2A-4E4E-A180-6350699BBBB6}" name="answer_3"/>
+    <tableColumn id="8" xr3:uid="{94C9D2B5-29C7-AB45-A7C3-04A6FDFA80BA}" name="answer_4"/>
+    <tableColumn id="9" xr3:uid="{63313003-860C-7C43-852A-1D6F64FAAF9E}" name="answer_5"/>
+    <tableColumn id="10" xr3:uid="{C3DB7393-33E9-4D4F-80F8-21BCA4B57A31}" name="needs_review"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9958,6 +11675,4526 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="I2:I132 I134:I190">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="yes"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{473DCC94-29A8-C34F-A636-6325DFC4A1BA}">
+  <dimension ref="A1:J289"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="3" width="18" style="9" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="9" width="38" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="42" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B2" s="7">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" ht="42" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B3" s="7">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" ht="42" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" ht="42" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>965</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" ht="42" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="8">
+        <v>2</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>940</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="42" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B7" s="8">
+        <v>2</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" ht="42" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B8" s="8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" ht="42" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B9" s="8">
+        <v>2</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>935</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>937</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" ht="42" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B10" s="8">
+        <v>2</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>938</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" ht="42" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B11" s="8">
+        <v>2</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="42" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B12" s="8">
+        <v>2</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="42" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B13" s="8">
+        <v>2</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" ht="42" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B14" s="8">
+        <v>2</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" ht="42" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B15" s="8">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" ht="42" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B16" s="8">
+        <v>2</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10" ht="42" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B17" s="8">
+        <v>2</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" ht="42" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B18" s="8">
+        <v>2</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10" ht="42" customHeight="1">
+      <c r="A19" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B19" s="8">
+        <v>2</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10" ht="42" customHeight="1">
+      <c r="A20" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B20" s="8">
+        <v>2</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>984</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>985</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10" ht="42" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B21" s="8">
+        <v>2</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:10" ht="42" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B22" s="8">
+        <v>2</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>914</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10" ht="42" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B23" s="7">
+        <v>2</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="1:10" ht="42" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B24" s="7">
+        <v>2</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>943</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="1:10" ht="42" customHeight="1">
+      <c r="A25" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B25" s="8">
+        <v>2</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="1:10" ht="42" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B26" s="8">
+        <v>2</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+    </row>
+    <row r="27" spans="1:10" ht="42" customHeight="1">
+      <c r="A27" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B27" s="8">
+        <v>2</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+    </row>
+    <row r="28" spans="1:10" ht="42" customHeight="1">
+      <c r="A28" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B28" s="8">
+        <v>2</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>916</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+    </row>
+    <row r="29" spans="1:10" ht="42" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B29" s="8">
+        <v>2</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>958</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+    </row>
+    <row r="30" spans="1:10" ht="42" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B30" s="8">
+        <v>2</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+    </row>
+    <row r="31" spans="1:10" ht="42" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B31" s="8">
+        <v>2</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+    </row>
+    <row r="32" spans="1:10" ht="42" customHeight="1">
+      <c r="A32" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B32" s="8">
+        <v>2</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>990</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>992</v>
+      </c>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+    </row>
+    <row r="33" spans="1:10" ht="42" customHeight="1">
+      <c r="A33" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B33" s="8">
+        <v>2</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+    </row>
+    <row r="34" spans="1:10" ht="42" customHeight="1">
+      <c r="A34" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B34" s="8">
+        <v>2</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+    </row>
+    <row r="35" spans="1:10" ht="42" customHeight="1">
+      <c r="A35" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B35" s="7">
+        <v>2</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>946</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>947</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+    </row>
+    <row r="36" spans="1:10" ht="42" customHeight="1">
+      <c r="A36" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B36" s="7">
+        <v>2</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+    </row>
+    <row r="37" spans="1:10" ht="42" customHeight="1">
+      <c r="A37" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B37" s="7">
+        <v>2</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+    </row>
+    <row r="38" spans="1:10" ht="42" customHeight="1">
+      <c r="A38" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B38" s="7">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>950</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+    </row>
+    <row r="39" spans="1:10" ht="42" customHeight="1">
+      <c r="A39" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B39" s="8">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+    </row>
+    <row r="40" spans="1:10" ht="42" customHeight="1">
+      <c r="A40" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B40" s="8">
+        <v>2</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+    </row>
+    <row r="41" spans="1:10" ht="42" customHeight="1">
+      <c r="A41" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B41" s="8">
+        <v>2</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+    </row>
+    <row r="42" spans="1:10" ht="42" customHeight="1">
+      <c r="A42" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B42" s="8">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+    </row>
+    <row r="43" spans="1:10" ht="42" customHeight="1">
+      <c r="A43" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B43" s="8">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+    </row>
+    <row r="44" spans="1:10" ht="42" customHeight="1">
+      <c r="A44" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B44" s="8">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>882</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+    </row>
+    <row r="45" spans="1:10" ht="42" customHeight="1">
+      <c r="A45" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B45" s="8">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+    </row>
+    <row r="46" spans="1:10" ht="42" customHeight="1">
+      <c r="A46" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B46" s="8">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+    </row>
+    <row r="47" spans="1:10" ht="42" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B47" s="8">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>960</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>961</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>962</v>
+      </c>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+    </row>
+    <row r="48" spans="1:10" ht="42" customHeight="1">
+      <c r="A48" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B48" s="8">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+    </row>
+    <row r="49" spans="1:10" ht="42" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B49" s="8">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>978</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>980</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>981</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+    </row>
+    <row r="50" spans="1:10" ht="42" customHeight="1">
+      <c r="A50" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B50" s="8">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>979</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>982</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+    </row>
+    <row r="51" spans="1:10" ht="42" customHeight="1">
+      <c r="A51" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B51" s="8">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>972</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>974</v>
+      </c>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+    </row>
+    <row r="52" spans="1:10" ht="42" customHeight="1">
+      <c r="A52" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B52" s="8">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>973</v>
+      </c>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+    </row>
+    <row r="53" spans="1:10" ht="42" customHeight="1">
+      <c r="A53" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B53" s="8">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+    </row>
+    <row r="54" spans="1:10" ht="42" customHeight="1">
+      <c r="A54" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B54" s="7">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+    </row>
+    <row r="55" spans="1:10" ht="42" customHeight="1">
+      <c r="A55" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B55" s="8">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+    </row>
+    <row r="56" spans="1:10" ht="42" customHeight="1">
+      <c r="A56" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B56" s="8">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>933</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+    </row>
+    <row r="57" spans="1:10" ht="42" customHeight="1">
+      <c r="A57" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B57" s="8">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+    </row>
+    <row r="58" spans="1:10" ht="42" customHeight="1">
+      <c r="A58" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B58" s="8">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>975</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>977</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+    </row>
+    <row r="59" spans="1:10" ht="42" customHeight="1">
+      <c r="A59" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+    </row>
+    <row r="60" spans="1:10" ht="42" customHeight="1">
+      <c r="A60" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>1118</v>
+      </c>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+    </row>
+    <row r="61" spans="1:10" ht="42" customHeight="1">
+      <c r="A61" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+    </row>
+    <row r="62" spans="1:10" ht="42" customHeight="1">
+      <c r="A62" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+    </row>
+    <row r="63" spans="1:10" ht="42" customHeight="1">
+      <c r="A63" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>562</v>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+    </row>
+    <row r="64" spans="1:10" ht="42" customHeight="1">
+      <c r="A64" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+    </row>
+    <row r="65" spans="1:10" ht="42" customHeight="1">
+      <c r="A65" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+    </row>
+    <row r="66" spans="1:10" ht="42" customHeight="1">
+      <c r="A66" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="J66" s="5"/>
+    </row>
+    <row r="67" spans="1:10" ht="42" customHeight="1">
+      <c r="A67" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+    </row>
+    <row r="68" spans="1:10" ht="42" customHeight="1">
+      <c r="A68" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+    </row>
+    <row r="69" spans="1:10" ht="42" customHeight="1">
+      <c r="A69" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+    </row>
+    <row r="70" spans="1:10" ht="42" customHeight="1">
+      <c r="A70" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+    </row>
+    <row r="71" spans="1:10" ht="42" customHeight="1">
+      <c r="A71" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+    </row>
+    <row r="72" spans="1:10" ht="42" customHeight="1">
+      <c r="A72" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+    </row>
+    <row r="73" spans="1:10" ht="42" customHeight="1">
+      <c r="A73" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+    </row>
+    <row r="74" spans="1:10" ht="42" customHeight="1">
+      <c r="A74" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+    </row>
+    <row r="75" spans="1:10" ht="42" customHeight="1">
+      <c r="A75" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+    </row>
+    <row r="76" spans="1:10" ht="42" customHeight="1">
+      <c r="A76" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+    </row>
+    <row r="77" spans="1:10" ht="42" customHeight="1">
+      <c r="A77" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+    </row>
+    <row r="78" spans="1:10" ht="42" customHeight="1">
+      <c r="A78" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+    </row>
+    <row r="79" spans="1:10" ht="42" customHeight="1">
+      <c r="A79" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+    </row>
+    <row r="80" spans="1:10" ht="42" customHeight="1">
+      <c r="A80" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+    </row>
+    <row r="81" spans="1:10" ht="42" customHeight="1">
+      <c r="A81" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+    </row>
+    <row r="82" spans="1:10" ht="42" customHeight="1">
+      <c r="A82" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5"/>
+    </row>
+    <row r="83" spans="1:10" ht="42" customHeight="1">
+      <c r="A83" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5"/>
+    </row>
+    <row r="84" spans="1:10" ht="42" customHeight="1">
+      <c r="A84" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H84" s="5"/>
+      <c r="I84" s="5"/>
+      <c r="J84" s="5"/>
+    </row>
+    <row r="85" spans="1:10" ht="42" customHeight="1">
+      <c r="A85" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5"/>
+    </row>
+    <row r="86" spans="1:10" ht="42" customHeight="1">
+      <c r="A86" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5"/>
+    </row>
+    <row r="87" spans="1:10" ht="42" customHeight="1">
+      <c r="A87" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5"/>
+    </row>
+    <row r="88" spans="1:10" ht="42" customHeight="1">
+      <c r="A88" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="J88" s="5"/>
+    </row>
+    <row r="89" spans="1:10" ht="42" customHeight="1">
+      <c r="A89" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+    </row>
+    <row r="90" spans="1:10" ht="42" customHeight="1">
+      <c r="A90" s="4"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5"/>
+    </row>
+    <row r="91" spans="1:10" ht="42" customHeight="1">
+      <c r="A91" s="4"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+      <c r="I91" s="5"/>
+      <c r="J91" s="5"/>
+    </row>
+    <row r="92" spans="1:10" ht="42" customHeight="1">
+      <c r="A92" s="4"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="5"/>
+    </row>
+    <row r="93" spans="1:10" ht="42" customHeight="1">
+      <c r="A93" s="4"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5"/>
+    </row>
+    <row r="94" spans="1:10" ht="42" customHeight="1">
+      <c r="A94" s="4"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5"/>
+    </row>
+    <row r="95" spans="1:10" ht="42" customHeight="1">
+      <c r="A95" s="4"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+    </row>
+    <row r="96" spans="1:10" ht="42" customHeight="1">
+      <c r="A96" s="4"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5"/>
+    </row>
+    <row r="97" spans="1:10" ht="42" customHeight="1">
+      <c r="A97" s="4"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+    </row>
+    <row r="98" spans="1:10" ht="42" customHeight="1">
+      <c r="A98" s="4"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5"/>
+    </row>
+    <row r="99" spans="1:10" ht="42" customHeight="1">
+      <c r="A99" s="4"/>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5"/>
+    </row>
+    <row r="100" spans="1:10" ht="42" customHeight="1">
+      <c r="A100" s="4"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5"/>
+    </row>
+    <row r="101" spans="1:10" ht="42" customHeight="1">
+      <c r="A101" s="4"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+      <c r="I101" s="5"/>
+      <c r="J101" s="5"/>
+    </row>
+    <row r="102" spans="1:10" ht="42" customHeight="1">
+      <c r="A102" s="4"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+      <c r="I102" s="5"/>
+      <c r="J102" s="5"/>
+    </row>
+    <row r="103" spans="1:10" ht="42" customHeight="1">
+      <c r="A103" s="4"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+      <c r="I103" s="5"/>
+      <c r="J103" s="5"/>
+    </row>
+    <row r="104" spans="1:10" ht="42" customHeight="1">
+      <c r="A104" s="4"/>
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+    </row>
+    <row r="105" spans="1:10" ht="42" customHeight="1">
+      <c r="A105" s="4"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+    </row>
+    <row r="106" spans="1:10" ht="42" customHeight="1">
+      <c r="A106" s="4"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+    </row>
+    <row r="107" spans="1:10" ht="42" customHeight="1">
+      <c r="A107" s="4"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+      <c r="I107" s="5"/>
+      <c r="J107" s="5"/>
+    </row>
+    <row r="108" spans="1:10" ht="42" customHeight="1">
+      <c r="A108" s="4"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+    </row>
+    <row r="109" spans="1:10" ht="42" customHeight="1">
+      <c r="A109" s="4"/>
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+    </row>
+    <row r="110" spans="1:10" ht="42" customHeight="1">
+      <c r="A110" s="4"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+    </row>
+    <row r="111" spans="1:10" ht="42" customHeight="1">
+      <c r="A111" s="4"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+    </row>
+    <row r="112" spans="1:10" ht="42" customHeight="1">
+      <c r="A112" s="4"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="5"/>
+      <c r="H112" s="5"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+    </row>
+    <row r="113" spans="1:10" ht="42" customHeight="1">
+      <c r="A113" s="4"/>
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="5"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+      <c r="I113" s="5"/>
+      <c r="J113" s="5"/>
+    </row>
+    <row r="114" spans="1:10" ht="42" customHeight="1">
+      <c r="A114" s="4"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="8"/>
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="5"/>
+    </row>
+    <row r="115" spans="1:10" ht="42" customHeight="1">
+      <c r="A115" s="4"/>
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="5"/>
+    </row>
+    <row r="116" spans="1:10" ht="42" customHeight="1">
+      <c r="A116" s="4"/>
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
+      <c r="I116" s="5"/>
+      <c r="J116" s="5"/>
+    </row>
+    <row r="117" spans="1:10" ht="42" customHeight="1">
+      <c r="A117" s="4"/>
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+      <c r="I117" s="5"/>
+      <c r="J117" s="5"/>
+    </row>
+    <row r="118" spans="1:10" ht="42" customHeight="1">
+      <c r="A118" s="4"/>
+      <c r="B118" s="7"/>
+      <c r="C118" s="8"/>
+      <c r="D118" s="5"/>
+      <c r="E118" s="5"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+      <c r="I118" s="5"/>
+      <c r="J118" s="5"/>
+    </row>
+    <row r="119" spans="1:10" ht="42" customHeight="1">
+      <c r="A119" s="4"/>
+      <c r="B119" s="8"/>
+      <c r="C119" s="8"/>
+      <c r="D119" s="5"/>
+      <c r="E119" s="5"/>
+      <c r="F119" s="5"/>
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+      <c r="I119" s="5"/>
+      <c r="J119" s="5"/>
+    </row>
+    <row r="120" spans="1:10" ht="42" customHeight="1">
+      <c r="A120" s="4"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="5"/>
+      <c r="E120" s="5"/>
+      <c r="F120" s="5"/>
+      <c r="G120" s="5"/>
+      <c r="H120" s="5"/>
+      <c r="I120" s="5"/>
+      <c r="J120" s="5"/>
+    </row>
+    <row r="121" spans="1:10" ht="42" customHeight="1">
+      <c r="A121" s="4"/>
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
+      <c r="I121" s="5"/>
+      <c r="J121" s="5"/>
+    </row>
+    <row r="122" spans="1:10" ht="42" customHeight="1">
+      <c r="A122" s="4"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="5"/>
+      <c r="E122" s="5"/>
+      <c r="F122" s="5"/>
+      <c r="G122" s="5"/>
+      <c r="H122" s="5"/>
+      <c r="I122" s="5"/>
+      <c r="J122" s="5"/>
+    </row>
+    <row r="123" spans="1:10" ht="42" customHeight="1">
+      <c r="A123" s="4"/>
+      <c r="B123" s="8"/>
+      <c r="C123" s="8"/>
+      <c r="D123" s="5"/>
+      <c r="E123" s="5"/>
+      <c r="F123" s="5"/>
+      <c r="G123" s="5"/>
+      <c r="H123" s="5"/>
+      <c r="I123" s="5"/>
+      <c r="J123" s="5"/>
+    </row>
+    <row r="124" spans="1:10" ht="42" customHeight="1">
+      <c r="A124" s="4"/>
+      <c r="B124" s="8"/>
+      <c r="C124" s="8"/>
+      <c r="D124" s="5"/>
+      <c r="E124" s="5"/>
+      <c r="F124" s="5"/>
+      <c r="G124" s="5"/>
+      <c r="H124" s="5"/>
+      <c r="I124" s="5"/>
+      <c r="J124" s="5"/>
+    </row>
+    <row r="125" spans="1:10" ht="42" customHeight="1">
+      <c r="A125" s="4"/>
+      <c r="B125" s="8"/>
+      <c r="C125" s="8"/>
+      <c r="D125" s="5"/>
+      <c r="E125" s="5"/>
+      <c r="F125" s="5"/>
+      <c r="G125" s="5"/>
+      <c r="H125" s="5"/>
+      <c r="I125" s="5"/>
+      <c r="J125" s="5"/>
+    </row>
+    <row r="126" spans="1:10" ht="42" customHeight="1">
+      <c r="A126" s="4"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="8"/>
+      <c r="D126" s="5"/>
+      <c r="E126" s="5"/>
+      <c r="F126" s="5"/>
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
+      <c r="I126" s="5"/>
+      <c r="J126" s="5"/>
+    </row>
+    <row r="127" spans="1:10" ht="42" customHeight="1">
+      <c r="A127" s="4"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="8"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="5"/>
+      <c r="F127" s="5"/>
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+      <c r="I127" s="5"/>
+      <c r="J127" s="5"/>
+    </row>
+    <row r="128" spans="1:10" ht="42" customHeight="1">
+      <c r="A128" s="4"/>
+      <c r="B128" s="7"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="5"/>
+      <c r="E128" s="5"/>
+      <c r="F128" s="5"/>
+      <c r="G128" s="5"/>
+      <c r="H128" s="5"/>
+      <c r="I128" s="5"/>
+      <c r="J128" s="5"/>
+    </row>
+    <row r="129" spans="1:10" ht="42" customHeight="1">
+      <c r="A129" s="4"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="8"/>
+      <c r="D129" s="5"/>
+      <c r="E129" s="5"/>
+      <c r="F129" s="5"/>
+      <c r="G129" s="5"/>
+      <c r="H129" s="5"/>
+      <c r="I129" s="5"/>
+      <c r="J129" s="5"/>
+    </row>
+    <row r="130" spans="1:10" ht="42" customHeight="1">
+      <c r="A130" s="4"/>
+      <c r="B130" s="7"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="5"/>
+      <c r="F130" s="5"/>
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
+      <c r="I130" s="5"/>
+      <c r="J130" s="5"/>
+    </row>
+    <row r="131" spans="1:10" ht="42" customHeight="1">
+      <c r="A131" s="4"/>
+      <c r="B131" s="8"/>
+      <c r="C131" s="8"/>
+      <c r="D131" s="5"/>
+      <c r="E131" s="5"/>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5"/>
+      <c r="H131" s="5"/>
+      <c r="I131" s="5"/>
+      <c r="J131" s="5"/>
+    </row>
+    <row r="132" spans="1:10" ht="42" customHeight="1">
+      <c r="A132" s="4"/>
+      <c r="B132" s="8"/>
+      <c r="C132" s="8"/>
+      <c r="D132" s="5"/>
+      <c r="E132" s="5"/>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5"/>
+      <c r="H132" s="5"/>
+      <c r="I132" s="5"/>
+      <c r="J132" s="5"/>
+    </row>
+    <row r="133" spans="1:10" ht="42" customHeight="1">
+      <c r="A133" s="4"/>
+      <c r="B133" s="8"/>
+      <c r="C133" s="8"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="5"/>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5"/>
+      <c r="H133" s="5"/>
+      <c r="I133" s="5"/>
+      <c r="J133" s="5"/>
+    </row>
+    <row r="134" spans="1:10" ht="42" customHeight="1">
+      <c r="A134" s="4"/>
+      <c r="B134" s="7"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5"/>
+      <c r="H134" s="5"/>
+      <c r="I134" s="5"/>
+      <c r="J134" s="5"/>
+    </row>
+    <row r="135" spans="1:10" ht="42" customHeight="1">
+      <c r="A135" s="4"/>
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+      <c r="I135" s="5"/>
+      <c r="J135" s="5"/>
+    </row>
+    <row r="136" spans="1:10" ht="42" customHeight="1">
+      <c r="A136" s="4"/>
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="5"/>
+      <c r="E136" s="5"/>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5"/>
+      <c r="H136" s="5"/>
+      <c r="I136" s="5"/>
+      <c r="J136" s="5"/>
+    </row>
+    <row r="137" spans="1:10" ht="42" customHeight="1">
+      <c r="A137" s="4"/>
+      <c r="B137" s="8"/>
+      <c r="C137" s="8"/>
+      <c r="D137" s="5"/>
+      <c r="E137" s="5"/>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5"/>
+      <c r="H137" s="5"/>
+      <c r="I137" s="5"/>
+      <c r="J137" s="5"/>
+    </row>
+    <row r="138" spans="1:10" ht="42" customHeight="1">
+      <c r="A138" s="4"/>
+      <c r="B138" s="7"/>
+      <c r="C138" s="8"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="5"/>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5"/>
+      <c r="H138" s="5"/>
+      <c r="I138" s="5"/>
+      <c r="J138" s="5"/>
+    </row>
+    <row r="139" spans="1:10" ht="42" customHeight="1">
+      <c r="A139" s="4"/>
+      <c r="B139" s="8"/>
+      <c r="C139" s="8"/>
+      <c r="D139" s="5"/>
+      <c r="E139" s="5"/>
+      <c r="F139" s="5"/>
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
+      <c r="I139" s="5"/>
+      <c r="J139" s="5"/>
+    </row>
+    <row r="140" spans="1:10" ht="42" customHeight="1">
+      <c r="A140" s="4"/>
+      <c r="B140" s="8"/>
+      <c r="C140" s="8"/>
+      <c r="D140" s="5"/>
+      <c r="E140" s="5"/>
+      <c r="F140" s="5"/>
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+      <c r="I140" s="5"/>
+      <c r="J140" s="5"/>
+    </row>
+    <row r="141" spans="1:10" ht="42" customHeight="1">
+      <c r="A141" s="4"/>
+      <c r="B141" s="8"/>
+      <c r="C141" s="8"/>
+      <c r="D141" s="5"/>
+      <c r="E141" s="5"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="5"/>
+      <c r="H141" s="5"/>
+      <c r="I141" s="5"/>
+      <c r="J141" s="5"/>
+    </row>
+    <row r="142" spans="1:10" ht="42" customHeight="1">
+      <c r="A142" s="4"/>
+      <c r="B142" s="7"/>
+      <c r="C142" s="8"/>
+      <c r="D142" s="5"/>
+      <c r="E142" s="5"/>
+      <c r="F142" s="5"/>
+      <c r="G142" s="5"/>
+      <c r="H142" s="5"/>
+      <c r="I142" s="5"/>
+      <c r="J142" s="5"/>
+    </row>
+    <row r="143" spans="1:10" ht="42" customHeight="1">
+      <c r="A143" s="4"/>
+      <c r="B143" s="8"/>
+      <c r="C143" s="8"/>
+      <c r="D143" s="5"/>
+      <c r="E143" s="5"/>
+      <c r="F143" s="5"/>
+      <c r="G143" s="5"/>
+      <c r="H143" s="5"/>
+      <c r="I143" s="5"/>
+      <c r="J143" s="5"/>
+    </row>
+    <row r="144" spans="1:10" ht="42" customHeight="1">
+      <c r="A144" s="4"/>
+      <c r="B144" s="8"/>
+      <c r="C144" s="8"/>
+      <c r="D144" s="5"/>
+      <c r="E144" s="5"/>
+      <c r="F144" s="5"/>
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="5"/>
+    </row>
+    <row r="145" spans="1:10" ht="42" customHeight="1">
+      <c r="A145" s="4"/>
+      <c r="B145" s="8"/>
+      <c r="C145" s="8"/>
+      <c r="D145" s="5"/>
+      <c r="E145" s="5"/>
+      <c r="F145" s="5"/>
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+      <c r="I145" s="5"/>
+      <c r="J145" s="5"/>
+    </row>
+    <row r="146" spans="1:10" ht="42" customHeight="1">
+      <c r="A146" s="4"/>
+      <c r="B146" s="8"/>
+      <c r="C146" s="8"/>
+      <c r="D146" s="5"/>
+      <c r="E146" s="5"/>
+      <c r="F146" s="5"/>
+      <c r="G146" s="5"/>
+      <c r="H146" s="5"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5"/>
+    </row>
+    <row r="147" spans="1:10" ht="42" customHeight="1">
+      <c r="A147" s="4"/>
+      <c r="B147" s="8"/>
+      <c r="C147" s="8"/>
+      <c r="D147" s="5"/>
+      <c r="E147" s="5"/>
+      <c r="F147" s="5"/>
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+      <c r="I147" s="5"/>
+      <c r="J147" s="5"/>
+    </row>
+    <row r="148" spans="1:10" ht="42" customHeight="1">
+      <c r="A148" s="4"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="5"/>
+      <c r="E148" s="5"/>
+      <c r="F148" s="5"/>
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5"/>
+    </row>
+    <row r="149" spans="1:10" ht="42" customHeight="1">
+      <c r="A149" s="4"/>
+      <c r="B149" s="8"/>
+      <c r="C149" s="8"/>
+      <c r="D149" s="5"/>
+      <c r="E149" s="5"/>
+      <c r="F149" s="5"/>
+      <c r="G149" s="5"/>
+      <c r="H149" s="5"/>
+      <c r="I149" s="5"/>
+      <c r="J149" s="5"/>
+    </row>
+    <row r="150" spans="1:10" ht="42" customHeight="1">
+      <c r="A150" s="4"/>
+      <c r="B150" s="8"/>
+      <c r="C150" s="8"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="5"/>
+    </row>
+    <row r="151" spans="1:10" ht="42" customHeight="1">
+      <c r="A151" s="4"/>
+      <c r="B151" s="8"/>
+      <c r="C151" s="8"/>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5"/>
+      <c r="F151" s="5"/>
+      <c r="G151" s="5"/>
+      <c r="H151" s="5"/>
+      <c r="I151" s="5"/>
+      <c r="J151" s="5"/>
+    </row>
+    <row r="152" spans="1:10" ht="42" customHeight="1">
+      <c r="A152" s="4"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="8"/>
+      <c r="D152" s="5"/>
+      <c r="E152" s="5"/>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="5"/>
+    </row>
+    <row r="153" spans="1:10" ht="42" customHeight="1">
+      <c r="A153" s="4"/>
+      <c r="B153" s="8"/>
+      <c r="C153" s="8"/>
+      <c r="D153" s="5"/>
+      <c r="E153" s="5"/>
+      <c r="F153" s="5"/>
+      <c r="G153" s="5"/>
+      <c r="H153" s="5"/>
+      <c r="I153" s="5"/>
+      <c r="J153" s="5"/>
+    </row>
+    <row r="154" spans="1:10" ht="42" customHeight="1">
+      <c r="A154" s="4"/>
+      <c r="B154" s="8"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="5"/>
+      <c r="E154" s="5"/>
+      <c r="F154" s="5"/>
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5"/>
+    </row>
+    <row r="155" spans="1:10" ht="42" customHeight="1">
+      <c r="A155" s="4"/>
+      <c r="B155" s="8"/>
+      <c r="C155" s="8"/>
+      <c r="D155" s="5"/>
+      <c r="E155" s="5"/>
+      <c r="F155" s="5"/>
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5"/>
+      <c r="J155" s="5"/>
+    </row>
+    <row r="156" spans="1:10" ht="42" customHeight="1">
+      <c r="A156" s="4"/>
+      <c r="B156" s="7"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="5"/>
+      <c r="E156" s="5"/>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
+      <c r="I156" s="5"/>
+      <c r="J156" s="5"/>
+    </row>
+    <row r="157" spans="1:10" ht="42" customHeight="1">
+      <c r="A157" s="4"/>
+      <c r="B157" s="8"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="5"/>
+      <c r="E157" s="5"/>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
+      <c r="I157" s="5"/>
+      <c r="J157" s="5"/>
+    </row>
+    <row r="158" spans="1:10" ht="42" customHeight="1">
+      <c r="A158" s="4"/>
+      <c r="B158" s="8"/>
+      <c r="C158" s="8"/>
+      <c r="D158" s="5"/>
+      <c r="E158" s="5"/>
+      <c r="F158" s="5"/>
+      <c r="G158" s="5"/>
+      <c r="H158" s="5"/>
+      <c r="I158" s="5"/>
+      <c r="J158" s="5"/>
+    </row>
+    <row r="159" spans="1:10" ht="42" customHeight="1">
+      <c r="A159" s="4"/>
+      <c r="B159" s="8"/>
+      <c r="C159" s="8"/>
+      <c r="D159" s="5"/>
+      <c r="E159" s="5"/>
+      <c r="F159" s="5"/>
+      <c r="G159" s="5"/>
+      <c r="H159" s="5"/>
+      <c r="I159" s="5"/>
+      <c r="J159" s="5"/>
+    </row>
+    <row r="160" spans="1:10" ht="42" customHeight="1">
+      <c r="A160" s="4"/>
+      <c r="B160" s="8"/>
+      <c r="C160" s="8"/>
+      <c r="D160" s="5"/>
+      <c r="E160" s="5"/>
+      <c r="F160" s="5"/>
+      <c r="G160" s="5"/>
+      <c r="H160" s="5"/>
+      <c r="I160" s="5"/>
+      <c r="J160" s="5"/>
+    </row>
+    <row r="161" spans="1:10" ht="42" customHeight="1">
+      <c r="A161" s="4"/>
+      <c r="B161" s="8"/>
+      <c r="C161" s="8"/>
+      <c r="D161" s="5"/>
+      <c r="E161" s="5"/>
+      <c r="F161" s="5"/>
+      <c r="G161" s="5"/>
+      <c r="H161" s="5"/>
+      <c r="I161" s="5"/>
+      <c r="J161" s="5"/>
+    </row>
+    <row r="162" spans="1:10" ht="42" customHeight="1">
+      <c r="A162" s="4"/>
+      <c r="B162" s="8"/>
+      <c r="C162" s="8"/>
+      <c r="D162" s="5"/>
+      <c r="E162" s="5"/>
+      <c r="F162" s="5"/>
+      <c r="G162" s="5"/>
+      <c r="H162" s="5"/>
+      <c r="I162" s="5"/>
+      <c r="J162" s="5"/>
+    </row>
+    <row r="163" spans="1:10" ht="42" customHeight="1">
+      <c r="A163" s="4"/>
+      <c r="B163" s="8"/>
+      <c r="C163" s="8"/>
+      <c r="D163" s="5"/>
+      <c r="E163" s="5"/>
+      <c r="F163" s="5"/>
+      <c r="G163" s="5"/>
+      <c r="H163" s="5"/>
+      <c r="I163" s="5"/>
+      <c r="J163" s="5"/>
+    </row>
+    <row r="164" spans="1:10" ht="42" customHeight="1">
+      <c r="A164" s="4"/>
+      <c r="B164" s="8"/>
+      <c r="C164" s="8"/>
+      <c r="D164" s="5"/>
+      <c r="E164" s="5"/>
+      <c r="F164" s="5"/>
+      <c r="G164" s="5"/>
+      <c r="H164" s="5"/>
+      <c r="I164" s="5"/>
+      <c r="J164" s="5"/>
+    </row>
+    <row r="165" spans="1:10" ht="42" customHeight="1">
+      <c r="A165" s="4"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="8"/>
+      <c r="D165" s="5"/>
+      <c r="E165" s="5"/>
+      <c r="F165" s="5"/>
+      <c r="G165" s="5"/>
+      <c r="H165" s="5"/>
+      <c r="I165" s="5"/>
+      <c r="J165" s="5"/>
+    </row>
+    <row r="166" spans="1:10" ht="42" customHeight="1">
+      <c r="A166" s="4"/>
+      <c r="B166" s="8"/>
+      <c r="C166" s="8"/>
+      <c r="D166" s="5"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5"/>
+      <c r="G166" s="5"/>
+      <c r="H166" s="5"/>
+      <c r="I166" s="5"/>
+      <c r="J166" s="5"/>
+    </row>
+    <row r="167" spans="1:10" ht="42" customHeight="1">
+      <c r="A167" s="4"/>
+      <c r="B167" s="8"/>
+      <c r="C167" s="8"/>
+      <c r="D167" s="5"/>
+      <c r="E167" s="5"/>
+      <c r="F167" s="5"/>
+      <c r="G167" s="5"/>
+      <c r="H167" s="5"/>
+      <c r="I167" s="5"/>
+      <c r="J167" s="5"/>
+    </row>
+    <row r="168" spans="1:10" ht="42" customHeight="1">
+      <c r="A168" s="4"/>
+      <c r="B168" s="8"/>
+      <c r="C168" s="8"/>
+      <c r="D168" s="5"/>
+      <c r="E168" s="5"/>
+      <c r="F168" s="5"/>
+      <c r="G168" s="5"/>
+      <c r="H168" s="5"/>
+      <c r="I168" s="5"/>
+      <c r="J168" s="5"/>
+    </row>
+    <row r="169" spans="1:10" ht="42" customHeight="1">
+      <c r="A169" s="4"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="8"/>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5"/>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5"/>
+      <c r="J169" s="5"/>
+    </row>
+    <row r="170" spans="1:10" ht="42" customHeight="1">
+      <c r="A170" s="4"/>
+      <c r="B170" s="8"/>
+      <c r="C170" s="8"/>
+      <c r="D170" s="5"/>
+      <c r="E170" s="5"/>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5"/>
+      <c r="H170" s="5"/>
+      <c r="I170" s="5"/>
+      <c r="J170" s="5"/>
+    </row>
+    <row r="171" spans="1:10" ht="42" customHeight="1">
+      <c r="A171" s="4"/>
+      <c r="B171" s="8"/>
+      <c r="C171" s="8"/>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5"/>
+      <c r="G171" s="5"/>
+      <c r="H171" s="5"/>
+      <c r="I171" s="5"/>
+      <c r="J171" s="5"/>
+    </row>
+    <row r="172" spans="1:10" ht="42" customHeight="1">
+      <c r="A172" s="4"/>
+      <c r="B172" s="8"/>
+      <c r="C172" s="8"/>
+      <c r="D172" s="5"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="5"/>
+      <c r="G172" s="5"/>
+      <c r="H172" s="5"/>
+      <c r="I172" s="5"/>
+      <c r="J172" s="5"/>
+    </row>
+    <row r="173" spans="1:10" ht="42" customHeight="1">
+      <c r="A173" s="4"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="8"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="5"/>
+      <c r="G173" s="5"/>
+      <c r="H173" s="5"/>
+      <c r="I173" s="5"/>
+      <c r="J173" s="5"/>
+    </row>
+    <row r="174" spans="1:10" ht="42" customHeight="1">
+      <c r="A174" s="4"/>
+      <c r="B174" s="8"/>
+      <c r="C174" s="8"/>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5"/>
+      <c r="H174" s="5"/>
+      <c r="I174" s="5"/>
+      <c r="J174" s="5"/>
+    </row>
+    <row r="175" spans="1:10" ht="42" customHeight="1">
+      <c r="A175" s="4"/>
+      <c r="B175" s="8"/>
+      <c r="C175" s="8"/>
+      <c r="D175" s="5"/>
+      <c r="E175" s="5"/>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5"/>
+      <c r="H175" s="5"/>
+      <c r="I175" s="5"/>
+      <c r="J175" s="5"/>
+    </row>
+    <row r="176" spans="1:10" ht="42" customHeight="1">
+      <c r="A176" s="4"/>
+      <c r="B176" s="8"/>
+      <c r="C176" s="8"/>
+      <c r="D176" s="5"/>
+      <c r="E176" s="5"/>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5"/>
+      <c r="J176" s="5"/>
+    </row>
+    <row r="177" spans="1:10" ht="42" customHeight="1">
+      <c r="A177" s="4"/>
+      <c r="B177" s="7"/>
+      <c r="C177" s="8"/>
+      <c r="D177" s="5"/>
+      <c r="E177" s="5"/>
+      <c r="F177" s="5"/>
+      <c r="G177" s="5"/>
+      <c r="H177" s="5"/>
+      <c r="I177" s="5"/>
+      <c r="J177" s="5"/>
+    </row>
+    <row r="178" spans="1:10" ht="42" customHeight="1">
+      <c r="A178" s="4"/>
+      <c r="B178" s="8"/>
+      <c r="C178" s="8"/>
+      <c r="D178" s="5"/>
+      <c r="E178" s="5"/>
+      <c r="F178" s="5"/>
+      <c r="G178" s="5"/>
+      <c r="H178" s="5"/>
+      <c r="I178" s="5"/>
+      <c r="J178" s="5"/>
+    </row>
+    <row r="179" spans="1:10" ht="42" customHeight="1">
+      <c r="A179" s="4"/>
+      <c r="B179" s="8"/>
+      <c r="C179" s="8"/>
+      <c r="D179" s="5"/>
+      <c r="E179" s="5"/>
+      <c r="F179" s="5"/>
+      <c r="G179" s="5"/>
+      <c r="H179" s="5"/>
+      <c r="I179" s="5"/>
+      <c r="J179" s="5"/>
+    </row>
+    <row r="180" spans="1:10" ht="42" customHeight="1">
+      <c r="A180" s="4"/>
+      <c r="B180" s="8"/>
+      <c r="C180" s="8"/>
+      <c r="D180" s="5"/>
+      <c r="E180" s="5"/>
+      <c r="F180" s="5"/>
+      <c r="G180" s="5"/>
+      <c r="H180" s="5"/>
+      <c r="I180" s="5"/>
+      <c r="J180" s="5"/>
+    </row>
+    <row r="181" spans="1:10" ht="42" customHeight="1">
+      <c r="A181" s="4"/>
+      <c r="B181" s="7"/>
+      <c r="C181" s="8"/>
+      <c r="D181" s="5"/>
+      <c r="E181" s="5"/>
+      <c r="F181" s="5"/>
+      <c r="G181" s="5"/>
+      <c r="H181" s="5"/>
+      <c r="I181" s="5"/>
+      <c r="J181" s="5"/>
+    </row>
+    <row r="182" spans="1:10" ht="42" customHeight="1">
+      <c r="A182" s="4"/>
+      <c r="B182" s="8"/>
+      <c r="C182" s="8"/>
+      <c r="D182" s="5"/>
+      <c r="E182" s="5"/>
+      <c r="F182" s="5"/>
+      <c r="G182" s="5"/>
+      <c r="H182" s="5"/>
+      <c r="I182" s="5"/>
+      <c r="J182" s="5"/>
+    </row>
+    <row r="183" spans="1:10" ht="42" customHeight="1">
+      <c r="A183" s="4"/>
+      <c r="B183" s="8"/>
+      <c r="C183" s="8"/>
+      <c r="D183" s="5"/>
+      <c r="E183" s="5"/>
+      <c r="F183" s="5"/>
+      <c r="G183" s="5"/>
+      <c r="H183" s="5"/>
+      <c r="I183" s="5"/>
+      <c r="J183" s="5"/>
+    </row>
+    <row r="184" spans="1:10" ht="42" customHeight="1">
+      <c r="A184" s="4"/>
+      <c r="B184" s="8"/>
+      <c r="C184" s="8"/>
+      <c r="D184" s="5"/>
+      <c r="E184" s="5"/>
+      <c r="F184" s="5"/>
+      <c r="G184" s="5"/>
+      <c r="H184" s="5"/>
+      <c r="I184" s="5"/>
+      <c r="J184" s="5"/>
+    </row>
+    <row r="185" spans="1:10" ht="42" customHeight="1">
+      <c r="A185" s="4"/>
+      <c r="B185" s="7"/>
+      <c r="C185" s="8"/>
+      <c r="D185" s="5"/>
+      <c r="E185" s="5"/>
+      <c r="F185" s="5"/>
+      <c r="G185" s="5"/>
+      <c r="H185" s="5"/>
+      <c r="I185" s="5"/>
+      <c r="J185" s="5"/>
+    </row>
+    <row r="186" spans="1:10" ht="42" customHeight="1">
+      <c r="A186" s="4"/>
+      <c r="B186" s="7"/>
+      <c r="C186" s="8"/>
+      <c r="D186" s="5"/>
+      <c r="E186" s="5"/>
+      <c r="F186" s="5"/>
+      <c r="G186" s="5"/>
+      <c r="H186" s="5"/>
+      <c r="I186" s="5"/>
+      <c r="J186" s="5"/>
+    </row>
+    <row r="187" spans="1:10" ht="42" customHeight="1">
+      <c r="A187" s="4"/>
+      <c r="B187" s="8"/>
+      <c r="C187" s="8"/>
+      <c r="D187" s="5"/>
+      <c r="E187" s="5"/>
+      <c r="F187" s="5"/>
+      <c r="G187" s="5"/>
+      <c r="H187" s="5"/>
+      <c r="I187" s="5"/>
+      <c r="J187" s="5"/>
+    </row>
+    <row r="188" spans="1:10" ht="42" customHeight="1">
+      <c r="A188" s="4"/>
+      <c r="B188" s="8"/>
+      <c r="C188" s="8"/>
+      <c r="D188" s="5"/>
+      <c r="E188" s="5"/>
+      <c r="F188" s="5"/>
+      <c r="G188" s="5"/>
+      <c r="H188" s="5"/>
+      <c r="I188" s="5"/>
+      <c r="J188" s="5"/>
+    </row>
+    <row r="189" spans="1:10" ht="42" customHeight="1">
+      <c r="A189" s="4"/>
+      <c r="B189" s="7"/>
+      <c r="C189" s="8"/>
+      <c r="D189" s="5"/>
+      <c r="E189" s="5"/>
+      <c r="F189" s="5"/>
+      <c r="G189" s="5"/>
+      <c r="H189" s="5"/>
+      <c r="I189" s="5"/>
+      <c r="J189" s="5"/>
+    </row>
+    <row r="190" spans="1:10" ht="42" customHeight="1">
+      <c r="A190" s="4"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="8"/>
+      <c r="D190" s="5"/>
+      <c r="E190" s="5"/>
+      <c r="F190" s="5"/>
+      <c r="G190" s="5"/>
+      <c r="H190" s="5"/>
+      <c r="I190" s="5"/>
+      <c r="J190" s="5"/>
+    </row>
+    <row r="191" spans="1:10" ht="42" customHeight="1">
+      <c r="A191" s="4"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="8"/>
+      <c r="D191" s="5"/>
+      <c r="E191" s="5"/>
+      <c r="F191" s="5"/>
+      <c r="G191" s="5"/>
+      <c r="H191" s="5"/>
+      <c r="I191" s="5"/>
+      <c r="J191" s="5"/>
+    </row>
+    <row r="192" spans="1:10" ht="42" customHeight="1">
+      <c r="A192" s="4"/>
+      <c r="B192" s="8"/>
+      <c r="C192" s="8"/>
+      <c r="D192" s="5"/>
+      <c r="E192" s="5"/>
+      <c r="F192" s="5"/>
+      <c r="G192" s="5"/>
+      <c r="H192" s="5"/>
+      <c r="I192" s="5"/>
+      <c r="J192" s="5"/>
+    </row>
+    <row r="193" spans="1:10" ht="42" customHeight="1">
+      <c r="A193" s="4"/>
+      <c r="B193" s="8"/>
+      <c r="C193" s="8"/>
+      <c r="D193" s="5"/>
+      <c r="E193" s="5"/>
+      <c r="F193" s="5"/>
+      <c r="G193" s="5"/>
+      <c r="H193" s="5"/>
+      <c r="I193" s="5"/>
+      <c r="J193" s="5"/>
+    </row>
+    <row r="194" spans="1:10" ht="42" customHeight="1">
+      <c r="A194" s="4"/>
+      <c r="B194" s="8"/>
+      <c r="C194" s="8"/>
+      <c r="D194" s="5"/>
+      <c r="E194" s="5"/>
+      <c r="F194" s="5"/>
+      <c r="G194" s="5"/>
+      <c r="H194" s="5"/>
+      <c r="I194" s="5"/>
+      <c r="J194" s="5"/>
+    </row>
+    <row r="195" spans="1:10" ht="42" customHeight="1">
+      <c r="A195" s="4"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="8"/>
+      <c r="D195" s="5"/>
+      <c r="E195" s="5"/>
+      <c r="F195" s="5"/>
+      <c r="G195" s="5"/>
+      <c r="H195" s="5"/>
+      <c r="I195" s="5"/>
+      <c r="J195" s="5"/>
+    </row>
+    <row r="196" spans="1:10" ht="42" customHeight="1">
+      <c r="A196" s="4"/>
+      <c r="B196" s="8"/>
+      <c r="C196" s="8"/>
+      <c r="D196" s="5"/>
+      <c r="E196" s="5"/>
+      <c r="F196" s="5"/>
+      <c r="G196" s="5"/>
+      <c r="H196" s="5"/>
+      <c r="I196" s="5"/>
+      <c r="J196" s="5"/>
+    </row>
+    <row r="197" spans="1:10" ht="42" customHeight="1">
+      <c r="A197" s="4"/>
+      <c r="B197" s="8"/>
+      <c r="C197" s="8"/>
+      <c r="D197" s="5"/>
+      <c r="E197" s="5"/>
+      <c r="F197" s="5"/>
+      <c r="G197" s="5"/>
+      <c r="H197" s="5"/>
+      <c r="I197" s="5"/>
+      <c r="J197" s="5"/>
+    </row>
+    <row r="198" spans="1:10" ht="42" customHeight="1">
+      <c r="A198" s="4"/>
+      <c r="B198" s="8"/>
+      <c r="C198" s="8"/>
+      <c r="D198" s="5"/>
+      <c r="E198" s="5"/>
+      <c r="F198" s="5"/>
+      <c r="G198" s="5"/>
+      <c r="H198" s="5"/>
+      <c r="I198" s="5"/>
+      <c r="J198" s="5"/>
+    </row>
+    <row r="199" spans="1:10" ht="42" customHeight="1">
+      <c r="A199" s="4"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="8"/>
+      <c r="D199" s="5"/>
+      <c r="E199" s="5"/>
+      <c r="F199" s="5"/>
+      <c r="G199" s="5"/>
+      <c r="H199" s="5"/>
+      <c r="I199" s="5"/>
+      <c r="J199" s="5"/>
+    </row>
+    <row r="200" spans="1:10" ht="42" customHeight="1">
+      <c r="A200" s="4"/>
+      <c r="B200" s="8"/>
+      <c r="C200" s="8"/>
+      <c r="D200" s="5"/>
+      <c r="E200" s="5"/>
+      <c r="F200" s="5"/>
+      <c r="G200" s="5"/>
+      <c r="H200" s="5"/>
+      <c r="I200" s="5"/>
+      <c r="J200" s="5"/>
+    </row>
+    <row r="201" spans="1:10" ht="42" customHeight="1">
+      <c r="A201" s="4"/>
+      <c r="B201" s="7"/>
+      <c r="C201" s="8"/>
+      <c r="D201" s="5"/>
+      <c r="E201" s="5"/>
+      <c r="F201" s="5"/>
+      <c r="G201" s="5"/>
+      <c r="H201" s="5"/>
+      <c r="I201" s="5"/>
+      <c r="J201" s="5"/>
+    </row>
+    <row r="202" spans="1:10" ht="42" customHeight="1">
+      <c r="A202" s="4"/>
+      <c r="B202" s="8"/>
+      <c r="C202" s="8"/>
+      <c r="D202" s="5"/>
+      <c r="E202" s="5"/>
+      <c r="F202" s="5"/>
+      <c r="G202" s="5"/>
+      <c r="H202" s="5"/>
+      <c r="I202" s="5"/>
+      <c r="J202" s="5"/>
+    </row>
+    <row r="203" spans="1:10" ht="42" customHeight="1">
+      <c r="A203" s="4"/>
+      <c r="B203" s="8"/>
+      <c r="C203" s="8"/>
+      <c r="D203" s="5"/>
+      <c r="E203" s="5"/>
+      <c r="F203" s="5"/>
+      <c r="G203" s="5"/>
+      <c r="H203" s="5"/>
+      <c r="I203" s="5"/>
+      <c r="J203" s="5"/>
+    </row>
+    <row r="204" spans="1:10" ht="42" customHeight="1">
+      <c r="A204" s="4"/>
+      <c r="B204" s="8"/>
+      <c r="C204" s="8"/>
+      <c r="D204" s="5"/>
+      <c r="E204" s="5"/>
+      <c r="F204" s="5"/>
+      <c r="G204" s="5"/>
+      <c r="H204" s="5"/>
+      <c r="I204" s="5"/>
+      <c r="J204" s="5"/>
+    </row>
+    <row r="205" spans="1:10" ht="42" customHeight="1">
+      <c r="A205" s="4"/>
+      <c r="B205" s="7"/>
+      <c r="C205" s="8"/>
+      <c r="D205" s="5"/>
+      <c r="E205" s="5"/>
+      <c r="F205" s="5"/>
+      <c r="G205" s="5"/>
+      <c r="H205" s="5"/>
+      <c r="I205" s="5"/>
+      <c r="J205" s="5"/>
+    </row>
+    <row r="206" spans="1:10" ht="42" customHeight="1">
+      <c r="A206" s="4"/>
+      <c r="B206" s="8"/>
+      <c r="C206" s="8"/>
+      <c r="D206" s="5"/>
+      <c r="E206" s="5"/>
+      <c r="F206" s="5"/>
+      <c r="G206" s="5"/>
+      <c r="H206" s="5"/>
+      <c r="I206" s="5"/>
+      <c r="J206" s="5"/>
+    </row>
+    <row r="207" spans="1:10" ht="42" customHeight="1">
+      <c r="A207" s="4"/>
+      <c r="B207" s="8"/>
+      <c r="C207" s="8"/>
+      <c r="D207" s="5"/>
+      <c r="E207" s="5"/>
+      <c r="F207" s="5"/>
+      <c r="G207" s="5"/>
+      <c r="H207" s="5"/>
+      <c r="I207" s="5"/>
+      <c r="J207" s="5"/>
+    </row>
+    <row r="208" spans="1:10" ht="42" customHeight="1">
+      <c r="A208" s="4"/>
+      <c r="B208" s="8"/>
+      <c r="C208" s="8"/>
+      <c r="D208" s="5"/>
+      <c r="E208" s="5"/>
+      <c r="F208" s="5"/>
+      <c r="G208" s="5"/>
+      <c r="H208" s="5"/>
+      <c r="I208" s="5"/>
+      <c r="J208" s="5"/>
+    </row>
+    <row r="209" spans="1:10" ht="42" customHeight="1">
+      <c r="A209" s="4"/>
+      <c r="B209" s="7"/>
+      <c r="C209" s="8"/>
+      <c r="D209" s="5"/>
+      <c r="E209" s="5"/>
+      <c r="F209" s="5"/>
+      <c r="G209" s="5"/>
+      <c r="H209" s="5"/>
+      <c r="I209" s="5"/>
+      <c r="J209" s="5"/>
+    </row>
+    <row r="210" spans="1:10" ht="42" customHeight="1">
+      <c r="A210" s="4"/>
+      <c r="B210" s="8"/>
+      <c r="C210" s="8"/>
+      <c r="D210" s="5"/>
+      <c r="E210" s="5"/>
+      <c r="F210" s="5"/>
+      <c r="G210" s="5"/>
+      <c r="H210" s="5"/>
+      <c r="I210" s="5"/>
+      <c r="J210" s="5"/>
+    </row>
+    <row r="211" spans="1:10" ht="42" customHeight="1">
+      <c r="A211" s="4"/>
+      <c r="B211" s="8"/>
+      <c r="C211" s="8"/>
+      <c r="D211" s="5"/>
+      <c r="E211" s="5"/>
+      <c r="F211" s="5"/>
+      <c r="G211" s="5"/>
+      <c r="H211" s="5"/>
+      <c r="I211" s="5"/>
+      <c r="J211" s="5"/>
+    </row>
+    <row r="212" spans="1:10" ht="42" customHeight="1">
+      <c r="A212" s="4"/>
+      <c r="B212" s="8"/>
+      <c r="C212" s="8"/>
+      <c r="D212" s="5"/>
+      <c r="E212" s="5"/>
+      <c r="F212" s="5"/>
+      <c r="G212" s="5"/>
+      <c r="H212" s="5"/>
+      <c r="I212" s="5"/>
+      <c r="J212" s="5"/>
+    </row>
+    <row r="213" spans="1:10" ht="42" customHeight="1">
+      <c r="A213" s="4"/>
+      <c r="B213" s="8"/>
+      <c r="C213" s="8"/>
+      <c r="D213" s="5"/>
+      <c r="E213" s="5"/>
+      <c r="F213" s="5"/>
+      <c r="G213" s="5"/>
+      <c r="H213" s="5"/>
+      <c r="I213" s="5"/>
+      <c r="J213" s="5"/>
+    </row>
+    <row r="214" spans="1:10" ht="42" customHeight="1">
+      <c r="A214" s="4"/>
+      <c r="B214" s="8"/>
+      <c r="C214" s="8"/>
+      <c r="D214" s="5"/>
+      <c r="E214" s="5"/>
+      <c r="F214" s="5"/>
+      <c r="G214" s="5"/>
+      <c r="H214" s="5"/>
+      <c r="I214" s="5"/>
+      <c r="J214" s="5"/>
+    </row>
+    <row r="215" spans="1:10" ht="42" customHeight="1">
+      <c r="A215" s="4"/>
+      <c r="B215" s="8"/>
+      <c r="C215" s="8"/>
+      <c r="D215" s="10"/>
+      <c r="E215" s="5"/>
+      <c r="F215" s="5"/>
+      <c r="G215" s="5"/>
+      <c r="H215" s="5"/>
+      <c r="I215" s="5"/>
+      <c r="J215" s="5"/>
+    </row>
+    <row r="216" spans="1:10" ht="42" customHeight="1">
+      <c r="A216" s="4"/>
+      <c r="B216" s="8"/>
+      <c r="C216" s="8"/>
+      <c r="D216" s="10"/>
+      <c r="E216" s="5"/>
+      <c r="F216" s="5"/>
+      <c r="G216" s="5"/>
+      <c r="H216" s="5"/>
+      <c r="I216" s="5"/>
+      <c r="J216" s="5"/>
+    </row>
+    <row r="217" spans="1:10" ht="42" customHeight="1">
+      <c r="A217" s="4"/>
+      <c r="B217" s="8"/>
+      <c r="C217" s="8"/>
+      <c r="D217" s="10"/>
+      <c r="E217" s="5"/>
+      <c r="F217" s="5"/>
+      <c r="G217" s="5"/>
+      <c r="H217" s="5"/>
+      <c r="I217" s="5"/>
+      <c r="J217" s="5"/>
+    </row>
+    <row r="218" spans="1:10" ht="42" customHeight="1">
+      <c r="A218" s="4"/>
+      <c r="B218" s="8"/>
+      <c r="C218" s="8"/>
+      <c r="D218" s="10"/>
+      <c r="E218" s="5"/>
+      <c r="F218" s="5"/>
+      <c r="G218" s="5"/>
+      <c r="H218" s="5"/>
+      <c r="I218" s="5"/>
+      <c r="J218" s="5"/>
+    </row>
+    <row r="219" spans="1:10" ht="42" customHeight="1">
+      <c r="A219" s="4"/>
+      <c r="B219" s="8"/>
+      <c r="C219" s="8"/>
+      <c r="D219" s="10"/>
+      <c r="E219" s="5"/>
+      <c r="F219" s="5"/>
+      <c r="G219" s="5"/>
+      <c r="H219" s="5"/>
+      <c r="I219" s="5"/>
+      <c r="J219" s="5"/>
+    </row>
+    <row r="220" spans="1:10" ht="42" customHeight="1">
+      <c r="A220" s="4"/>
+      <c r="B220" s="8"/>
+      <c r="C220" s="8"/>
+      <c r="D220" s="5"/>
+      <c r="E220" s="5"/>
+      <c r="F220" s="5"/>
+      <c r="G220" s="5"/>
+      <c r="H220" s="5"/>
+      <c r="I220" s="5"/>
+      <c r="J220" s="5"/>
+    </row>
+    <row r="221" spans="1:10" ht="42" customHeight="1">
+      <c r="A221" s="4"/>
+      <c r="B221" s="8"/>
+      <c r="C221" s="8"/>
+      <c r="D221" s="5"/>
+      <c r="E221" s="5"/>
+      <c r="F221" s="5"/>
+      <c r="G221" s="5"/>
+      <c r="H221" s="5"/>
+      <c r="I221" s="5"/>
+      <c r="J221" s="5"/>
+    </row>
+    <row r="222" spans="1:10" ht="42" customHeight="1">
+      <c r="A222" s="4"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="8"/>
+      <c r="D222" s="5"/>
+      <c r="E222" s="5"/>
+      <c r="F222" s="5"/>
+      <c r="G222" s="5"/>
+      <c r="H222" s="5"/>
+      <c r="I222" s="5"/>
+      <c r="J222" s="5"/>
+    </row>
+    <row r="223" spans="1:10" ht="42" customHeight="1">
+      <c r="A223" s="4"/>
+      <c r="B223" s="8"/>
+      <c r="C223" s="8"/>
+      <c r="D223" s="5"/>
+      <c r="E223" s="5"/>
+      <c r="F223" s="5"/>
+      <c r="G223" s="5"/>
+      <c r="H223" s="5"/>
+      <c r="I223" s="5"/>
+      <c r="J223" s="5"/>
+    </row>
+    <row r="224" spans="1:10" ht="42" customHeight="1">
+      <c r="A224" s="4"/>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8"/>
+      <c r="D224" s="5"/>
+      <c r="E224" s="5"/>
+      <c r="F224" s="5"/>
+      <c r="G224" s="5"/>
+      <c r="H224" s="5"/>
+      <c r="I224" s="5"/>
+      <c r="J224" s="5"/>
+    </row>
+    <row r="225" spans="1:10" ht="42" customHeight="1">
+      <c r="A225" s="4"/>
+      <c r="B225" s="8"/>
+      <c r="C225" s="8"/>
+      <c r="D225" s="5"/>
+      <c r="E225" s="5"/>
+      <c r="F225" s="5"/>
+      <c r="G225" s="5"/>
+      <c r="H225" s="5"/>
+      <c r="I225" s="5"/>
+      <c r="J225" s="5"/>
+    </row>
+    <row r="226" spans="1:10" ht="42" customHeight="1">
+      <c r="A226" s="4"/>
+      <c r="B226" s="7"/>
+      <c r="C226" s="8"/>
+      <c r="D226" s="5"/>
+      <c r="E226" s="5"/>
+      <c r="F226" s="5"/>
+      <c r="G226" s="5"/>
+      <c r="H226" s="5"/>
+      <c r="I226" s="5"/>
+      <c r="J226" s="5"/>
+    </row>
+    <row r="227" spans="1:10" ht="42" customHeight="1">
+      <c r="A227" s="4"/>
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="5"/>
+      <c r="E227" s="5"/>
+      <c r="F227" s="5"/>
+      <c r="G227" s="5"/>
+      <c r="H227" s="5"/>
+      <c r="I227" s="5"/>
+      <c r="J227" s="5"/>
+    </row>
+    <row r="228" spans="1:10" ht="42" customHeight="1">
+      <c r="A228" s="4"/>
+      <c r="B228" s="8"/>
+      <c r="C228" s="8"/>
+      <c r="D228" s="5"/>
+      <c r="E228" s="5"/>
+      <c r="F228" s="5"/>
+      <c r="G228" s="5"/>
+      <c r="H228" s="5"/>
+      <c r="I228" s="5"/>
+      <c r="J228" s="5"/>
+    </row>
+    <row r="229" spans="1:10" ht="42" customHeight="1">
+      <c r="A229" s="4"/>
+      <c r="B229" s="8"/>
+      <c r="C229" s="8"/>
+      <c r="D229" s="5"/>
+      <c r="E229" s="5"/>
+      <c r="F229" s="5"/>
+      <c r="G229" s="5"/>
+      <c r="H229" s="5"/>
+      <c r="I229" s="5"/>
+      <c r="J229" s="5"/>
+    </row>
+    <row r="230" spans="1:10" ht="42" customHeight="1">
+      <c r="A230" s="4"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="8"/>
+      <c r="D230" s="5"/>
+      <c r="E230" s="5"/>
+      <c r="F230" s="5"/>
+      <c r="G230" s="5"/>
+      <c r="H230" s="5"/>
+      <c r="I230" s="5"/>
+      <c r="J230" s="5"/>
+    </row>
+    <row r="231" spans="1:10" ht="42" customHeight="1">
+      <c r="A231" s="4"/>
+      <c r="B231" s="8"/>
+      <c r="C231" s="8"/>
+      <c r="D231" s="5"/>
+      <c r="E231" s="5"/>
+      <c r="F231" s="5"/>
+      <c r="G231" s="5"/>
+      <c r="H231" s="5"/>
+      <c r="I231" s="5"/>
+      <c r="J231" s="5"/>
+    </row>
+    <row r="232" spans="1:10" ht="42" customHeight="1">
+      <c r="A232" s="4"/>
+      <c r="B232" s="8"/>
+      <c r="C232" s="8"/>
+      <c r="D232" s="5"/>
+      <c r="E232" s="5"/>
+      <c r="F232" s="5"/>
+      <c r="G232" s="5"/>
+      <c r="H232" s="5"/>
+      <c r="I232" s="5"/>
+      <c r="J232" s="5"/>
+    </row>
+    <row r="233" spans="1:10" ht="42" customHeight="1">
+      <c r="A233" s="4"/>
+      <c r="B233" s="8"/>
+      <c r="C233" s="8"/>
+      <c r="D233" s="5"/>
+      <c r="E233" s="5"/>
+      <c r="F233" s="5"/>
+      <c r="G233" s="5"/>
+      <c r="H233" s="5"/>
+      <c r="I233" s="5"/>
+      <c r="J233" s="5"/>
+    </row>
+    <row r="234" spans="1:10" ht="42" customHeight="1">
+      <c r="A234" s="4"/>
+      <c r="B234" s="7"/>
+      <c r="C234" s="8"/>
+      <c r="D234" s="5"/>
+      <c r="E234" s="5"/>
+      <c r="F234" s="5"/>
+      <c r="G234" s="5"/>
+      <c r="H234" s="5"/>
+      <c r="I234" s="5"/>
+      <c r="J234" s="5"/>
+    </row>
+    <row r="235" spans="1:10" ht="42" customHeight="1">
+      <c r="A235" s="4"/>
+      <c r="B235" s="7"/>
+      <c r="C235" s="8"/>
+      <c r="D235" s="5"/>
+      <c r="E235" s="5"/>
+      <c r="F235" s="5"/>
+      <c r="G235" s="5"/>
+      <c r="H235" s="5"/>
+      <c r="I235" s="5"/>
+      <c r="J235" s="5"/>
+    </row>
+    <row r="236" spans="1:10" ht="42" customHeight="1">
+      <c r="A236" s="4"/>
+      <c r="B236" s="8"/>
+      <c r="C236" s="8"/>
+      <c r="D236" s="5"/>
+      <c r="E236" s="5"/>
+      <c r="F236" s="5"/>
+      <c r="G236" s="5"/>
+      <c r="H236" s="5"/>
+      <c r="I236" s="5"/>
+      <c r="J236" s="5"/>
+    </row>
+    <row r="237" spans="1:10" ht="42" customHeight="1">
+      <c r="A237" s="4"/>
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
+      <c r="D237" s="5"/>
+      <c r="E237" s="5"/>
+      <c r="F237" s="5"/>
+      <c r="G237" s="5"/>
+      <c r="H237" s="5"/>
+      <c r="I237" s="5"/>
+      <c r="J237" s="5"/>
+    </row>
+    <row r="238" spans="1:10" ht="42" customHeight="1">
+      <c r="A238" s="4"/>
+      <c r="B238" s="8"/>
+      <c r="C238" s="8"/>
+      <c r="D238" s="5"/>
+      <c r="E238" s="5"/>
+      <c r="F238" s="5"/>
+      <c r="G238" s="5"/>
+      <c r="H238" s="5"/>
+      <c r="I238" s="5"/>
+      <c r="J238" s="5"/>
+    </row>
+    <row r="239" spans="1:10" ht="42" customHeight="1">
+      <c r="A239" s="4"/>
+      <c r="B239" s="7"/>
+      <c r="C239" s="8"/>
+      <c r="D239" s="5"/>
+      <c r="E239" s="5"/>
+      <c r="F239" s="5"/>
+      <c r="G239" s="5"/>
+      <c r="H239" s="5"/>
+      <c r="I239" s="5"/>
+      <c r="J239" s="5"/>
+    </row>
+    <row r="240" spans="1:10" ht="42" customHeight="1">
+      <c r="A240" s="4"/>
+      <c r="B240" s="8"/>
+      <c r="C240" s="8"/>
+      <c r="D240" s="5"/>
+      <c r="E240" s="5"/>
+      <c r="F240" s="5"/>
+      <c r="G240" s="5"/>
+      <c r="H240" s="5"/>
+      <c r="I240" s="5"/>
+      <c r="J240" s="5"/>
+    </row>
+    <row r="241" spans="1:10" ht="42" customHeight="1">
+      <c r="A241" s="4"/>
+      <c r="B241" s="8"/>
+      <c r="C241" s="8"/>
+      <c r="D241" s="5"/>
+      <c r="E241" s="5"/>
+      <c r="F241" s="5"/>
+      <c r="G241" s="5"/>
+      <c r="H241" s="5"/>
+      <c r="I241" s="5"/>
+      <c r="J241" s="5"/>
+    </row>
+    <row r="242" spans="1:10" ht="42" customHeight="1">
+      <c r="A242" s="4"/>
+      <c r="B242" s="8"/>
+      <c r="C242" s="8"/>
+      <c r="D242" s="5"/>
+      <c r="E242" s="5"/>
+      <c r="F242" s="5"/>
+      <c r="G242" s="5"/>
+      <c r="H242" s="5"/>
+      <c r="I242" s="5"/>
+      <c r="J242" s="5"/>
+    </row>
+    <row r="243" spans="1:10" ht="42" customHeight="1">
+      <c r="A243" s="4"/>
+      <c r="B243" s="7"/>
+      <c r="C243" s="8"/>
+      <c r="D243" s="5"/>
+      <c r="E243" s="5"/>
+      <c r="F243" s="5"/>
+      <c r="G243" s="5"/>
+      <c r="H243" s="5"/>
+      <c r="I243" s="5"/>
+      <c r="J243" s="5"/>
+    </row>
+    <row r="244" spans="1:10" ht="42" customHeight="1">
+      <c r="A244" s="4"/>
+      <c r="B244" s="8"/>
+      <c r="C244" s="8"/>
+      <c r="D244" s="5"/>
+      <c r="E244" s="5"/>
+      <c r="F244" s="5"/>
+      <c r="G244" s="5"/>
+      <c r="H244" s="5"/>
+      <c r="I244" s="5"/>
+      <c r="J244" s="5"/>
+    </row>
+    <row r="245" spans="1:10" ht="42" customHeight="1">
+      <c r="A245" s="4"/>
+      <c r="B245" s="8"/>
+      <c r="C245" s="8"/>
+      <c r="D245" s="5"/>
+      <c r="E245" s="5"/>
+      <c r="F245" s="5"/>
+      <c r="G245" s="5"/>
+      <c r="H245" s="5"/>
+      <c r="I245" s="5"/>
+      <c r="J245" s="5"/>
+    </row>
+    <row r="246" spans="1:10" ht="42" customHeight="1">
+      <c r="A246" s="4"/>
+      <c r="B246" s="8"/>
+      <c r="C246" s="8"/>
+      <c r="D246" s="5"/>
+      <c r="E246" s="5"/>
+      <c r="F246" s="5"/>
+      <c r="G246" s="5"/>
+      <c r="H246" s="5"/>
+      <c r="I246" s="5"/>
+      <c r="J246" s="5"/>
+    </row>
+    <row r="247" spans="1:10" ht="42" customHeight="1">
+      <c r="A247" s="4"/>
+      <c r="B247" s="7"/>
+      <c r="C247" s="8"/>
+      <c r="D247" s="5"/>
+      <c r="E247" s="5"/>
+      <c r="F247" s="5"/>
+      <c r="G247" s="5"/>
+      <c r="H247" s="5"/>
+      <c r="I247" s="5"/>
+      <c r="J247" s="5"/>
+    </row>
+    <row r="248" spans="1:10" ht="42" customHeight="1">
+      <c r="A248" s="4"/>
+      <c r="B248" s="8"/>
+      <c r="C248" s="8"/>
+      <c r="D248" s="5"/>
+      <c r="E248" s="5"/>
+      <c r="F248" s="5"/>
+      <c r="G248" s="5"/>
+      <c r="H248" s="5"/>
+      <c r="I248" s="5"/>
+      <c r="J248" s="5"/>
+    </row>
+    <row r="249" spans="1:10" ht="42" customHeight="1">
+      <c r="A249" s="4"/>
+      <c r="B249" s="8"/>
+      <c r="C249" s="8"/>
+      <c r="D249" s="5"/>
+      <c r="E249" s="5"/>
+      <c r="F249" s="5"/>
+      <c r="G249" s="5"/>
+      <c r="H249" s="5"/>
+      <c r="I249" s="5"/>
+      <c r="J249" s="5"/>
+    </row>
+    <row r="250" spans="1:10" ht="42" customHeight="1">
+      <c r="A250" s="4"/>
+      <c r="B250" s="8"/>
+      <c r="C250" s="8"/>
+      <c r="D250" s="5"/>
+      <c r="E250" s="5"/>
+      <c r="F250" s="5"/>
+      <c r="G250" s="5"/>
+      <c r="H250" s="5"/>
+      <c r="I250" s="5"/>
+      <c r="J250" s="5"/>
+    </row>
+    <row r="251" spans="1:10" ht="42" customHeight="1">
+      <c r="A251" s="4"/>
+      <c r="B251" s="8"/>
+      <c r="C251" s="8"/>
+      <c r="D251" s="5"/>
+      <c r="E251" s="5"/>
+      <c r="F251" s="5"/>
+      <c r="G251" s="5"/>
+      <c r="H251" s="5"/>
+      <c r="I251" s="5"/>
+      <c r="J251" s="5"/>
+    </row>
+    <row r="252" spans="1:10" ht="42" customHeight="1">
+      <c r="A252" s="4"/>
+      <c r="B252" s="8"/>
+      <c r="C252" s="8"/>
+      <c r="D252" s="5"/>
+      <c r="E252" s="5"/>
+      <c r="F252" s="5"/>
+      <c r="G252" s="5"/>
+      <c r="H252" s="5"/>
+      <c r="I252" s="5"/>
+      <c r="J252" s="5"/>
+    </row>
+    <row r="253" spans="1:10" ht="42" customHeight="1">
+      <c r="A253" s="4"/>
+      <c r="B253" s="8"/>
+      <c r="C253" s="8"/>
+      <c r="D253" s="5"/>
+      <c r="E253" s="5"/>
+      <c r="F253" s="5"/>
+      <c r="G253" s="5"/>
+      <c r="H253" s="5"/>
+      <c r="I253" s="5"/>
+      <c r="J253" s="5"/>
+    </row>
+    <row r="254" spans="1:10" ht="42" customHeight="1">
+      <c r="A254" s="4"/>
+      <c r="B254" s="8"/>
+      <c r="C254" s="8"/>
+      <c r="D254" s="5"/>
+      <c r="E254" s="5"/>
+      <c r="F254" s="5"/>
+      <c r="G254" s="5"/>
+      <c r="H254" s="5"/>
+      <c r="I254" s="5"/>
+      <c r="J254" s="5"/>
+    </row>
+    <row r="255" spans="1:10" ht="42" customHeight="1">
+      <c r="A255" s="4"/>
+      <c r="B255" s="8"/>
+      <c r="C255" s="8"/>
+      <c r="D255" s="5"/>
+      <c r="E255" s="5"/>
+      <c r="F255" s="5"/>
+      <c r="G255" s="5"/>
+      <c r="H255" s="5"/>
+      <c r="I255" s="5"/>
+      <c r="J255" s="5"/>
+    </row>
+    <row r="256" spans="1:10" ht="42" customHeight="1">
+      <c r="A256" s="4"/>
+      <c r="B256" s="8"/>
+      <c r="C256" s="8"/>
+      <c r="D256" s="5"/>
+      <c r="E256" s="5"/>
+      <c r="F256" s="5"/>
+      <c r="G256" s="5"/>
+      <c r="H256" s="5"/>
+      <c r="I256" s="5"/>
+      <c r="J256" s="5"/>
+    </row>
+    <row r="257" spans="1:10" ht="42" customHeight="1">
+      <c r="A257" s="4"/>
+      <c r="B257" s="8"/>
+      <c r="C257" s="8"/>
+      <c r="D257" s="5"/>
+      <c r="E257" s="5"/>
+      <c r="F257" s="5"/>
+      <c r="G257" s="5"/>
+      <c r="H257" s="5"/>
+      <c r="I257" s="5"/>
+      <c r="J257" s="5"/>
+    </row>
+    <row r="258" spans="1:10" ht="42" customHeight="1">
+      <c r="A258" s="4"/>
+      <c r="B258" s="8"/>
+      <c r="C258" s="8"/>
+      <c r="D258" s="5"/>
+      <c r="E258" s="5"/>
+      <c r="F258" s="5"/>
+      <c r="G258" s="5"/>
+      <c r="H258" s="5"/>
+      <c r="I258" s="5"/>
+      <c r="J258" s="5"/>
+    </row>
+    <row r="259" spans="1:10" ht="42" customHeight="1">
+      <c r="A259" s="4"/>
+      <c r="B259" s="8"/>
+      <c r="C259" s="8"/>
+      <c r="D259" s="5"/>
+      <c r="E259" s="5"/>
+      <c r="F259" s="5"/>
+      <c r="G259" s="5"/>
+      <c r="H259" s="5"/>
+      <c r="I259" s="5"/>
+      <c r="J259" s="5"/>
+    </row>
+    <row r="260" spans="1:10" ht="42" customHeight="1">
+      <c r="A260" s="4"/>
+      <c r="B260" s="8"/>
+      <c r="C260" s="8"/>
+      <c r="D260" s="5"/>
+      <c r="E260" s="5"/>
+      <c r="F260" s="5"/>
+      <c r="G260" s="5"/>
+      <c r="H260" s="5"/>
+      <c r="I260" s="5"/>
+      <c r="J260" s="5"/>
+    </row>
+    <row r="261" spans="1:10" ht="42" customHeight="1">
+      <c r="A261" s="4"/>
+      <c r="B261" s="8"/>
+      <c r="C261" s="8"/>
+      <c r="D261" s="5"/>
+      <c r="E261" s="5"/>
+      <c r="F261" s="5"/>
+      <c r="G261" s="5"/>
+      <c r="H261" s="5"/>
+      <c r="I261" s="5"/>
+      <c r="J261" s="5"/>
+    </row>
+    <row r="262" spans="1:10" ht="42" customHeight="1">
+      <c r="A262" s="4"/>
+      <c r="B262" s="8"/>
+      <c r="C262" s="8"/>
+      <c r="D262" s="5"/>
+      <c r="E262" s="5"/>
+      <c r="F262" s="5"/>
+      <c r="G262" s="5"/>
+      <c r="H262" s="5"/>
+      <c r="I262" s="5"/>
+      <c r="J262" s="5"/>
+    </row>
+    <row r="263" spans="1:10" ht="42" customHeight="1">
+      <c r="A263" s="4"/>
+      <c r="B263" s="8"/>
+      <c r="C263" s="8"/>
+      <c r="D263" s="5"/>
+      <c r="E263" s="5"/>
+      <c r="F263" s="5"/>
+      <c r="G263" s="5"/>
+      <c r="H263" s="5"/>
+      <c r="I263" s="5"/>
+      <c r="J263" s="5"/>
+    </row>
+    <row r="264" spans="1:10" ht="42" customHeight="1">
+      <c r="A264" s="4"/>
+      <c r="B264" s="8"/>
+      <c r="C264" s="8"/>
+      <c r="D264" s="5"/>
+      <c r="E264" s="5"/>
+      <c r="F264" s="5"/>
+      <c r="G264" s="5"/>
+      <c r="H264" s="5"/>
+      <c r="I264" s="5"/>
+      <c r="J264" s="5"/>
+    </row>
+    <row r="265" spans="1:10" ht="42" customHeight="1">
+      <c r="A265" s="4"/>
+      <c r="B265" s="8"/>
+      <c r="C265" s="8"/>
+      <c r="D265" s="5"/>
+      <c r="E265" s="5"/>
+      <c r="F265" s="5"/>
+      <c r="G265" s="5"/>
+      <c r="H265" s="5"/>
+      <c r="I265" s="5"/>
+      <c r="J265" s="5"/>
+    </row>
+    <row r="266" spans="1:10" ht="42" customHeight="1">
+      <c r="A266" s="4"/>
+      <c r="B266" s="8"/>
+      <c r="C266" s="8"/>
+      <c r="D266" s="5"/>
+      <c r="E266" s="5"/>
+      <c r="F266" s="5"/>
+      <c r="G266" s="5"/>
+      <c r="H266" s="5"/>
+      <c r="I266" s="5"/>
+      <c r="J266" s="5"/>
+    </row>
+    <row r="267" spans="1:10" ht="42" customHeight="1">
+      <c r="A267" s="4"/>
+      <c r="B267" s="8"/>
+      <c r="C267" s="8"/>
+      <c r="D267" s="5"/>
+      <c r="E267" s="5"/>
+      <c r="F267" s="5"/>
+      <c r="G267" s="5"/>
+      <c r="H267" s="5"/>
+      <c r="I267" s="5"/>
+      <c r="J267" s="5"/>
+    </row>
+    <row r="268" spans="1:10" ht="42" customHeight="1">
+      <c r="A268" s="4"/>
+      <c r="B268" s="8"/>
+      <c r="C268" s="8"/>
+      <c r="D268" s="5"/>
+      <c r="E268" s="5"/>
+      <c r="F268" s="5"/>
+      <c r="G268" s="5"/>
+      <c r="H268" s="5"/>
+      <c r="I268" s="5"/>
+      <c r="J268" s="5"/>
+    </row>
+    <row r="269" spans="1:10" ht="42" customHeight="1">
+      <c r="A269" s="4"/>
+      <c r="B269" s="8"/>
+      <c r="C269" s="8"/>
+      <c r="D269" s="5"/>
+      <c r="E269" s="5"/>
+      <c r="F269" s="5"/>
+      <c r="G269" s="5"/>
+      <c r="H269" s="5"/>
+      <c r="I269" s="5"/>
+      <c r="J269" s="5"/>
+    </row>
+    <row r="270" spans="1:10" ht="42" customHeight="1">
+      <c r="A270" s="4"/>
+      <c r="B270" s="8"/>
+      <c r="C270" s="8"/>
+      <c r="D270" s="5"/>
+      <c r="E270" s="5"/>
+      <c r="F270" s="5"/>
+      <c r="G270" s="5"/>
+      <c r="H270" s="5"/>
+      <c r="I270" s="5"/>
+      <c r="J270" s="5"/>
+    </row>
+    <row r="271" spans="1:10" ht="42" customHeight="1">
+      <c r="A271" s="4"/>
+      <c r="B271" s="8"/>
+      <c r="C271" s="8"/>
+      <c r="D271" s="5"/>
+      <c r="E271" s="5"/>
+      <c r="F271" s="5"/>
+      <c r="G271" s="5"/>
+      <c r="H271" s="5"/>
+      <c r="I271" s="5"/>
+      <c r="J271" s="5"/>
+    </row>
+    <row r="272" spans="1:10" ht="42" customHeight="1">
+      <c r="A272" s="4"/>
+      <c r="B272" s="8"/>
+      <c r="C272" s="8"/>
+      <c r="D272" s="5"/>
+      <c r="E272" s="5"/>
+      <c r="F272" s="5"/>
+      <c r="G272" s="5"/>
+      <c r="H272" s="5"/>
+      <c r="I272" s="5"/>
+      <c r="J272" s="5"/>
+    </row>
+    <row r="273" spans="1:10" ht="42" customHeight="1">
+      <c r="A273" s="4"/>
+      <c r="B273" s="8"/>
+      <c r="C273" s="8"/>
+      <c r="D273" s="5"/>
+      <c r="E273" s="5"/>
+      <c r="F273" s="5"/>
+      <c r="G273" s="5"/>
+      <c r="H273" s="5"/>
+      <c r="I273" s="5"/>
+      <c r="J273" s="5"/>
+    </row>
+    <row r="274" spans="1:10" ht="42" customHeight="1">
+      <c r="A274" s="4"/>
+      <c r="B274" s="8"/>
+      <c r="C274" s="8"/>
+      <c r="D274" s="5"/>
+      <c r="E274" s="5"/>
+      <c r="F274" s="5"/>
+    </row>
+    <row r="275" spans="1:10" ht="42" customHeight="1">
+      <c r="A275" s="4"/>
+      <c r="B275" s="8"/>
+      <c r="C275" s="8"/>
+      <c r="D275" s="5"/>
+      <c r="E275" s="5"/>
+      <c r="F275" s="5"/>
+    </row>
+    <row r="276" spans="1:10" ht="42" customHeight="1">
+      <c r="A276" s="4"/>
+      <c r="B276" s="8"/>
+      <c r="C276" s="8"/>
+      <c r="D276" s="5"/>
+      <c r="E276" s="5"/>
+      <c r="F276" s="5"/>
+    </row>
+    <row r="277" spans="1:10" ht="42" customHeight="1">
+      <c r="A277" s="4"/>
+      <c r="B277" s="8"/>
+      <c r="C277" s="8"/>
+      <c r="D277" s="5"/>
+      <c r="E277" s="5"/>
+      <c r="F277" s="5"/>
+    </row>
+    <row r="278" spans="1:10" ht="42" customHeight="1">
+      <c r="A278" s="4"/>
+      <c r="B278" s="8"/>
+      <c r="C278" s="8"/>
+      <c r="D278" s="5"/>
+      <c r="E278" s="5"/>
+      <c r="F278" s="5"/>
+    </row>
+    <row r="279" spans="1:10" ht="42" customHeight="1">
+      <c r="A279" s="4"/>
+      <c r="B279" s="8"/>
+      <c r="C279" s="8"/>
+      <c r="D279" s="5"/>
+      <c r="E279" s="5"/>
+      <c r="F279" s="5"/>
+    </row>
+    <row r="280" spans="1:10" ht="42" customHeight="1">
+      <c r="A280" s="4"/>
+      <c r="B280" s="8"/>
+      <c r="C280" s="8"/>
+      <c r="D280" s="5"/>
+      <c r="E280" s="5"/>
+      <c r="F280" s="5"/>
+    </row>
+    <row r="281" spans="1:10" ht="42" customHeight="1">
+      <c r="A281" s="4"/>
+      <c r="B281" s="8"/>
+      <c r="C281" s="8"/>
+      <c r="D281" s="5"/>
+      <c r="E281" s="5"/>
+      <c r="F281" s="5"/>
+    </row>
+    <row r="282" spans="1:10" ht="42" customHeight="1">
+      <c r="A282" s="4"/>
+      <c r="B282" s="8"/>
+      <c r="C282" s="8"/>
+      <c r="D282" s="5"/>
+      <c r="E282" s="5"/>
+      <c r="F282" s="5"/>
+    </row>
+    <row r="283" spans="1:10" ht="42" customHeight="1">
+      <c r="A283" s="4"/>
+      <c r="B283" s="8"/>
+      <c r="C283" s="8"/>
+      <c r="D283" s="5"/>
+      <c r="E283" s="5"/>
+      <c r="F283" s="5"/>
+    </row>
+    <row r="284" spans="1:10" ht="42" customHeight="1">
+      <c r="A284" s="4"/>
+      <c r="B284" s="8"/>
+      <c r="C284" s="8"/>
+      <c r="D284" s="5"/>
+      <c r="E284" s="5"/>
+      <c r="F284" s="5"/>
+    </row>
+    <row r="285" spans="1:10" ht="42" customHeight="1">
+      <c r="A285" s="4"/>
+      <c r="B285" s="8"/>
+      <c r="C285" s="8"/>
+      <c r="D285" s="5"/>
+      <c r="E285" s="5"/>
+      <c r="F285" s="5"/>
+    </row>
+    <row r="286" spans="1:10" ht="42" customHeight="1">
+      <c r="A286" s="4"/>
+      <c r="B286" s="8"/>
+      <c r="C286" s="8"/>
+      <c r="D286" s="5"/>
+      <c r="E286" s="5"/>
+      <c r="F286" s="5"/>
+    </row>
+    <row r="287" spans="1:10" ht="42" customHeight="1">
+      <c r="A287" s="4"/>
+      <c r="B287" s="8"/>
+      <c r="C287" s="8"/>
+      <c r="D287" s="5"/>
+      <c r="E287" s="5"/>
+      <c r="F287" s="5"/>
+    </row>
+    <row r="288" spans="1:10" ht="42" customHeight="1">
+      <c r="A288" s="4"/>
+      <c r="B288" s="8"/>
+      <c r="C288" s="8"/>
+      <c r="D288" s="5"/>
+      <c r="E288" s="5"/>
+      <c r="F288" s="5"/>
+    </row>
+    <row r="289" spans="1:6" ht="42" customHeight="1">
+      <c r="A289" s="4"/>
+      <c r="B289" s="8"/>
+      <c r="C289" s="8"/>
+      <c r="D289" s="5"/>
+      <c r="E289" s="5"/>
+      <c r="F289" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="I2:I189 I191:I247">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="yes"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/question-bank.xlsx
+++ b/data/question-bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsun/Documents/Codex/exam-recall-trainer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9900D2CD-37B6-F742-AD4D-432D0CD721C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE988A4-F3A6-F34C-B36F-568EDC55939E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="600" windowWidth="27140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4220,10 +4220,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>As [A−] : [HA] ratio is unchanged</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Describe the difference between an element and a compound</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -5520,6 +5516,27 @@
   </si>
   <si>
     <t>More soluble impurity removed: removing / filtering crystals from cold solution</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>As [A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>] : [HA] ratio is unchanged</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -11730,7 +11747,7 @@
     </row>
     <row r="2" spans="1:10" ht="42" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B2" s="7">
         <v>2</v>
@@ -11739,13 +11756,13 @@
         <v>833</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>900</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>901</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -11754,7 +11771,7 @@
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -11763,13 +11780,13 @@
         <v>833</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>968</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>969</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -11778,7 +11795,7 @@
     </row>
     <row r="4" spans="1:10" ht="42" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B4" s="7">
         <v>2</v>
@@ -11787,13 +11804,13 @@
         <v>833</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>966</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>967</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -11802,7 +11819,7 @@
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B5" s="7">
         <v>2</v>
@@ -11811,13 +11828,13 @@
         <v>833</v>
       </c>
       <c r="D5" s="12" t="s">
+        <v>964</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>965</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>966</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -11826,7 +11843,7 @@
     </row>
     <row r="6" spans="1:10" ht="42" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B6" s="8">
         <v>2</v>
@@ -11835,10 +11852,10 @@
         <v>833</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>940</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>941</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -11848,7 +11865,7 @@
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B7" s="8">
         <v>2</v>
@@ -11857,10 +11874,10 @@
         <v>834</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -11870,7 +11887,7 @@
     </row>
     <row r="8" spans="1:10" ht="42" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B8" s="8">
         <v>2</v>
@@ -11879,10 +11896,10 @@
         <v>834</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -11892,7 +11909,7 @@
     </row>
     <row r="9" spans="1:10" ht="42" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B9" s="8">
         <v>2</v>
@@ -11901,13 +11918,13 @@
         <v>834</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>936</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>937</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -11916,7 +11933,7 @@
     </row>
     <row r="10" spans="1:10" ht="42" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B10" s="8">
         <v>2</v>
@@ -11925,10 +11942,10 @@
         <v>834</v>
       </c>
       <c r="D10" s="5" t="s">
+        <v>937</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>938</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>939</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -11938,7 +11955,7 @@
     </row>
     <row r="11" spans="1:10" ht="42" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B11" s="8">
         <v>2</v>
@@ -11947,13 +11964,13 @@
         <v>834</v>
       </c>
       <c r="D11" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>924</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>925</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>926</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -11962,7 +11979,7 @@
     </row>
     <row r="12" spans="1:10" ht="42" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B12" s="8">
         <v>2</v>
@@ -11984,7 +12001,7 @@
     </row>
     <row r="13" spans="1:10" ht="42" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B13" s="8">
         <v>2</v>
@@ -12006,7 +12023,7 @@
     </row>
     <row r="14" spans="1:10" ht="42" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B14" s="8">
         <v>2</v>
@@ -12030,7 +12047,7 @@
     </row>
     <row r="15" spans="1:10" ht="42" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B15" s="8">
         <v>2</v>
@@ -12052,7 +12069,7 @@
     </row>
     <row r="16" spans="1:10" ht="42" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B16" s="8">
         <v>2</v>
@@ -12076,7 +12093,7 @@
     </row>
     <row r="17" spans="1:10" ht="42" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B17" s="8">
         <v>2</v>
@@ -12102,7 +12119,7 @@
     </row>
     <row r="18" spans="1:10" ht="42" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B18" s="8">
         <v>2</v>
@@ -12111,13 +12128,13 @@
         <v>834</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G18" s="11"/>
       <c r="H18" s="5"/>
@@ -12126,7 +12143,7 @@
     </row>
     <row r="19" spans="1:10" ht="42" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B19" s="8">
         <v>2</v>
@@ -12135,10 +12152,10 @@
         <v>834</v>
       </c>
       <c r="D19" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>921</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>922</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="11"/>
@@ -12148,7 +12165,7 @@
     </row>
     <row r="20" spans="1:10" ht="42" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B20" s="8">
         <v>2</v>
@@ -12157,13 +12174,13 @@
         <v>834</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>984</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>985</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>986</v>
       </c>
       <c r="G20" s="11"/>
       <c r="H20" s="5"/>
@@ -12172,7 +12189,7 @@
     </row>
     <row r="21" spans="1:10" ht="42" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B21" s="8">
         <v>2</v>
@@ -12196,7 +12213,7 @@
     </row>
     <row r="22" spans="1:10" ht="42" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B22" s="8">
         <v>2</v>
@@ -12205,10 +12222,10 @@
         <v>834</v>
       </c>
       <c r="D22" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>914</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>915</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="11"/>
@@ -12218,7 +12235,7 @@
     </row>
     <row r="23" spans="1:10" ht="42" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B23" s="7">
         <v>2</v>
@@ -12241,7 +12258,7 @@
     </row>
     <row r="24" spans="1:10" ht="42" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B24" s="7">
         <v>2</v>
@@ -12250,13 +12267,13 @@
         <v>835</v>
       </c>
       <c r="D24" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>943</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>944</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
@@ -12264,7 +12281,7 @@
     </row>
     <row r="25" spans="1:10" ht="42" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B25" s="8">
         <v>2</v>
@@ -12288,7 +12305,7 @@
     </row>
     <row r="26" spans="1:10" ht="42" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B26" s="8">
         <v>2</v>
@@ -12314,7 +12331,7 @@
     </row>
     <row r="27" spans="1:10" ht="42" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B27" s="8">
         <v>2</v>
@@ -12323,26 +12340,26 @@
         <v>835</v>
       </c>
       <c r="D27" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>905</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>906</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>907</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>908</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>909</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="1:10" ht="42" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B28" s="8">
         <v>2</v>
@@ -12351,13 +12368,13 @@
         <v>835</v>
       </c>
       <c r="D28" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>916</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>918</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>917</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
@@ -12366,7 +12383,7 @@
     </row>
     <row r="29" spans="1:10" ht="42" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="B29" s="8">
         <v>2</v>
@@ -12375,10 +12392,10 @@
         <v>835</v>
       </c>
       <c r="D29" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>957</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>958</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -12388,7 +12405,7 @@
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B30" s="8">
         <v>2</v>
@@ -12397,10 +12414,10 @@
         <v>835</v>
       </c>
       <c r="D30" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>955</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>956</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -12410,16 +12427,16 @@
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B31" s="8">
         <v>2</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>859</v>
@@ -12434,41 +12451,41 @@
     </row>
     <row r="32" spans="1:10" ht="42" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B32" s="8">
         <v>2</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D32" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>988</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>989</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>990</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="H32" s="5" t="s">
         <v>991</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>992</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
     </row>
     <row r="33" spans="1:10" ht="42" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B33" s="8">
         <v>2</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>888</v>
@@ -12484,13 +12501,13 @@
     </row>
     <row r="34" spans="1:10" ht="42" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B34" s="8">
         <v>2</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>861</v>
@@ -12510,7 +12527,7 @@
     </row>
     <row r="35" spans="1:10" ht="42" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B35" s="7">
         <v>2</v>
@@ -12519,13 +12536,13 @@
         <v>836</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>946</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>947</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -12534,7 +12551,7 @@
     </row>
     <row r="36" spans="1:10" ht="42" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B36" s="7">
         <v>2</v>
@@ -12543,13 +12560,13 @@
         <v>836</v>
       </c>
       <c r="D36" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>952</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>953</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>954</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
@@ -12558,7 +12575,7 @@
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B37" s="7">
         <v>2</v>
@@ -12584,7 +12601,7 @@
     </row>
     <row r="38" spans="1:10" ht="42" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B38" s="7">
         <v>2</v>
@@ -12593,26 +12610,26 @@
         <v>836</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>947</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>948</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="F38" s="5" t="s">
         <v>949</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>951</v>
-      </c>
       <c r="H38" s="5" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
     </row>
     <row r="39" spans="1:10" ht="42" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B39" s="8">
         <v>2</v>
@@ -12636,7 +12653,7 @@
     </row>
     <row r="40" spans="1:10" ht="42" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B40" s="8">
         <v>2</v>
@@ -12658,7 +12675,7 @@
     </row>
     <row r="41" spans="1:10" ht="42" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B41" s="8">
         <v>2</v>
@@ -12682,7 +12699,7 @@
     </row>
     <row r="42" spans="1:10" ht="42" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B42" s="8">
         <v>2</v>
@@ -12691,16 +12708,16 @@
         <v>837</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>927</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="F42" s="5" t="s">
         <v>928</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="G42" s="5" t="s">
         <v>929</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>930</v>
       </c>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -12708,7 +12725,7 @@
     </row>
     <row r="43" spans="1:10" ht="42" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B43" s="8">
         <v>2</v>
@@ -12732,7 +12749,7 @@
     </row>
     <row r="44" spans="1:10" ht="42" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B44" s="8">
         <v>2</v>
@@ -12756,7 +12773,7 @@
     </row>
     <row r="45" spans="1:10" ht="42" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B45" s="8">
         <v>2</v>
@@ -12765,13 +12782,13 @@
         <v>837</v>
       </c>
       <c r="D45" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>903</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>904</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
@@ -12780,7 +12797,7 @@
     </row>
     <row r="46" spans="1:10" ht="42" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B46" s="8">
         <v>2</v>
@@ -12795,7 +12812,7 @@
         <v>897</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>898</v>
+        <v>1189</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
@@ -12804,7 +12821,7 @@
     </row>
     <row r="47" spans="1:10" ht="42" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B47" s="8">
         <v>2</v>
@@ -12813,16 +12830,16 @@
         <v>837</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>958</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>959</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="F47" s="5" t="s">
         <v>960</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="G47" s="5" t="s">
         <v>961</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>962</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -12830,7 +12847,7 @@
     </row>
     <row r="48" spans="1:10" ht="42" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B48" s="8">
         <v>2</v>
@@ -12852,7 +12869,7 @@
     </row>
     <row r="49" spans="1:10" ht="42" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B49" s="8">
         <v>2</v>
@@ -12861,13 +12878,13 @@
         <v>837</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E49" s="5" t="s">
+        <v>979</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>980</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>981</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -12876,7 +12893,7 @@
     </row>
     <row r="50" spans="1:10" ht="42" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B50" s="8">
         <v>2</v>
@@ -12885,13 +12902,13 @@
         <v>837</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -12900,7 +12917,7 @@
     </row>
     <row r="51" spans="1:10" ht="42" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B51" s="8">
         <v>2</v>
@@ -12909,10 +12926,10 @@
         <v>837</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -12922,7 +12939,7 @@
     </row>
     <row r="52" spans="1:10" ht="42" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B52" s="8">
         <v>2</v>
@@ -12931,10 +12948,10 @@
         <v>837</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -12944,7 +12961,7 @@
     </row>
     <row r="53" spans="1:10" ht="42" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B53" s="8">
         <v>2</v>
@@ -12966,7 +12983,7 @@
     </row>
     <row r="54" spans="1:10" ht="42" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B54" s="7">
         <v>2</v>
@@ -12988,7 +13005,7 @@
     </row>
     <row r="55" spans="1:10" ht="42" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B55" s="8">
         <v>2</v>
@@ -13010,7 +13027,7 @@
     </row>
     <row r="56" spans="1:10" ht="42" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B56" s="8">
         <v>2</v>
@@ -13019,16 +13036,16 @@
         <v>837</v>
       </c>
       <c r="D56" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>931</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="F56" s="5" t="s">
         <v>932</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="G56" s="5" t="s">
         <v>933</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>934</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -13036,7 +13053,7 @@
     </row>
     <row r="57" spans="1:10" ht="42" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B57" s="8">
         <v>2</v>
@@ -13060,7 +13077,7 @@
     </row>
     <row r="58" spans="1:10" ht="42" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B58" s="8">
         <v>2</v>
@@ -13069,13 +13086,13 @@
         <v>837</v>
       </c>
       <c r="D58" s="5" t="s">
+        <v>974</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>975</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>977</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>976</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
@@ -13084,81 +13101,81 @@
     </row>
     <row r="59" spans="1:10" ht="42" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E59" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>1109</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="5" t="s">
         <v>1110</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="H59" s="5" t="s">
         <v>1111</v>
-      </c>
-      <c r="H59" s="5" t="s">
-        <v>1112</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
     </row>
     <row r="60" spans="1:10" ht="42" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E60" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G60" s="5" t="s">
         <v>1116</v>
       </c>
-      <c r="F60" s="5" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G60" s="5" t="s">
+      <c r="H60" s="5" t="s">
         <v>1117</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>1118</v>
       </c>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
     </row>
     <row r="61" spans="1:10" ht="42" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B61" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D61" s="5" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>1119</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
         <v>1120</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="G61" s="5" t="s">
         <v>1121</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>1122</v>
       </c>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -13166,25 +13183,25 @@
     </row>
     <row r="62" spans="1:10" ht="42" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C62" s="7" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D62" s="5" t="s">
         <v>1126</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="E62" s="5" t="s">
         <v>1127</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="F62" s="5" t="s">
         <v>1128</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="G62" s="5" t="s">
         <v>1129</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>1130</v>
       </c>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
@@ -13192,13 +13209,13 @@
     </row>
     <row r="63" spans="1:10" ht="42" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B63" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>561</v>
@@ -13214,13 +13231,13 @@
     </row>
     <row r="64" spans="1:10" ht="42" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>564</v>
@@ -13236,13 +13253,13 @@
     </row>
     <row r="65" spans="1:10" ht="42" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B65" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>567</v>
@@ -13260,49 +13277,49 @@
     </row>
     <row r="66" spans="1:10" ht="42" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D66" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>1069</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="F66" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G66" s="5" t="s">
         <v>1070</v>
       </c>
-      <c r="F66" s="5" t="s">
-        <v>1188</v>
-      </c>
-      <c r="G66" s="5" t="s">
+      <c r="H66" s="5" t="s">
         <v>1071</v>
       </c>
-      <c r="H66" s="5" t="s">
+      <c r="I66" s="5" t="s">
         <v>1072</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>1073</v>
       </c>
       <c r="J66" s="5"/>
     </row>
     <row r="67" spans="1:10" ht="42" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D67" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>1074</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>1075</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -13312,22 +13329,22 @@
     </row>
     <row r="68" spans="1:10" ht="42" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D68" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>1076</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>1077</v>
-      </c>
       <c r="F68" s="5" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -13336,19 +13353,19 @@
     </row>
     <row r="69" spans="1:10" ht="42" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B69" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -13358,19 +13375,19 @@
     </row>
     <row r="70" spans="1:10" ht="42" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -13380,19 +13397,19 @@
     </row>
     <row r="71" spans="1:10" ht="42" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B71" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D71" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>1082</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>1083</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -13402,50 +13419,50 @@
     </row>
     <row r="72" spans="1:10" ht="42" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D72" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>1084</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="F72" s="5" t="s">
         <v>1085</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="G72" s="5" t="s">
         <v>1086</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="H72" s="5" t="s">
         <v>1087</v>
-      </c>
-      <c r="H72" s="5" t="s">
-        <v>1088</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
     </row>
     <row r="73" spans="1:10" ht="42" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E73" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F73" s="5" t="s">
         <v>1089</v>
-      </c>
-      <c r="F73" s="5" t="s">
-        <v>1090</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
@@ -13454,22 +13471,22 @@
     </row>
     <row r="74" spans="1:10" ht="42" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D74" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E74" s="5" t="s">
         <v>1092</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="F74" s="5" t="s">
         <v>1093</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>1094</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
@@ -13478,22 +13495,22 @@
     </row>
     <row r="75" spans="1:10" ht="42" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E75" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F75" s="5" t="s">
         <v>1097</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>1098</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
@@ -13502,19 +13519,19 @@
     </row>
     <row r="76" spans="1:10" ht="42" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -13524,53 +13541,53 @@
     </row>
     <row r="77" spans="1:10" ht="42" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D77" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>1100</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="F77" s="5" t="s">
         <v>1101</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="G77" s="5" t="s">
         <v>1102</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="H77" s="5" t="s">
         <v>1103</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>1104</v>
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
     </row>
     <row r="78" spans="1:10" ht="42" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D78" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>1105</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="F78" s="5" t="s">
         <v>1106</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="G78" s="5" t="s">
         <v>1107</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>1108</v>
       </c>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
@@ -13578,22 +13595,22 @@
     </row>
     <row r="79" spans="1:10" ht="42" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D79" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>1131</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="F79" s="5" t="s">
         <v>1132</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>1133</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -13602,22 +13619,22 @@
     </row>
     <row r="80" spans="1:10" ht="42" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>1134</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="F80" s="5" t="s">
         <v>1135</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>1136</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -13626,25 +13643,25 @@
     </row>
     <row r="81" spans="1:10" ht="42" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D81" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>1137</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="F81" s="5" t="s">
         <v>1138</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="G81" s="5" t="s">
         <v>1139</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>1140</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
@@ -13652,22 +13669,22 @@
     </row>
     <row r="82" spans="1:10" ht="42" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E82" s="5" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>1141</v>
-      </c>
-      <c r="F82" s="5" t="s">
-        <v>1142</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
@@ -13676,19 +13693,19 @@
     </row>
     <row r="83" spans="1:10" ht="42" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D83" s="5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>1144</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>1145</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -13698,25 +13715,25 @@
     </row>
     <row r="84" spans="1:10" ht="42" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D84" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E84" s="5" t="s">
         <v>1146</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="F84" s="5" t="s">
         <v>1147</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="G84" s="5" t="s">
         <v>1148</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>1149</v>
       </c>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
@@ -13724,22 +13741,22 @@
     </row>
     <row r="85" spans="1:10" ht="42" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D85" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E85" s="5" t="s">
         <v>1150</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="F85" s="5" t="s">
         <v>1151</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>1152</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -13748,108 +13765,108 @@
     </row>
     <row r="86" spans="1:10" ht="42" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D86" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>1153</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="F86" s="5" t="s">
         <v>1154</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="G86" s="5" t="s">
         <v>1155</v>
       </c>
-      <c r="G86" s="5" t="s">
+      <c r="H86" s="5" t="s">
         <v>1156</v>
-      </c>
-      <c r="H86" s="5" t="s">
-        <v>1157</v>
       </c>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
     </row>
     <row r="87" spans="1:10" ht="42" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D87" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E87" s="5" t="s">
         <v>1158</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="F87" s="5" t="s">
         <v>1159</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="G87" s="5" t="s">
         <v>1160</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>1161</v>
-      </c>
       <c r="H87" s="5" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
     </row>
     <row r="88" spans="1:10" ht="42" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D88" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>1162</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="F88" s="5" t="s">
         <v>1163</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="G88" s="5" t="s">
         <v>1164</v>
       </c>
-      <c r="G88" s="5" t="s">
+      <c r="H88" s="5" t="s">
         <v>1165</v>
       </c>
-      <c r="H88" s="5" t="s">
+      <c r="I88" s="5" t="s">
         <v>1166</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>1167</v>
       </c>
       <c r="J88" s="5"/>
     </row>
     <row r="89" spans="1:10" ht="42" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D89" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>1168</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="F89" s="5" t="s">
         <v>1169</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>1170</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>

--- a/data/question-bank.xlsx
+++ b/data/question-bank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adamsun/Documents/Codex/exam-recall-trainer/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE988A4-F3A6-F34C-B36F-568EDC55939E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30258CE7-780D-EE46-9399-2BE87039AD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="600" windowWidth="27140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="540" yWindow="600" windowWidth="27140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CIE_IGCSE_CHEM" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="1474">
   <si>
     <t>id</t>
   </si>
@@ -3943,10 +3943,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>enthalpy of hydrogenation is less exothermic than 3x that of cyclohexene</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Outline how modern chemists have improved communication when naming chemical substances</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -4245,10 +4241,6 @@
   </si>
   <si>
     <t>Explain why the complex is colored</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ligand causes d-orbitals to split, creating ΔE</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -4806,8 +4798,1802 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>1 General Terms</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how recrystallization is carried out</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dissolved in minimum volume hot solvent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Solution allowed to cool slowly</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crystals filtered off</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crystals rinsed with small quantity of cold solvent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State the most important factor to be considered when choosing a solvent for recrystallization</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Solid very soluble in hot solvent AND not very soluble in cold solvent</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how impurities with differing solubilities are separated from the desired product</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less soluble impurity removed: filtering hot solution from solids</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deduce how using too much solvent would affect the product of recrystallization</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deduce how using too little solvent would affect the product of recrystallization</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low / decreased yield</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low / decreased purity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how you would separate iron from other substances</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use a magnet to remove iron</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how you would separate sand and sodium chloride</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add excess water to dissolve NaCl</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Filter the sand, and produce saltwater filtrate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heat the sand to dry</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boil off / evaporate water from salt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fractional distillation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>They have different boiling points</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe, with reason, how you would separate methanol and butan-1-ol</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why it is important to seal the chamber for chromatography</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Saturate chamber with solvent vapor</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prevents evaporation of solvent before completion of experiment</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why it is important to keep the start line horizontal when running the chromatograph</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why it is important to keep the start line above the solvent level when running the chromatograph</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prevent angled solvent front for improved separation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Solvent moves straight up paper at same rate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prevent the sample dissolving in the solvent with unpredictable movement</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain how the separation of inks is achieved using paper chromatography</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Continuous cycle of adsorption and desorption</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sample moves when in solvent AND does not move when on paper</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Samples have different attractions / affinities to mobile phase and stationary phase</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Separations based on polarities</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>The student hypothesized there were more than four coloured inks in the mixture. Suggest how the student could modify this chromatography experiment to evaluate the hypothesis</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try different solvent/solvent system</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Run chromatogram on longer paper for longer time</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Run thin layer chromatography / TLC</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Corrosive / skin burn</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage to respiratory tract</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eye damage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poisoning</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline common safety precautions in labs</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline common health and safety risks in lab experiments</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fume hood / respirators</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use of gloves</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Safety goggles</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Keep away from flames / use explosive-free container</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline common green chemistry perspectives in labs</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use less reagent - reduce chemical waste</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry out reactions with less effects on global warming</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry out reactions with less effects on depletion of ozone layer</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>3 Separating Mixtures</t>
+  </si>
+  <si>
+    <t>3 Separating Mixtures</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 Key Experiments</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2 Lab Apparatus</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest how the constant temperature could be easily maintained in a school laboratory</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thermostatic water bath</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temperature controlled hot plate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temperature controlled incubator</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State assumptions that are made to calculate the enthalpy of neutralization</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Specific heat capacity of solution is equal to that of water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Density of solution is equal to that of water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest a change to the apparatus that would reduce heat loss for calorimetry</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Replace glass flask with a polystyrene cup</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add a lid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deduce sources of systematic errors for calorimetry experiments</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heat loss to surroundings</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water evaporating from beaker</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not accounting for the heat absorbed by beakers / cups</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce heat loss to surroundings, better insulator</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polystyrene cup has a lower specific heat</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest advantages of replacing glass cup with a polystyrene cup for calorimetry experiments</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>For colorimetry experiment, a student started the experiment and recorded the absorbance value immediately. Suggest why this may not give a reliable result</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equilibrium not reached, reaction still occurring</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>For colorimetry experiment, describe how the solution can be used to construct a calibration curve</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dilute solution to make multiple concentrations</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure the absorbance of these solutions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plot graph of absorbance against concentration with a straight line of best fit</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>For colorimetry experiment, explain how calibration curve can be used to determine the unknown concentration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Measure the absorbance of the unknown</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use the calibrated graph to determine concentration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe the process of preparing a standard solution from a solid using a volumetric flask</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fully dissolve solid in deionized water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transfer the solution with washings</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fill up to line</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stopper the flask and turn over several times to homogenize the solution</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest how to make a (known c &amp; v solution) from the original (known c &amp; v solution)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carry out calculation to find out volume required</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Use ... cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> volumetric pipette / burette to transfer to ... cm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> volumetric flask</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fill up to line with deionized water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evaluate the use of an indicator versus a pH probe to determine the end point of the titration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probe more precise</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probe no personal judgement of color change involved</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probes must be calibrated before use</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probes provide continuous monitoring</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pH probe not chemically adding to system</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest a reason why trial 1 should not be included when finding the mean volume for titration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value not concordant with other values</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mean volume would be too high</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 What Drives Chemical Reactions</t>
+  </si>
+  <si>
+    <t>Hot solution filtered</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>More soluble impurity removed: removing / filtering crystals from cold solution</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>As [A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>] : [HA] ratio is unchanged</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Molecules have sufficient energy to overcome intermolecular forces</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gaseous molecules are further apart than in liquid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why the volume of sample increases when boiling point is reached</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why the volume occupied by sample at very high pressure is higher than the value calculated using PV = nRT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not behaving as an ideal gas at very high pressure</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ideal gas molecules have no volume</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Volume of molecules is not negligible</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chloroethane can be converted to ethanol. Identify the reagent and conditions necessary for this reaction to occur</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reagent: NaOH</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Condition: aqueous, heat under reflux</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how σ bonds are formed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how π bonds are formed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Head-on / end-to-end overlap of atomic / hybridized orbitals</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sideways overlap of parallel p orbitals</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain which structural isomer is the major product when but-1-ene reacts with HBr</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Major product: 2-bromobutane</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Secondary carbocation is more stable than primary carbocation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Alkyl groups are more electron donating / have greater inductive effect </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polarimeter</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Predict, with a reason, the electrical conductivity of metallic solid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Predict, with a reason, the electrical conductivity of ionic solid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>High electrical conductivity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electrons are free to move</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low electrical conductivity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ions are fixed in position, cannot move freely</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline the evidence that the electrons in a ... atom occupy ... main energy levels</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Successive ionization energies</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>... large increases in ionization energy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe the difference between the reactions of sodium and potassium with water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sodium reaction is slower / less vigorous</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Suggest why atmospheric SO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> (g) is an environmental concern</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reacts with water to form sulfuric acid, acid rain</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Highly corrosive</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why ... can be used as an acid–base indicator</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why (indicator) is suitable for this titration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Endpoint / pKa of (indicator) is within vertical section of curve</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equivalence point falls within pH range of indicator</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Suggest why the K</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> value for pure water increases as temperature increases</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dissociation of water is endothermic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Outline why tetramethylsilane, TMS, is often used as a reference standard in </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>H NMR spectroscopy</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Signal outside range of common chemical shifts</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>All 12 H atoms in same environment, singlet with no splitting</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest why there is a small peak with m/z of M+1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carbon-13</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why a salt bridge must be included to connect the two half cells</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Balances charges / keeps each half-cell electrically neutral</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Completes circuit / allows ion flow between cells</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Predict, giving a reason, the strength of carboxylic acid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weak acid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Organic acid, has -COOH</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why (salt) solutions are acidic / basic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>(if acidic salt): salt of strong acid and weak base
+(if basic salt): salt of strong base and weak acid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest a way to reduce the random uncertainty of the answer</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Repeat experiment AND take average</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Predict an intermolecular force which would be stronger in the next member of the homologous series</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State the reagent and conditions necessary to convert ethene to ethanol</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reagent: steam</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Condition: high temperature, high pressure, conc. H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>SO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest why experimental confirmation of the rate equation would not prove that the mechanism is correct</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Different mechanisms could give same rate equation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Does not give information about what occurs after RDS</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how ... acts as a Brønsted–Lowry acid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how ... acts as a Brønsted–Lowry base</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accepts proton</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Donates proton</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State / label the essential features of the standard hydrogen electrode</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>(g) at 100kPa</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1 mol dm</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>(aq)</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pt electrode</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temperature 298K</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>State the environmental problem caused by sulfur dioxide, SO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Acid rain</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Smog</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State one assumption made when calculating pH of an acid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>] from dissociation of H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>O negligible</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Partially filled d-orbitals, ligand causes d-orbitals to split, creating ΔE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State why gases become less ideal at higher pressures</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intermolecular forces no longer negligible</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Volume of molecules no longer negligible</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how two enantiomers can be distinguished</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rotate plane of polarized light in opposite directions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Predict, giving a reason, the result of reacting aqueous sodium bromide separately with iodine and chlorine</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iodine: no reaction, because iodine is less reactive than bromine</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chlorine: produces bromine, because chlorine is more reactive than bromine</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline what is meant by the term “homologous series”</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Same functional group</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Same general formula</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Successive members differ by -CH</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why ... is fully miscible with water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Can form hydrogen bonds with water molecules</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest why temperature has a very small effect on the value of this equilibrium constant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enthalpy change is very small</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State the reagent and conditions necessary to carry out esterification</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reagent: (named carboxylic acid) (named alcohol)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Condition: heat under reflux, conc. H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>SO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why you would expect the entropy change for this reaction to be quite small / zero</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Same moles of gas on both sides of equation</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why molten ionic compound is considered an electrolyte</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contains free ions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Outline how the Lewis structure of the BeCl</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> molecule differs from most Lewis structures</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Incomplete octet / central atom does not have complete valence shell</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline, in terms of its electronic structure, what identifies a transition element</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Has a partially filled d sub-shell in a common oxidation state</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Discuss why transition elements, but not group I or group II elements, have variable oxidation states</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IE values of transition elements gradually increase, AND IE values of group I &amp; II elements show sudden rise</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Further IEs of transition elements are close to second IE, so the oxidation states can vary</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why the first ionization energy increases from Li (Na) to Be (Mg), but decreases from Be (Mg) to B (Al)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nuclear charge increases</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Li and Be have same subshell / shielding</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electron in B lost from p-subshell whereas that in Be lost from s-subshell</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outer electron in p-subshell experiences greater shielding</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how the first ionization energy could be found from atomic emission spectrum</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequency / wavelength of convergence limit is proportional to the ionization energy</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline how the conductivity meter distinguishes between strong acid and weak acid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strong acid has higher conductivity due to higher ion concentration</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline what is meant by dynamic equilibrium</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>In a closed system, the rate of the forward reaction equals the rate of the reverse reaction</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why electrons flow from zinc to copper when these half cells are connected with a wire</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc is more reactive than copper</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zinc loses electrons more easily</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Significant difference in electronegativity value</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Element with higher EN) partial negative charge</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Element with lower EN) partial positive charge</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain the polarity of X-Y bond</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest ways of reducing the percentage uncertainty in calorimetry experiment</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>More divisions per degree on thermometer</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Larger quantities of water</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Larger temperature change</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>More precise balance</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Explain why a colorimeter set at a wavelength of 500 nm is not suitable to investigate reactions of Zn</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> compounds</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Zn</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> has a complete d subshell</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>500nm in visible region, no absorbance will be seen</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Outline what a &lt;1 K</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> value indicates about the
+extent of this reaction</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Outline what a &gt;1 K</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> value indicates about the
+extent of this reaction</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reaction hardly proceeds</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reverse reaction favored</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forward reaction favored</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Reactants] &gt; [Products]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[Reactants] &lt; [Products]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe the structure of graphite and explain why graphite conducts electricity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Layers of carbon atoms in a giant structure</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delocalized electrons flow along layers</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Deduce pieces of information about the electron configuration of (element) from its position on the periodic table / atomic number</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group ... - number of valence electrons</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Period ... - number of occupied electron shells</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>... block - the orbitals that are highest occupied</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline why metal is malleable</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Layers of cations slide over each other without disrupting bonding</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Metallic bonds are non-directional</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Identify the technique used to determine the relative proportions of the isotopes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mass spectrometry</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe how coordinate bonds are formed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>One atom / ion donates a pair of electrons to another atom / ion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe the change when alkene is reacted with bromine</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bromine water from orange to colorless</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Discuss different ways to reduce the environmental impact of energy production from coal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove sulfur from coal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Add lime during combustion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Not allow sulfur oxides to be released into the environment</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reduce proportion of power produced by the combustion of coal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Identify a metal, in the same period as magnesium, that does not form a basic oxide</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aluminium</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest reasons why atoms are no longer regarded as the indivisible units of matter</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Subatomic particles (particles smaller than atoms) are discovered</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atoms can gain or lose electrons and become charged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atoms can be split by nuclear fission</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Describe metallic bonding</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electrostatic attraction between positive metal ions and delocalized electrons</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest an experiment that shows that magnesium is more reactive than zinc, giving the observation that would confirm this</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Put both metals in acid: Mg dissolves faster, bubbles evolve more rapidly</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Put Mg in Zn</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>(aq): Zn forms on surface of Mg</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Construct a cell with Mg and Zn electrodes: Size of Mg decreases, size of Zn increases</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carbonates react with HCl and the rate can be determined by graphing the mass loss. Suggest why this method is less suitable for the reaction of Mg with HCl</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Relative decrease in mass is too small</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State how the use of a catalyst affects the position of the equilibrium</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unaffected</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Referring to equilibrium, outline why adding a small volume of strong acid / base would leave the pH of the buffer solution almost unchanged</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Equilibrium shifts to left / right when H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> / OH</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> reacts with ...</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>As large excess ratio [A</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>] : [HA] and hence pH is almost unchanged</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contrast transition metal and group I or II metal in terms of chemical properties</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transition metals have variable oxidation states, while group I or II metals only have +1 or +2 oxidation states</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transition metals form colored compounds, while group I or II metals only form white or colorless compounds</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transition metals can act as catalysts, while group I or II metals generally do not</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transition metals generally form complex ions, while group I or II metals generally do not</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline the requirements for a collision between reactants to yield products</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Collision energy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Cambria Math"/>
+        <family val="1"/>
+      </rPr>
+      <t>≧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> activation energy</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Correct orientation / geometry</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Outline, giving a reason, how the C-X bond polarity changes going down group 17</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Decreased polarity down the group</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electronegativity of halogen decreases</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Does not represent subshells</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Only applies to hydrogen atom</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Does not take into account interaction between atoms</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Does not consider probability of finding electron at different positions</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Suggest limitations to the model of the electron energy levels (n=...)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explain why there is a large increase from the ..th to the ..th ionization energy of ...</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Less shielding, electron closer to nucleus, in a lower energy level</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>... electron domains attached to central atom</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State the meaning of a strong Brønsted–Lowry acid / base</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>State the meaning of a weak Brønsted–Lowry acid / base</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fully ionizes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Partially ionizes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Outline the differences between the bonding of carbon atoms in C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> and diamond</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> fullerene: bond angles between 109–120° AND diamond: 109°</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> fullerene: sp</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> AND diamond: sp</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> fullerene: bonded to 3 C AND diamond: bonded to 4 C</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Explain why C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> and diamond sublime at different temperatures and pressures</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Diamond: giant covalent structure AND sublimes at higher temperature</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>IBHL003</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>IBHL004</t>
@@ -5017,449 +6803,6 @@
     <t>IBHL072</t>
   </si>
   <si>
-    <t>1 General Terms</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Describe how recrystallization is carried out</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dissolved in minimum volume hot solvent</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Solution allowed to cool slowly</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crystals filtered off</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Crystals rinsed with small quantity of cold solvent</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>State the most important factor to be considered when choosing a solvent for recrystallization</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Solid very soluble in hot solvent AND not very soluble in cold solvent</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Outline how impurities with differing solubilities are separated from the desired product</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Less soluble impurity removed: filtering hot solution from solids</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Deduce how using too much solvent would affect the product of recrystallization</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Deduce how using too little solvent would affect the product of recrystallization</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Low / decreased yield</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Low / decreased purity</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Describe how you would separate iron from other substances</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use a magnet to remove iron</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Describe how you would separate sand and sodium chloride</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Add excess water to dissolve NaCl</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Filter the sand, and produce saltwater filtrate</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Heat the sand to dry</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boil off / evaporate water from salt</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fractional distillation</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>They have different boiling points</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Describe, with reason, how you would separate methanol and butan-1-ol</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Explain why it is important to seal the chamber for chromatography</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Saturate chamber with solvent vapor</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prevents evaporation of solvent before completion of experiment</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Explain why it is important to keep the start line horizontal when running the chromatograph</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Explain why it is important to keep the start line above the solvent level when running the chromatograph</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prevent angled solvent front for improved separation</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Solvent moves straight up paper at same rate</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prevent the sample dissolving in the solvent with unpredictable movement</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Explain how the separation of inks is achieved using paper chromatography</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Continuous cycle of adsorption and desorption</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sample moves when in solvent AND does not move when on paper</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Samples have different attractions / affinities to mobile phase and stationary phase</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Separations based on polarities</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>The student hypothesized there were more than four coloured inks in the mixture. Suggest how the student could modify this chromatography experiment to evaluate the hypothesis</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Try different solvent/solvent system</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Run chromatogram on longer paper for longer time</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Run thin layer chromatography / TLC</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Corrosive / skin burn</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Damage to respiratory tract</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eye damage</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Poisoning</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Outline common safety precautions in labs</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Outline common health and safety risks in lab experiments</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fume hood / respirators</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use of gloves</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Safety goggles</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Keep away from flames / use explosive-free container</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Outline common green chemistry perspectives in labs</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use less reagent - reduce chemical waste</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Carry out reactions with less effects on global warming</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Carry out reactions with less effects on depletion of ozone layer</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>3 Separating Mixtures</t>
-  </si>
-  <si>
-    <t>3 Separating Mixtures</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>4 Key Experiments</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2 Lab Apparatus</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suggest how the constant temperature could be easily maintained in a school laboratory</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thermostatic water bath</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Temperature controlled hot plate</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Temperature controlled incubator</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>State assumptions that are made to calculate the enthalpy of neutralization</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Specific heat capacity of solution is equal to that of water</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Density of solution is equal to that of water</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suggest a change to the apparatus that would reduce heat loss for calorimetry</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Replace glass flask with a polystyrene cup</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Add a lid</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Deduce sources of systematic errors for calorimetry experiments</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Heat loss to surroundings</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Water evaporating from beaker</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Not accounting for the heat absorbed by beakers / cups</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reduce heat loss to surroundings, better insulator</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Polystyrene cup has a lower specific heat</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suggest advantages of replacing glass cup with a polystyrene cup for calorimetry experiments</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>For colorimetry experiment, a student started the experiment and recorded the absorbance value immediately. Suggest why this may not give a reliable result</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equilibrium not reached, reaction still occurring</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>For colorimetry experiment, describe how the solution can be used to construct a calibration curve</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dilute solution to make multiple concentrations</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Measure the absorbance of these solutions</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Plot graph of absorbance against concentration with a straight line of best fit</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>For colorimetry experiment, explain how calibration curve can be used to determine the unknown concentration</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Measure the absorbance of the unknown</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Use the calibrated graph to determine concentration</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Describe the process of preparing a standard solution from a solid using a volumetric flask</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fully dissolve solid in deionized water</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Transfer the solution with washings</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fill up to line</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stopper the flask and turn over several times to homogenize the solution</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suggest how to make a (known c &amp; v solution) from the original (known c &amp; v solution)</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Carry out calculation to find out volume required</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Use ... cm</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t xml:space="preserve"> volumetric pipette / burette to transfer to ... cm</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t xml:space="preserve"> volumetric flask</t>
-    </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fill up to line with deionized water</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evaluate the use of an indicator versus a pH probe to determine the end point of the titration</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pH probe more precise</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pH probe no personal judgement of color change involved</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pH probes must be calibrated before use</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pH probes provide continuous monitoring</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pH probe not chemically adding to system</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Suggest a reason why trial 1 should not be included when finding the mean volume for titration</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Value not concordant with other values</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mean volume would be too high</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>IBHL073</t>
   </si>
   <si>
@@ -5508,35 +6851,259 @@
     <t>IBHL088</t>
   </si>
   <si>
-    <t>4 What Drives Chemical Reactions</t>
-  </si>
-  <si>
-    <t>Hot solution filtered</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>More soluble impurity removed: removing / filtering crystals from cold solution</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>As [A</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos"/>
-      </rPr>
-      <t>] : [HA] ratio is unchanged</t>
-    </r>
+    <t>IBHL089</t>
+  </si>
+  <si>
+    <t>IBHL090</t>
+  </si>
+  <si>
+    <t>IBHL091</t>
+  </si>
+  <si>
+    <t>IBHL092</t>
+  </si>
+  <si>
+    <t>IBHL093</t>
+  </si>
+  <si>
+    <t>IBHL094</t>
+  </si>
+  <si>
+    <t>IBHL095</t>
+  </si>
+  <si>
+    <t>IBHL096</t>
+  </si>
+  <si>
+    <t>IBHL097</t>
+  </si>
+  <si>
+    <t>IBHL098</t>
+  </si>
+  <si>
+    <t>IBHL099</t>
+  </si>
+  <si>
+    <t>IBHL100</t>
+  </si>
+  <si>
+    <t>IBHL101</t>
+  </si>
+  <si>
+    <t>IBHL102</t>
+  </si>
+  <si>
+    <t>IBHL103</t>
+  </si>
+  <si>
+    <t>IBHL104</t>
+  </si>
+  <si>
+    <t>IBHL105</t>
+  </si>
+  <si>
+    <t>IBHL106</t>
+  </si>
+  <si>
+    <t>IBHL107</t>
+  </si>
+  <si>
+    <t>IBHL108</t>
+  </si>
+  <si>
+    <t>IBHL109</t>
+  </si>
+  <si>
+    <t>IBHL110</t>
+  </si>
+  <si>
+    <t>IBHL111</t>
+  </si>
+  <si>
+    <t>IBHL112</t>
+  </si>
+  <si>
+    <t>IBHL113</t>
+  </si>
+  <si>
+    <t>IBHL114</t>
+  </si>
+  <si>
+    <t>IBHL115</t>
+  </si>
+  <si>
+    <t>IBHL116</t>
+  </si>
+  <si>
+    <t>IBHL117</t>
+  </si>
+  <si>
+    <t>IBHL118</t>
+  </si>
+  <si>
+    <t>IBHL119</t>
+  </si>
+  <si>
+    <t>IBHL120</t>
+  </si>
+  <si>
+    <t>IBHL121</t>
+  </si>
+  <si>
+    <t>IBHL122</t>
+  </si>
+  <si>
+    <t>IBHL123</t>
+  </si>
+  <si>
+    <t>IBHL124</t>
+  </si>
+  <si>
+    <t>IBHL125</t>
+  </si>
+  <si>
+    <t>IBHL126</t>
+  </si>
+  <si>
+    <t>IBHL127</t>
+  </si>
+  <si>
+    <t>IBHL128</t>
+  </si>
+  <si>
+    <t>IBHL129</t>
+  </si>
+  <si>
+    <t>IBHL130</t>
+  </si>
+  <si>
+    <t>IBHL131</t>
+  </si>
+  <si>
+    <t>IBHL132</t>
+  </si>
+  <si>
+    <t>IBHL133</t>
+  </si>
+  <si>
+    <t>IBHL134</t>
+  </si>
+  <si>
+    <t>IBHL135</t>
+  </si>
+  <si>
+    <t>IBHL136</t>
+  </si>
+  <si>
+    <t>IBHL137</t>
+  </si>
+  <si>
+    <t>IBHL138</t>
+  </si>
+  <si>
+    <t>IBHL139</t>
+  </si>
+  <si>
+    <t>IBHL140</t>
+  </si>
+  <si>
+    <t>IBHL141</t>
+  </si>
+  <si>
+    <t>IBHL142</t>
+  </si>
+  <si>
+    <t>IBHL143</t>
+  </si>
+  <si>
+    <t>IBHL144</t>
+  </si>
+  <si>
+    <t>IBHL145</t>
+  </si>
+  <si>
+    <t>IBHL146</t>
+  </si>
+  <si>
+    <t>IBHL147</t>
+  </si>
+  <si>
+    <t>IBHL148</t>
+  </si>
+  <si>
+    <t>IBHL149</t>
+  </si>
+  <si>
+    <t>IBHL150</t>
+  </si>
+  <si>
+    <t>IBHL151</t>
+  </si>
+  <si>
+    <t>IBHL152</t>
+  </si>
+  <si>
+    <t>IBHL153</t>
+  </si>
+  <si>
+    <t>IBHL154</t>
+  </si>
+  <si>
+    <t>IBHL155</t>
+  </si>
+  <si>
+    <t>IBHL156</t>
+  </si>
+  <si>
+    <t>IBHL157</t>
+  </si>
+  <si>
+    <t>IBHL158</t>
+  </si>
+  <si>
+    <t>IBHL159</t>
+  </si>
+  <si>
+    <t>IBHL160</t>
+  </si>
+  <si>
+    <t>IBHL161</t>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t>60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve"> fullerene: intermolecular forces AND sublimes at lower temperature</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reaction almost goes to completion</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hydrogen gas does not ignite with sodium</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Conjugate acid and base pair have different colors</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enthalpy of hydrogenation is less exothermic than 3x that of cyclohexene</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5688,7 +7255,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5728,6 +7295,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5801,7 +7371,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3341C51B-6098-4C4D-86EB-AB33DCEB7697}" name="QuestionBank3" displayName="QuestionBank3" ref="A1:J289" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3341C51B-6098-4C4D-86EB-AB33DCEB7697}" name="QuestionBank3" displayName="QuestionBank3" ref="A1:J362" totalsRowShown="0">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{D80898F7-B13A-514A-83F3-0623537EEFE1}" name="id"/>
     <tableColumn id="2" xr3:uid="{44BE18D2-8686-7F4B-AEEB-F2DB1EFD3E35}" name="paper" dataDxfId="5"/>
@@ -11703,7 +13273,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{473DCC94-29A8-C34F-A636-6325DFC4A1BA}">
-  <dimension ref="A1:J289"/>
+  <dimension ref="A1:J362"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -11747,7 +13317,7 @@
     </row>
     <row r="2" spans="1:10" ht="42" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B2" s="7">
         <v>2</v>
@@ -11756,13 +13326,13 @@
         <v>833</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>899</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>900</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -11771,7 +13341,7 @@
     </row>
     <row r="3" spans="1:10" ht="42" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B3" s="7">
         <v>2</v>
@@ -11780,13 +13350,13 @@
         <v>833</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -11795,7 +13365,7 @@
     </row>
     <row r="4" spans="1:10" ht="42" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>997</v>
+        <v>1310</v>
       </c>
       <c r="B4" s="7">
         <v>2</v>
@@ -11804,13 +13374,13 @@
         <v>833</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>963</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>965</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -11819,7 +13389,7 @@
     </row>
     <row r="5" spans="1:10" ht="42" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>998</v>
+        <v>1311</v>
       </c>
       <c r="B5" s="7">
         <v>2</v>
@@ -11828,13 +13398,13 @@
         <v>833</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -11843,103 +13413,113 @@
     </row>
     <row r="6" spans="1:10" ht="42" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="B6" s="8">
+        <v>1312</v>
+      </c>
+      <c r="B6" s="7">
         <v>2</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>833</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>939</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>940</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="D6" s="14" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B7" s="8">
+        <v>1313</v>
+      </c>
+      <c r="B7" s="7">
         <v>2</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>909</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>911</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+        <v>833</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10" ht="42" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B8" s="8">
+        <v>1314</v>
+      </c>
+      <c r="B8" s="7">
         <v>2</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>910</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>912</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+        <v>833</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>1251</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10" ht="42" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B9" s="8">
+        <v>1315</v>
+      </c>
+      <c r="B9" s="7">
         <v>2</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>934</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>935</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>936</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+        <v>833</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10" ht="42" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>1003</v>
+        <v>1316</v>
       </c>
       <c r="B10" s="8">
         <v>2</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>937</v>
@@ -11955,23 +13535,21 @@
     </row>
     <row r="11" spans="1:10" ht="42" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>1004</v>
+        <v>1317</v>
       </c>
       <c r="B11" s="8">
         <v>2</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>923</v>
+        <v>1213</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>924</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>925</v>
-      </c>
+        <v>1214</v>
+      </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -11979,19 +13557,19 @@
     </row>
     <row r="12" spans="1:10" ht="42" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>1005</v>
+        <v>1318</v>
       </c>
       <c r="B12" s="8">
         <v>2</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>872</v>
+        <v>1297</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>873</v>
+        <v>1298</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -12001,21 +13579,23 @@
     </row>
     <row r="13" spans="1:10" ht="42" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>1006</v>
+        <v>1319</v>
       </c>
       <c r="B13" s="8">
         <v>2</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>875</v>
+        <v>1127</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>876</v>
-      </c>
-      <c r="F13" s="5"/>
+        <v>1128</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>1129</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -12023,45 +13603,49 @@
     </row>
     <row r="14" spans="1:10" ht="42" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>1007</v>
+        <v>1320</v>
       </c>
       <c r="B14" s="8">
         <v>2</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>841</v>
+        <v>1105</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>842</v>
+        <v>1106</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>843</v>
-      </c>
-      <c r="G14" s="5"/>
+        <v>1107</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>1108</v>
+      </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
     </row>
     <row r="15" spans="1:10" ht="42" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>1008</v>
+        <v>1321</v>
       </c>
       <c r="B15" s="8">
         <v>2</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>844</v>
+        <v>1178</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="F15" s="5"/>
+        <v>1179</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>1180</v>
+      </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -12069,7 +13653,7 @@
     </row>
     <row r="16" spans="1:10" ht="42" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>1009</v>
+        <v>1322</v>
       </c>
       <c r="B16" s="8">
         <v>2</v>
@@ -12078,14 +13662,12 @@
         <v>834</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>845</v>
+        <v>907</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>848</v>
-      </c>
+        <v>909</v>
+      </c>
+      <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
@@ -12093,7 +13675,7 @@
     </row>
     <row r="17" spans="1:10" ht="42" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>1010</v>
+        <v>1323</v>
       </c>
       <c r="B17" s="8">
         <v>2</v>
@@ -12102,24 +13684,20 @@
         <v>834</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>846</v>
+        <v>908</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>849</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>850</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>851</v>
-      </c>
+        <v>910</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
     </row>
     <row r="18" spans="1:10" ht="42" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>1011</v>
+        <v>1324</v>
       </c>
       <c r="B18" s="8">
         <v>2</v>
@@ -12128,22 +13706,20 @@
         <v>834</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>919</v>
+        <v>1268</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>992</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>918</v>
-      </c>
-      <c r="G18" s="11"/>
+        <v>1269</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
     </row>
     <row r="19" spans="1:10" ht="42" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>1012</v>
+        <v>1325</v>
       </c>
       <c r="B19" s="8">
         <v>2</v>
@@ -12152,20 +13728,22 @@
         <v>834</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>920</v>
+        <v>1121</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>921</v>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="11"/>
+        <v>1123</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
     </row>
     <row r="20" spans="1:10" ht="42" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>1013</v>
+        <v>1326</v>
       </c>
       <c r="B20" s="8">
         <v>2</v>
@@ -12174,22 +13752,22 @@
         <v>834</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>983</v>
+        <v>1122</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>984</v>
+        <v>1125</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>985</v>
-      </c>
-      <c r="G20" s="11"/>
+        <v>1126</v>
+      </c>
+      <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
     <row r="21" spans="1:10" ht="42" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>1014</v>
+        <v>1327</v>
       </c>
       <c r="B21" s="8">
         <v>2</v>
@@ -12198,22 +13776,20 @@
         <v>834</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>869</v>
+        <v>1199</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>870</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>871</v>
-      </c>
-      <c r="G21" s="11"/>
+        <v>1200</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
     </row>
     <row r="22" spans="1:10" ht="42" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>1015</v>
+        <v>1328</v>
       </c>
       <c r="B22" s="8">
         <v>2</v>
@@ -12222,82 +13798,82 @@
         <v>834</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>913</v>
+        <v>1248</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>914</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="11"/>
+        <v>1249</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
     </row>
     <row r="23" spans="1:10" ht="42" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B23" s="7">
+        <v>1329</v>
+      </c>
+      <c r="B23" s="8">
         <v>2</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>838</v>
+        <v>932</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>840</v>
+        <v>933</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>839</v>
-      </c>
+        <v>934</v>
+      </c>
+      <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
     </row>
     <row r="24" spans="1:10" ht="42" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B24" s="7">
+        <v>1330</v>
+      </c>
+      <c r="B24" s="8">
         <v>2</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>941</v>
+        <v>1253</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>942</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>943</v>
-      </c>
+        <v>1254</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
     </row>
     <row r="25" spans="1:10" ht="42" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>1018</v>
+        <v>1331</v>
       </c>
       <c r="B25" s="8">
         <v>2</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>852</v>
+        <v>935</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>853</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>854</v>
-      </c>
+        <v>936</v>
+      </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -12305,77 +13881,65 @@
     </row>
     <row r="26" spans="1:10" ht="42" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>1019</v>
+        <v>1332</v>
       </c>
       <c r="B26" s="8">
         <v>2</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>865</v>
+        <v>1201</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>866</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>867</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>868</v>
-      </c>
+        <v>1202</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
     </row>
     <row r="27" spans="1:10" ht="42" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>1020</v>
+        <v>1333</v>
       </c>
       <c r="B27" s="8">
         <v>2</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>904</v>
+        <v>1112</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>905</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>906</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>907</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>908</v>
-      </c>
+        <v>1114</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
     </row>
     <row r="28" spans="1:10" ht="42" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>1021</v>
+        <v>1334</v>
       </c>
       <c r="B28" s="8">
         <v>2</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>915</v>
+        <v>1113</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>917</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>916</v>
-      </c>
+        <v>1115</v>
+      </c>
+      <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
@@ -12383,41 +13947,45 @@
     </row>
     <row r="29" spans="1:10" ht="42" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>1022</v>
+        <v>1335</v>
       </c>
       <c r="B29" s="8">
         <v>2</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>956</v>
+        <v>921</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>957</v>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+        <v>1299</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>923</v>
+      </c>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
     </row>
     <row r="30" spans="1:10" ht="42" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>1023</v>
+        <v>1336</v>
       </c>
       <c r="B30" s="8">
         <v>2</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>954</v>
+        <v>871</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>955</v>
+        <v>872</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -12427,23 +13995,21 @@
     </row>
     <row r="31" spans="1:10" ht="42" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>1024</v>
+        <v>1337</v>
       </c>
       <c r="B31" s="8">
         <v>2</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1186</v>
+        <v>834</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>922</v>
+        <v>874</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>859</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>860</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
@@ -12451,47 +14017,43 @@
     </row>
     <row r="32" spans="1:10" ht="42" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>1025</v>
+        <v>1338</v>
       </c>
       <c r="B32" s="8">
         <v>2</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1186</v>
+        <v>834</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>987</v>
+        <v>841</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>988</v>
+        <v>842</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>989</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>990</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>991</v>
-      </c>
+        <v>843</v>
+      </c>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
     </row>
     <row r="33" spans="1:10" ht="42" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>1026</v>
+        <v>1339</v>
       </c>
       <c r="B33" s="8">
         <v>2</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1186</v>
+        <v>834</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>888</v>
+        <v>844</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -12501,345 +14063,337 @@
     </row>
     <row r="34" spans="1:10" ht="42" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>1027</v>
+        <v>1340</v>
       </c>
       <c r="B34" s="8">
         <v>2</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1186</v>
+        <v>834</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>861</v>
+        <v>845</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>863</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>864</v>
-      </c>
+        <v>848</v>
+      </c>
+      <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
     </row>
     <row r="35" spans="1:10" ht="42" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B35" s="7">
+        <v>1341</v>
+      </c>
+      <c r="B35" s="8">
         <v>2</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>944</v>
+        <v>846</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>945</v>
+        <v>849</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>946</v>
-      </c>
-      <c r="G35" s="5"/>
+        <v>850</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>1473</v>
+      </c>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
     </row>
     <row r="36" spans="1:10" ht="42" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B36" s="7">
+        <v>1342</v>
+      </c>
+      <c r="B36" s="8">
         <v>2</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>951</v>
+        <v>1225</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>952</v>
+        <v>1222</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>953</v>
-      </c>
-      <c r="G36" s="5"/>
+        <v>1223</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>1224</v>
+      </c>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
     </row>
     <row r="37" spans="1:10" ht="42" customHeight="1">
       <c r="A37" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B37" s="7">
+        <v>1343</v>
+      </c>
+      <c r="B37" s="8">
         <v>2</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>855</v>
+        <v>1289</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>856</v>
+        <v>1290</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>857</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>858</v>
-      </c>
+        <v>1291</v>
+      </c>
+      <c r="G37" s="11"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
     </row>
     <row r="38" spans="1:10" ht="42" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B38" s="7">
+        <v>1344</v>
+      </c>
+      <c r="B38" s="8">
         <v>2</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>947</v>
+        <v>917</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>948</v>
+        <v>990</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>949</v>
-      </c>
-      <c r="G38" s="5" t="s">
-        <v>950</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>986</v>
-      </c>
+        <v>916</v>
+      </c>
+      <c r="G38" s="11"/>
+      <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
     </row>
     <row r="39" spans="1:10" ht="42" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>1032</v>
+        <v>1345</v>
       </c>
       <c r="B39" s="8">
         <v>2</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>177</v>
+        <v>918</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G39" s="5"/>
+        <v>919</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="11"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
     </row>
     <row r="40" spans="1:10" ht="42" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>1033</v>
+        <v>1346</v>
       </c>
       <c r="B40" s="8">
         <v>2</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>181</v>
+        <v>981</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
+        <v>982</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="G40" s="11"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
     </row>
     <row r="41" spans="1:10" ht="42" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>1034</v>
+        <v>1347</v>
       </c>
       <c r="B41" s="8">
         <v>2</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>184</v>
+        <v>1190</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="G41" s="5"/>
+        <v>1191</v>
+      </c>
+      <c r="F41" s="5"/>
+      <c r="G41" s="11"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
     </row>
     <row r="42" spans="1:10" ht="42" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>1035</v>
+        <v>1348</v>
       </c>
       <c r="B42" s="8">
         <v>2</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>926</v>
+        <v>868</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>927</v>
+        <v>869</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>928</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>929</v>
-      </c>
+        <v>870</v>
+      </c>
+      <c r="G42" s="11"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
     </row>
     <row r="43" spans="1:10" ht="42" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>1036</v>
+        <v>1349</v>
       </c>
       <c r="B43" s="8">
         <v>2</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>879</v>
+        <v>1241</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>880</v>
+        <v>1242</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>881</v>
-      </c>
-      <c r="G43" s="5"/>
+        <v>1243</v>
+      </c>
+      <c r="G43" s="11"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
     </row>
     <row r="44" spans="1:10" ht="42" customHeight="1">
       <c r="A44" s="2" t="s">
-        <v>1037</v>
+        <v>1350</v>
       </c>
       <c r="B44" s="8">
         <v>2</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>882</v>
+        <v>1304</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>883</v>
+        <v>1307</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>884</v>
-      </c>
-      <c r="G44" s="5"/>
+        <v>1306</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>1305</v>
+      </c>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
     </row>
     <row r="45" spans="1:10" ht="42" customHeight="1">
       <c r="A45" s="2" t="s">
-        <v>1038</v>
+        <v>1351</v>
       </c>
       <c r="B45" s="8">
         <v>2</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>901</v>
+        <v>1308</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>902</v>
+        <v>1309</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>903</v>
-      </c>
-      <c r="G45" s="5"/>
+        <v>1469</v>
+      </c>
+      <c r="G45" s="11"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
     </row>
     <row r="46" spans="1:10" ht="42" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>1039</v>
+        <v>1352</v>
       </c>
       <c r="B46" s="8">
         <v>2</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>885</v>
+        <v>911</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>897</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>1189</v>
-      </c>
-      <c r="G46" s="5"/>
+        <v>912</v>
+      </c>
+      <c r="F46" s="5"/>
+      <c r="G46" s="11"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
     </row>
     <row r="47" spans="1:10" ht="42" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B47" s="8">
+        <v>1353</v>
+      </c>
+      <c r="B47" s="7">
         <v>2</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>958</v>
+        <v>1244</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>959</v>
+        <v>1245</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>960</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>961</v>
+        <v>1246</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>1247</v>
       </c>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -12847,157 +14401,165 @@
     </row>
     <row r="48" spans="1:10" ht="42" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B48" s="8">
+        <v>1354</v>
+      </c>
+      <c r="B48" s="7">
         <v>2</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>877</v>
+        <v>838</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>878</v>
-      </c>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
+        <v>840</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>839</v>
+      </c>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
     </row>
     <row r="49" spans="1:10" ht="42" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B49" s="8">
+        <v>1355</v>
+      </c>
+      <c r="B49" s="7">
         <v>2</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>977</v>
+        <v>939</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>979</v>
+        <v>940</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>980</v>
-      </c>
-      <c r="G49" s="5"/>
+        <v>941</v>
+      </c>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
     <row r="50" spans="1:10" ht="42" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B50" s="8">
+        <v>1356</v>
+      </c>
+      <c r="B50" s="7">
         <v>2</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>978</v>
+        <v>1208</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>982</v>
+        <v>1209</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>981</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
+        <v>1210</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H50" s="5" t="s">
+        <v>1212</v>
+      </c>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
     </row>
     <row r="51" spans="1:10" ht="42" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B51" s="8">
+        <v>1357</v>
+      </c>
+      <c r="B51" s="7">
         <v>2</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>971</v>
+        <v>1262</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>973</v>
+        <v>1263</v>
       </c>
       <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
+      <c r="G51" s="11"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5"/>
     </row>
     <row r="52" spans="1:10" ht="42" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B52" s="8">
+        <v>1358</v>
+      </c>
+      <c r="B52" s="7">
         <v>2</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>970</v>
+        <v>1130</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>972</v>
-      </c>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
+        <v>1131</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>1471</v>
+      </c>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5"/>
     </row>
     <row r="53" spans="1:10" ht="42" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="B53" s="8">
+        <v>1359</v>
+      </c>
+      <c r="B53" s="7">
         <v>2</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>886</v>
+        <v>1183</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>887</v>
-      </c>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
+        <v>1184</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>1185</v>
+      </c>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
     </row>
     <row r="54" spans="1:10" ht="42" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B54" s="7">
+        <v>1360</v>
+      </c>
+      <c r="B54" s="8">
         <v>2</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>890</v>
+        <v>851</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>893</v>
-      </c>
-      <c r="F54" s="5"/>
+        <v>852</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>853</v>
+      </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -13005,21 +14567,23 @@
     </row>
     <row r="55" spans="1:10" ht="42" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>1048</v>
+        <v>1361</v>
       </c>
       <c r="B55" s="8">
         <v>2</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>891</v>
+        <v>1132</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>892</v>
-      </c>
-      <c r="F55" s="5"/>
+        <v>1133</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>1134</v>
+      </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -13027,25 +14591,25 @@
     </row>
     <row r="56" spans="1:10" ht="42" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>1049</v>
+        <v>1362</v>
       </c>
       <c r="B56" s="8">
         <v>2</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>930</v>
+        <v>864</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>931</v>
+        <v>865</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>932</v>
+        <v>866</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>933</v>
+        <v>867</v>
       </c>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -13053,22 +14617,22 @@
     </row>
     <row r="57" spans="1:10" ht="42" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>1050</v>
+        <v>1363</v>
       </c>
       <c r="B57" s="8">
         <v>2</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>894</v>
+        <v>1172</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>895</v>
+        <v>1173</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>896</v>
+        <v>1174</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -13077,23 +14641,21 @@
     </row>
     <row r="58" spans="1:10" ht="42" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>1051</v>
+        <v>1364</v>
       </c>
       <c r="B58" s="8">
         <v>2</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>974</v>
+        <v>1203</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>976</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>975</v>
-      </c>
+        <v>1204</v>
+      </c>
+      <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
@@ -13101,151 +14663,153 @@
     </row>
     <row r="59" spans="1:10" ht="42" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>994</v>
+        <v>1365</v>
+      </c>
+      <c r="B59" s="8">
+        <v>2</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1067</v>
+        <v>835</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>1113</v>
+        <v>1281</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>1108</v>
+        <v>1282</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>1109</v>
+        <v>1283</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>1110</v>
+        <v>1284</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>1111</v>
+        <v>1285</v>
       </c>
       <c r="I59" s="5"/>
       <c r="J59" s="5"/>
     </row>
     <row r="60" spans="1:10" ht="42" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>993</v>
+        <v>1366</v>
+      </c>
+      <c r="B60" s="8">
+        <v>2</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1067</v>
+        <v>835</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>1112</v>
+        <v>1205</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>1115</v>
+        <v>1206</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>1114</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H60" s="5" t="s">
-        <v>1117</v>
-      </c>
+        <v>1207</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5"/>
     </row>
     <row r="61" spans="1:10" ht="42" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>993</v>
+        <v>1367</v>
+      </c>
+      <c r="B61" s="8">
+        <v>2</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>1067</v>
+        <v>835</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>1118</v>
+        <v>903</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>1119</v>
+        <v>1177</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>1120</v>
+        <v>904</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>1121</v>
-      </c>
-      <c r="H61" s="5"/>
+        <v>905</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>906</v>
+      </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
     </row>
     <row r="62" spans="1:10" ht="42" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>993</v>
+        <v>1368</v>
+      </c>
+      <c r="B62" s="8">
+        <v>2</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>1125</v>
+        <v>835</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>1126</v>
+        <v>1231</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>1127</v>
+        <v>1232</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>1128</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>1129</v>
-      </c>
+        <v>1233</v>
+      </c>
+      <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="5"/>
     </row>
     <row r="63" spans="1:10" ht="42" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>993</v>
+        <v>1369</v>
+      </c>
+      <c r="B63" s="8">
+        <v>2</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>1125</v>
+        <v>835</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>561</v>
+        <v>1186</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+        <v>1187</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>1189</v>
+      </c>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="5"/>
     </row>
     <row r="64" spans="1:10" ht="42" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>993</v>
+        <v>1370</v>
+      </c>
+      <c r="B64" s="8">
+        <v>2</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>1125</v>
+        <v>835</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>564</v>
+        <v>913</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>565</v>
-      </c>
-      <c r="F64" s="5"/>
+        <v>915</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>914</v>
+      </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
@@ -13253,23 +14817,21 @@
     </row>
     <row r="65" spans="1:10" ht="42" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>993</v>
+        <v>1371</v>
+      </c>
+      <c r="B65" s="8">
+        <v>2</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>1125</v>
+        <v>835</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>567</v>
+        <v>1156</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="F65" s="5" t="s">
-        <v>569</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="F65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
@@ -13277,51 +14839,45 @@
     </row>
     <row r="66" spans="1:10" ht="42" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>993</v>
+        <v>1372</v>
+      </c>
+      <c r="B66" s="8">
+        <v>2</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1123</v>
+        <v>835</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>1068</v>
+        <v>954</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>1069</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>1070</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>1071</v>
-      </c>
-      <c r="I66" s="5" t="s">
-        <v>1072</v>
-      </c>
+        <v>955</v>
+      </c>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
       <c r="J66" s="5"/>
     </row>
     <row r="67" spans="1:10" ht="42" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>993</v>
+        <v>1373</v>
+      </c>
+      <c r="B67" s="8">
+        <v>2</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>1123</v>
+        <v>835</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>1073</v>
+        <v>1181</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F67" s="5"/>
+        <v>1120</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>1182</v>
+      </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
@@ -13329,23 +14885,21 @@
     </row>
     <row r="68" spans="1:10" ht="42" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>993</v>
+        <v>1374</v>
+      </c>
+      <c r="B68" s="8">
+        <v>2</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>1123</v>
+        <v>835</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>1075</v>
+        <v>952</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>1188</v>
-      </c>
+        <v>953</v>
+      </c>
+      <c r="F68" s="5"/>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
@@ -13353,19 +14907,19 @@
     </row>
     <row r="69" spans="1:10" ht="42" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>993</v>
+        <v>1375</v>
+      </c>
+      <c r="B69" s="8">
+        <v>2</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>1122</v>
+        <v>835</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>1077</v>
+        <v>1144</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>1079</v>
+        <v>1145</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -13375,21 +14929,23 @@
     </row>
     <row r="70" spans="1:10" ht="42" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>993</v>
+        <v>1376</v>
+      </c>
+      <c r="B70" s="8">
+        <v>2</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>1122</v>
+        <v>835</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>1078</v>
+        <v>1141</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>1080</v>
-      </c>
-      <c r="F70" s="5"/>
+        <v>1142</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>1143</v>
+      </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" s="5"/>
@@ -13397,21 +14953,23 @@
     </row>
     <row r="71" spans="1:10" ht="42" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>993</v>
+        <v>1377</v>
+      </c>
+      <c r="B71" s="8">
+        <v>2</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>1122</v>
+        <v>1098</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>1081</v>
+        <v>920</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F71" s="5"/>
+        <v>858</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>859</v>
+      </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
@@ -13419,75 +14977,77 @@
     </row>
     <row r="72" spans="1:10" ht="42" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>993</v>
+        <v>1378</v>
+      </c>
+      <c r="B72" s="8">
+        <v>2</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1122</v>
+        <v>1098</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>1083</v>
+        <v>985</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>1084</v>
+        <v>986</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>1085</v>
+        <v>987</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>1086</v>
+        <v>988</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>1087</v>
+        <v>989</v>
       </c>
       <c r="I72" s="5"/>
       <c r="J72" s="5"/>
     </row>
     <row r="73" spans="1:10" ht="42" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>993</v>
+        <v>1379</v>
+      </c>
+      <c r="B73" s="8">
+        <v>2</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>1122</v>
+        <v>1098</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>1090</v>
+        <v>1257</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>1088</v>
+        <v>1258</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
+        <v>1259</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>1261</v>
+      </c>
       <c r="I73" s="5"/>
       <c r="J73" s="5"/>
     </row>
     <row r="74" spans="1:10" ht="42" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>993</v>
+        <v>1380</v>
+      </c>
+      <c r="B74" s="8">
+        <v>2</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1122</v>
+        <v>1098</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>1091</v>
+        <v>887</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>1093</v>
-      </c>
+        <v>888</v>
+      </c>
+      <c r="F74" s="5"/>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
@@ -13495,23 +15055,21 @@
     </row>
     <row r="75" spans="1:10" ht="42" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>1171</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>993</v>
+        <v>1381</v>
+      </c>
+      <c r="B75" s="8">
+        <v>2</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>1122</v>
+        <v>1098</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>1094</v>
+        <v>1197</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>1097</v>
-      </c>
+        <v>1198</v>
+      </c>
+      <c r="F75" s="5"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
@@ -13519,98 +15077,94 @@
     </row>
     <row r="76" spans="1:10" ht="42" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>993</v>
+        <v>1382</v>
+      </c>
+      <c r="B76" s="8">
+        <v>2</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>1122</v>
+        <v>1098</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>1095</v>
+        <v>860</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
+        <v>861</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>863</v>
+      </c>
       <c r="H76" s="5"/>
       <c r="I76" s="5"/>
       <c r="J76" s="5"/>
     </row>
     <row r="77" spans="1:10" ht="42" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>993</v>
+        <v>1383</v>
+      </c>
+      <c r="B77" s="7">
+        <v>2</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>1122</v>
+        <v>836</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>1099</v>
+        <v>1274</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>1102</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>1103</v>
-      </c>
+        <v>1275</v>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
       <c r="I77" s="5"/>
       <c r="J77" s="5"/>
     </row>
     <row r="78" spans="1:10" ht="42" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B78" s="13" t="s">
-        <v>993</v>
+        <v>1384</v>
+      </c>
+      <c r="B78" s="7">
+        <v>2</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>1122</v>
+        <v>836</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>1104</v>
+        <v>1286</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>1105</v>
+        <v>1287</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>1106</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>1107</v>
-      </c>
+        <v>1288</v>
+      </c>
+      <c r="G78" s="5"/>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
       <c r="J78" s="5"/>
     </row>
     <row r="79" spans="1:10" ht="42" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>993</v>
+        <v>1385</v>
+      </c>
+      <c r="B79" s="7">
+        <v>2</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>1130</v>
+        <v>942</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>1131</v>
+        <v>943</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>1132</v>
+        <v>944</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
@@ -13619,22 +15173,22 @@
     </row>
     <row r="80" spans="1:10" ht="42" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B80" s="13" t="s">
-        <v>993</v>
+        <v>1386</v>
+      </c>
+      <c r="B80" s="7">
+        <v>2</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>1133</v>
+        <v>949</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>1134</v>
+        <v>950</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>1135</v>
+        <v>951</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
@@ -13643,25 +15197,25 @@
     </row>
     <row r="81" spans="1:10" ht="42" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>993</v>
+        <v>1387</v>
+      </c>
+      <c r="B81" s="7">
+        <v>2</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>1136</v>
+        <v>854</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>1137</v>
+        <v>855</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>1138</v>
+        <v>856</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>1139</v>
+        <v>857</v>
       </c>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
@@ -13669,45 +15223,51 @@
     </row>
     <row r="82" spans="1:10" ht="42" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="B82" s="13" t="s">
-        <v>993</v>
+        <v>1388</v>
+      </c>
+      <c r="B82" s="7">
+        <v>2</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>1142</v>
+        <v>945</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>1140</v>
+        <v>946</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>1141</v>
-      </c>
-      <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
+        <v>947</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>984</v>
+      </c>
       <c r="I82" s="5"/>
       <c r="J82" s="5"/>
     </row>
     <row r="83" spans="1:10" ht="42" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>993</v>
+        <v>1389</v>
+      </c>
+      <c r="B83" s="7">
+        <v>2</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>1143</v>
+        <v>1160</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>1144</v>
-      </c>
-      <c r="F83" s="5"/>
+        <v>1161</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>1162</v>
+      </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="5"/>
@@ -13715,48 +15275,44 @@
     </row>
     <row r="84" spans="1:10" ht="42" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B84" s="13" t="s">
-        <v>993</v>
+        <v>1390</v>
+      </c>
+      <c r="B84" s="7">
+        <v>2</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>1145</v>
+        <v>1217</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>1147</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>1148</v>
-      </c>
+        <v>1218</v>
+      </c>
+      <c r="F84" s="5"/>
+      <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="5"/>
       <c r="J84" s="5"/>
     </row>
     <row r="85" spans="1:10" ht="42" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>993</v>
+        <v>1391</v>
+      </c>
+      <c r="B85" s="8">
+        <v>2</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>1149</v>
+        <v>177</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>1150</v>
+        <v>178</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>1151</v>
+        <v>179</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
@@ -13765,144 +15321,162 @@
     </row>
     <row r="86" spans="1:10" ht="42" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B86" s="13" t="s">
-        <v>993</v>
+        <v>1392</v>
+      </c>
+      <c r="B86" s="8">
+        <v>2</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>1152</v>
+        <v>181</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>1155</v>
-      </c>
-      <c r="H86" s="5" t="s">
-        <v>1156</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="F86" s="5"/>
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
     </row>
     <row r="87" spans="1:10" ht="42" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>993</v>
+        <v>1393</v>
+      </c>
+      <c r="B87" s="8">
+        <v>2</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>1157</v>
+        <v>184</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>1158</v>
+        <v>178</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>1159</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>1160</v>
-      </c>
-      <c r="H87" s="5" t="s">
-        <v>1156</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
       <c r="I87" s="5"/>
       <c r="J87" s="5"/>
     </row>
     <row r="88" spans="1:10" ht="42" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B88" s="13" t="s">
-        <v>993</v>
+        <v>1394</v>
+      </c>
+      <c r="B88" s="8">
+        <v>2</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>1161</v>
+        <v>1192</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>1162</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>1163</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>1164</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>1165</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>1166</v>
-      </c>
+        <v>1193</v>
+      </c>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
       <c r="J88" s="5"/>
     </row>
     <row r="89" spans="1:10" ht="42" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>993</v>
+        <v>1395</v>
+      </c>
+      <c r="B89" s="8">
+        <v>2</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>1124</v>
+        <v>836</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>1167</v>
+        <v>1276</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>1169</v>
-      </c>
+        <v>1277</v>
+      </c>
+      <c r="F89" s="5"/>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
       <c r="J89" s="5"/>
     </row>
     <row r="90" spans="1:10" ht="42" customHeight="1">
-      <c r="A90" s="4"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
-      <c r="G90" s="5"/>
+      <c r="A90" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B90" s="8">
+        <v>2</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>1239</v>
+      </c>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
     </row>
     <row r="91" spans="1:10" ht="42" customHeight="1">
-      <c r="A91" s="4"/>
-      <c r="B91" s="7"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
-      <c r="G91" s="5"/>
+      <c r="A91" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B91" s="8">
+        <v>2</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>1240</v>
+      </c>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
     </row>
     <row r="92" spans="1:10" ht="42" customHeight="1">
-      <c r="A92" s="4"/>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
+      <c r="A92" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B92" s="8">
+        <v>2</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>1166</v>
+      </c>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
@@ -13910,11 +15484,21 @@
       <c r="J92" s="5"/>
     </row>
     <row r="93" spans="1:10" ht="42" customHeight="1">
-      <c r="A93" s="4"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
+      <c r="A93" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B93" s="8">
+        <v>2</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>1165</v>
+      </c>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
@@ -13922,11 +15506,21 @@
       <c r="J93" s="5"/>
     </row>
     <row r="94" spans="1:10" ht="42" customHeight="1">
-      <c r="A94" s="4"/>
-      <c r="B94" s="7"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
+      <c r="A94" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B94" s="8">
+        <v>2</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>1302</v>
+      </c>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
@@ -13934,11 +15528,21 @@
       <c r="J94" s="5"/>
     </row>
     <row r="95" spans="1:10" ht="42" customHeight="1">
-      <c r="A95" s="4"/>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
+      <c r="A95" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B95" s="8">
+        <v>2</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>1303</v>
+      </c>
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
@@ -13946,23 +15550,47 @@
       <c r="J95" s="5"/>
     </row>
     <row r="96" spans="1:10" ht="42" customHeight="1">
-      <c r="A96" s="4"/>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
+      <c r="A96" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B96" s="8">
+        <v>2</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>927</v>
+      </c>
       <c r="H96" s="5"/>
       <c r="I96" s="5"/>
       <c r="J96" s="5"/>
     </row>
     <row r="97" spans="1:10" ht="42" customHeight="1">
-      <c r="A97" s="4"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
+      <c r="A97" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B97" s="8">
+        <v>2</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>1216</v>
+      </c>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
@@ -13970,11 +15598,21 @@
       <c r="J97" s="5"/>
     </row>
     <row r="98" spans="1:10" ht="42" customHeight="1">
-      <c r="A98" s="4"/>
-      <c r="B98" s="7"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
+      <c r="A98" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B98" s="8">
+        <v>2</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>1153</v>
+      </c>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
@@ -13982,23 +15620,45 @@
       <c r="J98" s="5"/>
     </row>
     <row r="99" spans="1:10" ht="42" customHeight="1">
-      <c r="A99" s="4"/>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
+      <c r="A99" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B99" s="8">
+        <v>2</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>1151</v>
+      </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
     </row>
     <row r="100" spans="1:10" ht="42" customHeight="1">
-      <c r="A100" s="4"/>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
+      <c r="A100" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B100" s="8">
+        <v>2</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>1140</v>
+      </c>
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
@@ -14006,11 +15666,21 @@
       <c r="J100" s="5"/>
     </row>
     <row r="101" spans="1:10" ht="42" customHeight="1">
-      <c r="A101" s="4"/>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
+      <c r="A101" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B101" s="8">
+        <v>2</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>1176</v>
+      </c>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
@@ -14018,83 +15688,165 @@
       <c r="J101" s="5"/>
     </row>
     <row r="102" spans="1:10" ht="42" customHeight="1">
-      <c r="A102" s="4"/>
-      <c r="B102" s="7"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
+      <c r="A102" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B102" s="8">
+        <v>2</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>880</v>
+      </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
       <c r="I102" s="5"/>
       <c r="J102" s="5"/>
     </row>
     <row r="103" spans="1:10" ht="42" customHeight="1">
-      <c r="A103" s="4"/>
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
+      <c r="A103" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B103" s="8">
+        <v>2</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>882</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>883</v>
+      </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
     </row>
     <row r="104" spans="1:10" ht="42" customHeight="1">
-      <c r="A104" s="4"/>
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
+      <c r="A104" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B104" s="8">
+        <v>2</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>902</v>
+      </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
     </row>
     <row r="105" spans="1:10" ht="42" customHeight="1">
-      <c r="A105" s="4"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
+      <c r="A105" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B105" s="8">
+        <v>2</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>1280</v>
+      </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
     </row>
     <row r="106" spans="1:10" ht="42" customHeight="1">
-      <c r="A106" s="4"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
+      <c r="A106" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B106" s="8">
+        <v>2</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>1101</v>
+      </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
     </row>
     <row r="107" spans="1:10" ht="42" customHeight="1">
-      <c r="A107" s="4"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
+      <c r="A107" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B107" s="8">
+        <v>2</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>1138</v>
+      </c>
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
     </row>
     <row r="108" spans="1:10" ht="42" customHeight="1">
-      <c r="A108" s="4"/>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
+      <c r="A108" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B108" s="8">
+        <v>2</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>1472</v>
+      </c>
       <c r="F108" s="5"/>
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
@@ -14102,71 +15854,149 @@
       <c r="J108" s="5"/>
     </row>
     <row r="109" spans="1:10" ht="42" customHeight="1">
-      <c r="A109" s="4"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
+      <c r="A109" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B109" s="8">
+        <v>2</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>957</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>958</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>959</v>
+      </c>
       <c r="H109" s="5"/>
       <c r="I109" s="5"/>
       <c r="J109" s="5"/>
     </row>
     <row r="110" spans="1:10" ht="42" customHeight="1">
-      <c r="A110" s="4"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
+      <c r="A110" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B110" s="8">
+        <v>2</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>1273</v>
+      </c>
       <c r="H110" s="5"/>
       <c r="I110" s="5"/>
       <c r="J110" s="5"/>
     </row>
     <row r="111" spans="1:10" ht="42" customHeight="1">
-      <c r="A111" s="4"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="5"/>
-      <c r="H111" s="5"/>
+      <c r="A111" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B111" s="8">
+        <v>2</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>1171</v>
+      </c>
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
     </row>
     <row r="112" spans="1:10" ht="42" customHeight="1">
-      <c r="A112" s="4"/>
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
+      <c r="A112" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B112" s="8">
+        <v>2</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>1148</v>
+      </c>
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="5"/>
       <c r="J112" s="5"/>
     </row>
     <row r="113" spans="1:10" ht="42" customHeight="1">
-      <c r="A113" s="4"/>
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
+      <c r="A113" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B113" s="8">
+        <v>2</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>1221</v>
+      </c>
       <c r="G113" s="5"/>
       <c r="H113" s="5"/>
       <c r="I113" s="5"/>
       <c r="J113" s="5"/>
     </row>
     <row r="114" spans="1:10" ht="42" customHeight="1">
-      <c r="A114" s="4"/>
-      <c r="B114" s="7"/>
-      <c r="C114" s="8"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
+      <c r="A114" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B114" s="8">
+        <v>2</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>877</v>
+      </c>
       <c r="F114" s="5"/>
       <c r="G114" s="5"/>
       <c r="H114" s="5"/>
@@ -14174,35 +16004,69 @@
       <c r="J114" s="5"/>
     </row>
     <row r="115" spans="1:10" ht="42" customHeight="1">
-      <c r="A115" s="4"/>
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
+      <c r="A115" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B115" s="8">
+        <v>2</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>975</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>977</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>978</v>
+      </c>
       <c r="G115" s="5"/>
       <c r="H115" s="5"/>
       <c r="I115" s="5"/>
       <c r="J115" s="5"/>
     </row>
     <row r="116" spans="1:10" ht="42" customHeight="1">
-      <c r="A116" s="4"/>
-      <c r="B116" s="8"/>
-      <c r="C116" s="8"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
+      <c r="A116" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B116" s="8">
+        <v>2</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>980</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>979</v>
+      </c>
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" s="5"/>
       <c r="J116" s="5"/>
     </row>
     <row r="117" spans="1:10" ht="42" customHeight="1">
-      <c r="A117" s="4"/>
-      <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
+      <c r="A117" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B117" s="8">
+        <v>2</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>971</v>
+      </c>
       <c r="F117" s="5"/>
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
@@ -14210,11 +16074,21 @@
       <c r="J117" s="5"/>
     </row>
     <row r="118" spans="1:10" ht="42" customHeight="1">
-      <c r="A118" s="4"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="8"/>
-      <c r="D118" s="5"/>
-      <c r="E118" s="5"/>
+      <c r="A118" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B118" s="8">
+        <v>2</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>970</v>
+      </c>
       <c r="F118" s="5"/>
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
@@ -14222,11 +16096,21 @@
       <c r="J118" s="5"/>
     </row>
     <row r="119" spans="1:10" ht="42" customHeight="1">
-      <c r="A119" s="4"/>
-      <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
+      <c r="A119" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B119" s="8">
+        <v>2</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>886</v>
+      </c>
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
@@ -14234,11 +16118,21 @@
       <c r="J119" s="5"/>
     </row>
     <row r="120" spans="1:10" ht="42" customHeight="1">
-      <c r="A120" s="4"/>
-      <c r="B120" s="8"/>
-      <c r="C120" s="8"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
+      <c r="A120" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B120" s="8">
+        <v>2</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>1256</v>
+      </c>
       <c r="F120" s="5"/>
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
@@ -14246,59 +16140,119 @@
       <c r="J120" s="5"/>
     </row>
     <row r="121" spans="1:10" ht="42" customHeight="1">
-      <c r="A121" s="4"/>
-      <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
+      <c r="A121" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B121" s="8">
+        <v>2</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>1119</v>
+      </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
     </row>
     <row r="122" spans="1:10" ht="42" customHeight="1">
-      <c r="A122" s="4"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
+      <c r="A122" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B122" s="8">
+        <v>2</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>1159</v>
+      </c>
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
     </row>
     <row r="123" spans="1:10" ht="42" customHeight="1">
-      <c r="A123" s="4"/>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="5"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="5"/>
+      <c r="A123" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B123" s="8">
+        <v>2</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>1196</v>
+      </c>
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
     </row>
     <row r="124" spans="1:10" ht="42" customHeight="1">
-      <c r="A124" s="4"/>
-      <c r="B124" s="8"/>
-      <c r="C124" s="8"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="5"/>
+      <c r="A124" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B124" s="8">
+        <v>2</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>1111</v>
+      </c>
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
     </row>
     <row r="125" spans="1:10" ht="42" customHeight="1">
-      <c r="A125" s="4"/>
-      <c r="B125" s="8"/>
-      <c r="C125" s="8"/>
-      <c r="D125" s="5"/>
-      <c r="E125" s="5"/>
+      <c r="A125" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B125" s="7">
+        <v>2</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>892</v>
+      </c>
       <c r="F125" s="5"/>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
@@ -14306,11 +16260,21 @@
       <c r="J125" s="5"/>
     </row>
     <row r="126" spans="1:10" ht="42" customHeight="1">
-      <c r="A126" s="4"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="8"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
+      <c r="A126" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B126" s="8">
+        <v>2</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>891</v>
+      </c>
       <c r="F126" s="5"/>
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
@@ -14318,83 +16282,177 @@
       <c r="J126" s="5"/>
     </row>
     <row r="127" spans="1:10" ht="42" customHeight="1">
-      <c r="A127" s="4"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="8"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
+      <c r="A127" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B127" s="8">
+        <v>2</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>931</v>
+      </c>
       <c r="H127" s="5"/>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
     </row>
     <row r="128" spans="1:10" ht="42" customHeight="1">
-      <c r="A128" s="4"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="8"/>
-      <c r="D128" s="5"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="5"/>
+      <c r="A128" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B128" s="8">
+        <v>2</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>895</v>
+      </c>
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
     </row>
     <row r="129" spans="1:10" ht="42" customHeight="1">
-      <c r="A129" s="4"/>
-      <c r="B129" s="7"/>
-      <c r="C129" s="8"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
+      <c r="A129" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B129" s="8">
+        <v>2</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>972</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>974</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>973</v>
+      </c>
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
     </row>
     <row r="130" spans="1:10" ht="42" customHeight="1">
-      <c r="A130" s="4"/>
-      <c r="B130" s="7"/>
-      <c r="C130" s="8"/>
-      <c r="D130" s="5"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="5"/>
-      <c r="G130" s="5"/>
-      <c r="H130" s="5"/>
+      <c r="A130" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>992</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H130" s="5" t="s">
+        <v>1039</v>
+      </c>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
     </row>
     <row r="131" spans="1:10" ht="42" customHeight="1">
-      <c r="A131" s="4"/>
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
-      <c r="D131" s="5"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="5"/>
-      <c r="G131" s="5"/>
-      <c r="H131" s="5"/>
+      <c r="A131" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B131" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H131" s="5" t="s">
+        <v>1045</v>
+      </c>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
     </row>
     <row r="132" spans="1:10" ht="42" customHeight="1">
-      <c r="A132" s="4"/>
-      <c r="B132" s="8"/>
-      <c r="C132" s="8"/>
-      <c r="D132" s="5"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="5"/>
-      <c r="G132" s="5"/>
+      <c r="A132" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>1049</v>
+      </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
     </row>
     <row r="133" spans="1:10" ht="42" customHeight="1">
-      <c r="A133" s="4"/>
-      <c r="B133" s="8"/>
-      <c r="C133" s="8"/>
-      <c r="D133" s="5"/>
-      <c r="E133" s="5"/>
+      <c r="A133" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B133" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>1155</v>
+      </c>
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
@@ -14402,23 +16460,47 @@
       <c r="J133" s="5"/>
     </row>
     <row r="134" spans="1:10" ht="42" customHeight="1">
-      <c r="A134" s="4"/>
-      <c r="B134" s="7"/>
-      <c r="C134" s="8"/>
-      <c r="D134" s="5"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="5"/>
-      <c r="G134" s="5"/>
+      <c r="A134" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B134" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>1057</v>
+      </c>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
     </row>
     <row r="135" spans="1:10" ht="42" customHeight="1">
-      <c r="A135" s="4"/>
-      <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
-      <c r="D135" s="5"/>
-      <c r="E135" s="5"/>
+      <c r="A135" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B135" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>562</v>
+      </c>
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
@@ -14426,11 +16508,21 @@
       <c r="J135" s="5"/>
     </row>
     <row r="136" spans="1:10" ht="42" customHeight="1">
-      <c r="A136" s="4"/>
-      <c r="B136" s="8"/>
-      <c r="C136" s="8"/>
-      <c r="D136" s="5"/>
-      <c r="E136" s="5"/>
+      <c r="A136" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>565</v>
+      </c>
       <c r="F136" s="5"/>
       <c r="G136" s="5"/>
       <c r="H136" s="5"/>
@@ -14438,35 +16530,75 @@
       <c r="J136" s="5"/>
     </row>
     <row r="137" spans="1:10" ht="42" customHeight="1">
-      <c r="A137" s="4"/>
-      <c r="B137" s="8"/>
-      <c r="C137" s="8"/>
-      <c r="D137" s="5"/>
-      <c r="E137" s="5"/>
-      <c r="F137" s="5"/>
+      <c r="A137" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B137" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>569</v>
+      </c>
       <c r="G137" s="5"/>
       <c r="H137" s="5"/>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
     </row>
     <row r="138" spans="1:10" ht="42" customHeight="1">
-      <c r="A138" s="4"/>
-      <c r="B138" s="7"/>
-      <c r="C138" s="8"/>
-      <c r="D138" s="5"/>
-      <c r="E138" s="5"/>
-      <c r="F138" s="5"/>
-      <c r="G138" s="5"/>
-      <c r="H138" s="5"/>
-      <c r="I138" s="5"/>
+      <c r="A138" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>996</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="I138" s="5" t="s">
+        <v>1000</v>
+      </c>
       <c r="J138" s="5"/>
     </row>
     <row r="139" spans="1:10" ht="42" customHeight="1">
-      <c r="A139" s="4"/>
-      <c r="B139" s="8"/>
-      <c r="C139" s="8"/>
-      <c r="D139" s="5"/>
-      <c r="E139" s="5"/>
+      <c r="A139" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B139" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>1002</v>
+      </c>
       <c r="F139" s="5"/>
       <c r="G139" s="5"/>
       <c r="H139" s="5"/>
@@ -14474,23 +16606,45 @@
       <c r="J139" s="5"/>
     </row>
     <row r="140" spans="1:10" ht="42" customHeight="1">
-      <c r="A140" s="4"/>
-      <c r="B140" s="8"/>
-      <c r="C140" s="8"/>
-      <c r="D140" s="5"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="5"/>
+      <c r="A140" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>1100</v>
+      </c>
       <c r="G140" s="5"/>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
       <c r="J140" s="5"/>
     </row>
     <row r="141" spans="1:10" ht="42" customHeight="1">
-      <c r="A141" s="4"/>
-      <c r="B141" s="8"/>
-      <c r="C141" s="8"/>
-      <c r="D141" s="5"/>
-      <c r="E141" s="5"/>
+      <c r="A141" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B141" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>1007</v>
+      </c>
       <c r="F141" s="5"/>
       <c r="G141" s="5"/>
       <c r="H141" s="5"/>
@@ -14498,11 +16652,21 @@
       <c r="J141" s="5"/>
     </row>
     <row r="142" spans="1:10" ht="42" customHeight="1">
-      <c r="A142" s="4"/>
-      <c r="B142" s="7"/>
-      <c r="C142" s="8"/>
-      <c r="D142" s="5"/>
-      <c r="E142" s="5"/>
+      <c r="A142" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B142" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>1008</v>
+      </c>
       <c r="F142" s="5"/>
       <c r="G142" s="5"/>
       <c r="H142" s="5"/>
@@ -14510,11 +16674,21 @@
       <c r="J142" s="5"/>
     </row>
     <row r="143" spans="1:10" ht="42" customHeight="1">
-      <c r="A143" s="4"/>
-      <c r="B143" s="8"/>
-      <c r="C143" s="8"/>
-      <c r="D143" s="5"/>
-      <c r="E143" s="5"/>
+      <c r="A143" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B143" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>1010</v>
+      </c>
       <c r="F143" s="5"/>
       <c r="G143" s="5"/>
       <c r="H143" s="5"/>
@@ -14522,59 +16696,121 @@
       <c r="J143" s="5"/>
     </row>
     <row r="144" spans="1:10" ht="42" customHeight="1">
-      <c r="A144" s="4"/>
-      <c r="B144" s="8"/>
-      <c r="C144" s="8"/>
-      <c r="D144" s="5"/>
-      <c r="E144" s="5"/>
-      <c r="F144" s="5"/>
-      <c r="G144" s="5"/>
-      <c r="H144" s="5"/>
+      <c r="A144" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H144" s="5" t="s">
+        <v>1015</v>
+      </c>
       <c r="I144" s="5"/>
       <c r="J144" s="5"/>
     </row>
     <row r="145" spans="1:10" ht="42" customHeight="1">
-      <c r="A145" s="4"/>
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
-      <c r="D145" s="5"/>
-      <c r="E145" s="5"/>
-      <c r="F145" s="5"/>
+      <c r="A145" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B145" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>1017</v>
+      </c>
       <c r="G145" s="5"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
     </row>
     <row r="146" spans="1:10" ht="42" customHeight="1">
-      <c r="A146" s="4"/>
-      <c r="B146" s="8"/>
-      <c r="C146" s="8"/>
-      <c r="D146" s="5"/>
-      <c r="E146" s="5"/>
-      <c r="F146" s="5"/>
+      <c r="A146" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B146" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>1021</v>
+      </c>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
       <c r="I146" s="5"/>
       <c r="J146" s="5"/>
     </row>
     <row r="147" spans="1:10" ht="42" customHeight="1">
-      <c r="A147" s="4"/>
-      <c r="B147" s="8"/>
-      <c r="C147" s="8"/>
-      <c r="D147" s="5"/>
-      <c r="E147" s="5"/>
-      <c r="F147" s="5"/>
+      <c r="A147" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B147" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>1025</v>
+      </c>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
       <c r="J147" s="5"/>
     </row>
     <row r="148" spans="1:10" ht="42" customHeight="1">
-      <c r="A148" s="4"/>
-      <c r="B148" s="7"/>
-      <c r="C148" s="8"/>
-      <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
+      <c r="A148" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>1026</v>
+      </c>
       <c r="F148" s="5"/>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
@@ -14582,95 +16818,201 @@
       <c r="J148" s="5"/>
     </row>
     <row r="149" spans="1:10" ht="42" customHeight="1">
-      <c r="A149" s="4"/>
-      <c r="B149" s="8"/>
-      <c r="C149" s="8"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="5"/>
-      <c r="G149" s="5"/>
-      <c r="H149" s="5"/>
+      <c r="A149" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B149" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>1031</v>
+      </c>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
     </row>
     <row r="150" spans="1:10" ht="42" customHeight="1">
-      <c r="A150" s="4"/>
-      <c r="B150" s="8"/>
-      <c r="C150" s="8"/>
-      <c r="D150" s="5"/>
-      <c r="E150" s="5"/>
-      <c r="F150" s="5"/>
-      <c r="G150" s="5"/>
+      <c r="A150" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B150" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>1035</v>
+      </c>
       <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
     </row>
     <row r="151" spans="1:10" ht="42" customHeight="1">
-      <c r="A151" s="4"/>
-      <c r="B151" s="8"/>
-      <c r="C151" s="8"/>
-      <c r="D151" s="5"/>
-      <c r="E151" s="5"/>
-      <c r="F151" s="5"/>
+      <c r="A151" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>1060</v>
+      </c>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
     </row>
     <row r="152" spans="1:10" ht="42" customHeight="1">
-      <c r="A152" s="4"/>
-      <c r="B152" s="7"/>
-      <c r="C152" s="8"/>
-      <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
+      <c r="A152" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B152" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>1063</v>
+      </c>
       <c r="G152" s="5"/>
       <c r="H152" s="5"/>
       <c r="I152" s="5"/>
       <c r="J152" s="5"/>
     </row>
     <row r="153" spans="1:10" ht="42" customHeight="1">
-      <c r="A153" s="4"/>
-      <c r="B153" s="8"/>
-      <c r="C153" s="8"/>
-      <c r="D153" s="5"/>
-      <c r="E153" s="5"/>
-      <c r="F153" s="5"/>
-      <c r="G153" s="5"/>
+      <c r="A153" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>1067</v>
+      </c>
       <c r="H153" s="5"/>
       <c r="I153" s="5"/>
       <c r="J153" s="5"/>
     </row>
     <row r="154" spans="1:10" ht="42" customHeight="1">
-      <c r="A154" s="4"/>
-      <c r="B154" s="8"/>
-      <c r="C154" s="8"/>
-      <c r="D154" s="5"/>
-      <c r="E154" s="5"/>
-      <c r="F154" s="5"/>
+      <c r="A154" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>1069</v>
+      </c>
       <c r="G154" s="5"/>
       <c r="H154" s="5"/>
       <c r="I154" s="5"/>
       <c r="J154" s="5"/>
     </row>
     <row r="155" spans="1:10" ht="42" customHeight="1">
-      <c r="A155" s="4"/>
-      <c r="B155" s="8"/>
-      <c r="C155" s="8"/>
-      <c r="D155" s="5"/>
-      <c r="E155" s="5"/>
-      <c r="F155" s="5"/>
-      <c r="G155" s="5"/>
-      <c r="H155" s="5"/>
+      <c r="A155" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B155" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>1228</v>
+      </c>
       <c r="I155" s="5"/>
       <c r="J155" s="5"/>
     </row>
     <row r="156" spans="1:10" ht="42" customHeight="1">
-      <c r="A156" s="4"/>
-      <c r="B156" s="7"/>
-      <c r="C156" s="8"/>
-      <c r="D156" s="5"/>
-      <c r="E156" s="5"/>
+      <c r="A156" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>1072</v>
+      </c>
       <c r="F156" s="5"/>
       <c r="G156" s="5"/>
       <c r="H156" s="5"/>
@@ -14678,72 +17020,160 @@
       <c r="J156" s="5"/>
     </row>
     <row r="157" spans="1:10" ht="42" customHeight="1">
-      <c r="A157" s="4"/>
-      <c r="B157" s="8"/>
-      <c r="C157" s="8"/>
-      <c r="D157" s="5"/>
-      <c r="E157" s="5"/>
-      <c r="F157" s="5"/>
-      <c r="G157" s="5"/>
+      <c r="A157" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B157" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>1076</v>
+      </c>
       <c r="H157" s="5"/>
       <c r="I157" s="5"/>
       <c r="J157" s="5"/>
     </row>
     <row r="158" spans="1:10" ht="42" customHeight="1">
-      <c r="A158" s="4"/>
-      <c r="B158" s="8"/>
-      <c r="C158" s="8"/>
-      <c r="D158" s="5"/>
-      <c r="E158" s="5"/>
-      <c r="F158" s="5"/>
+      <c r="A158" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>1079</v>
+      </c>
       <c r="G158" s="5"/>
       <c r="H158" s="5"/>
       <c r="I158" s="5"/>
       <c r="J158" s="5"/>
     </row>
     <row r="159" spans="1:10" ht="42" customHeight="1">
-      <c r="A159" s="4"/>
-      <c r="B159" s="8"/>
-      <c r="C159" s="8"/>
-      <c r="D159" s="5"/>
-      <c r="E159" s="5"/>
-      <c r="F159" s="5"/>
-      <c r="G159" s="5"/>
-      <c r="H159" s="5"/>
+      <c r="A159" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B159" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>1084</v>
+      </c>
       <c r="I159" s="5"/>
       <c r="J159" s="5"/>
     </row>
     <row r="160" spans="1:10" ht="42" customHeight="1">
-      <c r="A160" s="4"/>
-      <c r="B160" s="8"/>
-      <c r="C160" s="8"/>
-      <c r="D160" s="5"/>
-      <c r="E160" s="5"/>
-      <c r="F160" s="5"/>
-      <c r="G160" s="5"/>
-      <c r="H160" s="5"/>
+      <c r="A160" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>1084</v>
+      </c>
       <c r="I160" s="5"/>
       <c r="J160" s="5"/>
     </row>
     <row r="161" spans="1:10" ht="42" customHeight="1">
-      <c r="A161" s="4"/>
-      <c r="B161" s="8"/>
-      <c r="C161" s="8"/>
-      <c r="D161" s="5"/>
-      <c r="E161" s="5"/>
-      <c r="F161" s="5"/>
-      <c r="G161" s="5"/>
-      <c r="H161" s="5"/>
-      <c r="I161" s="5"/>
+      <c r="A161" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B161" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>1093</v>
+      </c>
+      <c r="I161" s="5" t="s">
+        <v>1094</v>
+      </c>
       <c r="J161" s="5"/>
     </row>
     <row r="162" spans="1:10" ht="42" customHeight="1">
-      <c r="A162" s="4"/>
-      <c r="B162" s="8"/>
-      <c r="C162" s="8"/>
-      <c r="D162" s="5"/>
-      <c r="E162" s="5"/>
-      <c r="F162" s="5"/>
+      <c r="A162" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>1097</v>
+      </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
@@ -14763,7 +17193,7 @@
     </row>
     <row r="164" spans="1:10" ht="42" customHeight="1">
       <c r="A164" s="4"/>
-      <c r="B164" s="8"/>
+      <c r="B164" s="7"/>
       <c r="C164" s="8"/>
       <c r="D164" s="5"/>
       <c r="E164" s="5"/>
@@ -14775,7 +17205,7 @@
     </row>
     <row r="165" spans="1:10" ht="42" customHeight="1">
       <c r="A165" s="4"/>
-      <c r="B165" s="7"/>
+      <c r="B165" s="8"/>
       <c r="C165" s="8"/>
       <c r="D165" s="5"/>
       <c r="E165" s="5"/>
@@ -14799,7 +17229,7 @@
     </row>
     <row r="167" spans="1:10" ht="42" customHeight="1">
       <c r="A167" s="4"/>
-      <c r="B167" s="8"/>
+      <c r="B167" s="7"/>
       <c r="C167" s="8"/>
       <c r="D167" s="5"/>
       <c r="E167" s="5"/>
@@ -14823,7 +17253,7 @@
     </row>
     <row r="169" spans="1:10" ht="42" customHeight="1">
       <c r="A169" s="4"/>
-      <c r="B169" s="7"/>
+      <c r="B169" s="8"/>
       <c r="C169" s="8"/>
       <c r="D169" s="5"/>
       <c r="E169" s="5"/>
@@ -14847,7 +17277,7 @@
     </row>
     <row r="171" spans="1:10" ht="42" customHeight="1">
       <c r="A171" s="4"/>
-      <c r="B171" s="8"/>
+      <c r="B171" s="7"/>
       <c r="C171" s="8"/>
       <c r="D171" s="5"/>
       <c r="E171" s="5"/>
@@ -14871,7 +17301,7 @@
     </row>
     <row r="173" spans="1:10" ht="42" customHeight="1">
       <c r="A173" s="4"/>
-      <c r="B173" s="7"/>
+      <c r="B173" s="8"/>
       <c r="C173" s="8"/>
       <c r="D173" s="5"/>
       <c r="E173" s="5"/>
@@ -14895,7 +17325,7 @@
     </row>
     <row r="175" spans="1:10" ht="42" customHeight="1">
       <c r="A175" s="4"/>
-      <c r="B175" s="8"/>
+      <c r="B175" s="7"/>
       <c r="C175" s="8"/>
       <c r="D175" s="5"/>
       <c r="E175" s="5"/>
@@ -14919,7 +17349,7 @@
     </row>
     <row r="177" spans="1:10" ht="42" customHeight="1">
       <c r="A177" s="4"/>
-      <c r="B177" s="7"/>
+      <c r="B177" s="8"/>
       <c r="C177" s="8"/>
       <c r="D177" s="5"/>
       <c r="E177" s="5"/>
@@ -14943,7 +17373,7 @@
     </row>
     <row r="179" spans="1:10" ht="42" customHeight="1">
       <c r="A179" s="4"/>
-      <c r="B179" s="8"/>
+      <c r="B179" s="7"/>
       <c r="C179" s="8"/>
       <c r="D179" s="5"/>
       <c r="E179" s="5"/>
@@ -14967,7 +17397,7 @@
     </row>
     <row r="181" spans="1:10" ht="42" customHeight="1">
       <c r="A181" s="4"/>
-      <c r="B181" s="7"/>
+      <c r="B181" s="8"/>
       <c r="C181" s="8"/>
       <c r="D181" s="5"/>
       <c r="E181" s="5"/>
@@ -14991,7 +17421,7 @@
     </row>
     <row r="183" spans="1:10" ht="42" customHeight="1">
       <c r="A183" s="4"/>
-      <c r="B183" s="8"/>
+      <c r="B183" s="7"/>
       <c r="C183" s="8"/>
       <c r="D183" s="5"/>
       <c r="E183" s="5"/>
@@ -15015,7 +17445,7 @@
     </row>
     <row r="185" spans="1:10" ht="42" customHeight="1">
       <c r="A185" s="4"/>
-      <c r="B185" s="7"/>
+      <c r="B185" s="8"/>
       <c r="C185" s="8"/>
       <c r="D185" s="5"/>
       <c r="E185" s="5"/>
@@ -15027,7 +17457,7 @@
     </row>
     <row r="186" spans="1:10" ht="42" customHeight="1">
       <c r="A186" s="4"/>
-      <c r="B186" s="7"/>
+      <c r="B186" s="8"/>
       <c r="C186" s="8"/>
       <c r="D186" s="5"/>
       <c r="E186" s="5"/>
@@ -15039,7 +17469,7 @@
     </row>
     <row r="187" spans="1:10" ht="42" customHeight="1">
       <c r="A187" s="4"/>
-      <c r="B187" s="8"/>
+      <c r="B187" s="7"/>
       <c r="C187" s="8"/>
       <c r="D187" s="5"/>
       <c r="E187" s="5"/>
@@ -15063,7 +17493,7 @@
     </row>
     <row r="189" spans="1:10" ht="42" customHeight="1">
       <c r="A189" s="4"/>
-      <c r="B189" s="7"/>
+      <c r="B189" s="8"/>
       <c r="C189" s="8"/>
       <c r="D189" s="5"/>
       <c r="E189" s="5"/>
@@ -15075,7 +17505,7 @@
     </row>
     <row r="190" spans="1:10" ht="42" customHeight="1">
       <c r="A190" s="4"/>
-      <c r="B190" s="7"/>
+      <c r="B190" s="8"/>
       <c r="C190" s="8"/>
       <c r="D190" s="5"/>
       <c r="E190" s="5"/>
@@ -15195,7 +17625,7 @@
     </row>
     <row r="200" spans="1:10" ht="42" customHeight="1">
       <c r="A200" s="4"/>
-      <c r="B200" s="8"/>
+      <c r="B200" s="7"/>
       <c r="C200" s="8"/>
       <c r="D200" s="5"/>
       <c r="E200" s="5"/>
@@ -15219,7 +17649,7 @@
     </row>
     <row r="202" spans="1:10" ht="42" customHeight="1">
       <c r="A202" s="4"/>
-      <c r="B202" s="8"/>
+      <c r="B202" s="7"/>
       <c r="C202" s="8"/>
       <c r="D202" s="5"/>
       <c r="E202" s="5"/>
@@ -15231,7 +17661,7 @@
     </row>
     <row r="203" spans="1:10" ht="42" customHeight="1">
       <c r="A203" s="4"/>
-      <c r="B203" s="8"/>
+      <c r="B203" s="7"/>
       <c r="C203" s="8"/>
       <c r="D203" s="5"/>
       <c r="E203" s="5"/>
@@ -15255,7 +17685,7 @@
     </row>
     <row r="205" spans="1:10" ht="42" customHeight="1">
       <c r="A205" s="4"/>
-      <c r="B205" s="7"/>
+      <c r="B205" s="8"/>
       <c r="C205" s="8"/>
       <c r="D205" s="5"/>
       <c r="E205" s="5"/>
@@ -15279,7 +17709,7 @@
     </row>
     <row r="207" spans="1:10" ht="42" customHeight="1">
       <c r="A207" s="4"/>
-      <c r="B207" s="8"/>
+      <c r="B207" s="7"/>
       <c r="C207" s="8"/>
       <c r="D207" s="5"/>
       <c r="E207" s="5"/>
@@ -15303,7 +17733,7 @@
     </row>
     <row r="209" spans="1:10" ht="42" customHeight="1">
       <c r="A209" s="4"/>
-      <c r="B209" s="7"/>
+      <c r="B209" s="8"/>
       <c r="C209" s="8"/>
       <c r="D209" s="5"/>
       <c r="E209" s="5"/>
@@ -15327,7 +17757,7 @@
     </row>
     <row r="211" spans="1:10" ht="42" customHeight="1">
       <c r="A211" s="4"/>
-      <c r="B211" s="8"/>
+      <c r="B211" s="7"/>
       <c r="C211" s="8"/>
       <c r="D211" s="5"/>
       <c r="E211" s="5"/>
@@ -15375,9 +17805,9 @@
     </row>
     <row r="215" spans="1:10" ht="42" customHeight="1">
       <c r="A215" s="4"/>
-      <c r="B215" s="8"/>
+      <c r="B215" s="7"/>
       <c r="C215" s="8"/>
-      <c r="D215" s="10"/>
+      <c r="D215" s="5"/>
       <c r="E215" s="5"/>
       <c r="F215" s="5"/>
       <c r="G215" s="5"/>
@@ -15389,7 +17819,7 @@
       <c r="A216" s="4"/>
       <c r="B216" s="8"/>
       <c r="C216" s="8"/>
-      <c r="D216" s="10"/>
+      <c r="D216" s="5"/>
       <c r="E216" s="5"/>
       <c r="F216" s="5"/>
       <c r="G216" s="5"/>
@@ -15401,7 +17831,7 @@
       <c r="A217" s="4"/>
       <c r="B217" s="8"/>
       <c r="C217" s="8"/>
-      <c r="D217" s="10"/>
+      <c r="D217" s="5"/>
       <c r="E217" s="5"/>
       <c r="F217" s="5"/>
       <c r="G217" s="5"/>
@@ -15413,7 +17843,7 @@
       <c r="A218" s="4"/>
       <c r="B218" s="8"/>
       <c r="C218" s="8"/>
-      <c r="D218" s="10"/>
+      <c r="D218" s="5"/>
       <c r="E218" s="5"/>
       <c r="F218" s="5"/>
       <c r="G218" s="5"/>
@@ -15425,7 +17855,7 @@
       <c r="A219" s="4"/>
       <c r="B219" s="8"/>
       <c r="C219" s="8"/>
-      <c r="D219" s="10"/>
+      <c r="D219" s="5"/>
       <c r="E219" s="5"/>
       <c r="F219" s="5"/>
       <c r="G219" s="5"/>
@@ -15447,7 +17877,7 @@
     </row>
     <row r="221" spans="1:10" ht="42" customHeight="1">
       <c r="A221" s="4"/>
-      <c r="B221" s="8"/>
+      <c r="B221" s="7"/>
       <c r="C221" s="8"/>
       <c r="D221" s="5"/>
       <c r="E221" s="5"/>
@@ -15459,7 +17889,7 @@
     </row>
     <row r="222" spans="1:10" ht="42" customHeight="1">
       <c r="A222" s="4"/>
-      <c r="B222" s="7"/>
+      <c r="B222" s="8"/>
       <c r="C222" s="8"/>
       <c r="D222" s="5"/>
       <c r="E222" s="5"/>
@@ -15495,7 +17925,7 @@
     </row>
     <row r="225" spans="1:10" ht="42" customHeight="1">
       <c r="A225" s="4"/>
-      <c r="B225" s="8"/>
+      <c r="B225" s="7"/>
       <c r="C225" s="8"/>
       <c r="D225" s="5"/>
       <c r="E225" s="5"/>
@@ -15507,7 +17937,7 @@
     </row>
     <row r="226" spans="1:10" ht="42" customHeight="1">
       <c r="A226" s="4"/>
-      <c r="B226" s="7"/>
+      <c r="B226" s="8"/>
       <c r="C226" s="8"/>
       <c r="D226" s="5"/>
       <c r="E226" s="5"/>
@@ -15543,7 +17973,7 @@
     </row>
     <row r="229" spans="1:10" ht="42" customHeight="1">
       <c r="A229" s="4"/>
-      <c r="B229" s="8"/>
+      <c r="B229" s="7"/>
       <c r="C229" s="8"/>
       <c r="D229" s="5"/>
       <c r="E229" s="5"/>
@@ -15555,7 +17985,7 @@
     </row>
     <row r="230" spans="1:10" ht="42" customHeight="1">
       <c r="A230" s="4"/>
-      <c r="B230" s="7"/>
+      <c r="B230" s="8"/>
       <c r="C230" s="8"/>
       <c r="D230" s="5"/>
       <c r="E230" s="5"/>
@@ -15603,7 +18033,7 @@
     </row>
     <row r="234" spans="1:10" ht="42" customHeight="1">
       <c r="A234" s="4"/>
-      <c r="B234" s="7"/>
+      <c r="B234" s="8"/>
       <c r="C234" s="8"/>
       <c r="D234" s="5"/>
       <c r="E234" s="5"/>
@@ -15615,7 +18045,7 @@
     </row>
     <row r="235" spans="1:10" ht="42" customHeight="1">
       <c r="A235" s="4"/>
-      <c r="B235" s="7"/>
+      <c r="B235" s="8"/>
       <c r="C235" s="8"/>
       <c r="D235" s="5"/>
       <c r="E235" s="5"/>
@@ -15651,7 +18081,7 @@
     </row>
     <row r="238" spans="1:10" ht="42" customHeight="1">
       <c r="A238" s="4"/>
-      <c r="B238" s="8"/>
+      <c r="B238" s="7"/>
       <c r="C238" s="8"/>
       <c r="D238" s="5"/>
       <c r="E238" s="5"/>
@@ -15663,7 +18093,7 @@
     </row>
     <row r="239" spans="1:10" ht="42" customHeight="1">
       <c r="A239" s="4"/>
-      <c r="B239" s="7"/>
+      <c r="B239" s="8"/>
       <c r="C239" s="8"/>
       <c r="D239" s="5"/>
       <c r="E239" s="5"/>
@@ -15699,7 +18129,7 @@
     </row>
     <row r="242" spans="1:10" ht="42" customHeight="1">
       <c r="A242" s="4"/>
-      <c r="B242" s="8"/>
+      <c r="B242" s="7"/>
       <c r="C242" s="8"/>
       <c r="D242" s="5"/>
       <c r="E242" s="5"/>
@@ -15711,7 +18141,7 @@
     </row>
     <row r="243" spans="1:10" ht="42" customHeight="1">
       <c r="A243" s="4"/>
-      <c r="B243" s="7"/>
+      <c r="B243" s="8"/>
       <c r="C243" s="8"/>
       <c r="D243" s="5"/>
       <c r="E243" s="5"/>
@@ -15747,7 +18177,7 @@
     </row>
     <row r="246" spans="1:10" ht="42" customHeight="1">
       <c r="A246" s="4"/>
-      <c r="B246" s="8"/>
+      <c r="B246" s="7"/>
       <c r="C246" s="8"/>
       <c r="D246" s="5"/>
       <c r="E246" s="5"/>
@@ -15759,7 +18189,7 @@
     </row>
     <row r="247" spans="1:10" ht="42" customHeight="1">
       <c r="A247" s="4"/>
-      <c r="B247" s="7"/>
+      <c r="B247" s="8"/>
       <c r="C247" s="8"/>
       <c r="D247" s="5"/>
       <c r="E247" s="5"/>
@@ -15795,7 +18225,7 @@
     </row>
     <row r="250" spans="1:10" ht="42" customHeight="1">
       <c r="A250" s="4"/>
-      <c r="B250" s="8"/>
+      <c r="B250" s="7"/>
       <c r="C250" s="8"/>
       <c r="D250" s="5"/>
       <c r="E250" s="5"/>
@@ -15843,7 +18273,7 @@
     </row>
     <row r="254" spans="1:10" ht="42" customHeight="1">
       <c r="A254" s="4"/>
-      <c r="B254" s="8"/>
+      <c r="B254" s="7"/>
       <c r="C254" s="8"/>
       <c r="D254" s="5"/>
       <c r="E254" s="5"/>
@@ -15891,7 +18321,7 @@
     </row>
     <row r="258" spans="1:10" ht="42" customHeight="1">
       <c r="A258" s="4"/>
-      <c r="B258" s="8"/>
+      <c r="B258" s="7"/>
       <c r="C258" s="8"/>
       <c r="D258" s="5"/>
       <c r="E258" s="5"/>
@@ -15903,7 +18333,7 @@
     </row>
     <row r="259" spans="1:10" ht="42" customHeight="1">
       <c r="A259" s="4"/>
-      <c r="B259" s="8"/>
+      <c r="B259" s="7"/>
       <c r="C259" s="8"/>
       <c r="D259" s="5"/>
       <c r="E259" s="5"/>
@@ -15939,7 +18369,7 @@
     </row>
     <row r="262" spans="1:10" ht="42" customHeight="1">
       <c r="A262" s="4"/>
-      <c r="B262" s="8"/>
+      <c r="B262" s="7"/>
       <c r="C262" s="8"/>
       <c r="D262" s="5"/>
       <c r="E262" s="5"/>
@@ -15951,7 +18381,7 @@
     </row>
     <row r="263" spans="1:10" ht="42" customHeight="1">
       <c r="A263" s="4"/>
-      <c r="B263" s="8"/>
+      <c r="B263" s="7"/>
       <c r="C263" s="8"/>
       <c r="D263" s="5"/>
       <c r="E263" s="5"/>
@@ -15963,7 +18393,7 @@
     </row>
     <row r="264" spans="1:10" ht="42" customHeight="1">
       <c r="A264" s="4"/>
-      <c r="B264" s="8"/>
+      <c r="B264" s="7"/>
       <c r="C264" s="8"/>
       <c r="D264" s="5"/>
       <c r="E264" s="5"/>
@@ -16011,7 +18441,7 @@
     </row>
     <row r="268" spans="1:10" ht="42" customHeight="1">
       <c r="A268" s="4"/>
-      <c r="B268" s="8"/>
+      <c r="B268" s="7"/>
       <c r="C268" s="8"/>
       <c r="D268" s="5"/>
       <c r="E268" s="5"/>
@@ -16059,7 +18489,7 @@
     </row>
     <row r="272" spans="1:10" ht="42" customHeight="1">
       <c r="A272" s="4"/>
-      <c r="B272" s="8"/>
+      <c r="B272" s="7"/>
       <c r="C272" s="8"/>
       <c r="D272" s="5"/>
       <c r="E272" s="5"/>
@@ -16083,11 +18513,15 @@
     </row>
     <row r="274" spans="1:10" ht="42" customHeight="1">
       <c r="A274" s="4"/>
-      <c r="B274" s="8"/>
+      <c r="B274" s="7"/>
       <c r="C274" s="8"/>
       <c r="D274" s="5"/>
       <c r="E274" s="5"/>
       <c r="F274" s="5"/>
+      <c r="G274" s="5"/>
+      <c r="H274" s="5"/>
+      <c r="I274" s="5"/>
+      <c r="J274" s="5"/>
     </row>
     <row r="275" spans="1:10" ht="42" customHeight="1">
       <c r="A275" s="4"/>
@@ -16096,6 +18530,10 @@
       <c r="D275" s="5"/>
       <c r="E275" s="5"/>
       <c r="F275" s="5"/>
+      <c r="G275" s="5"/>
+      <c r="H275" s="5"/>
+      <c r="I275" s="5"/>
+      <c r="J275" s="5"/>
     </row>
     <row r="276" spans="1:10" ht="42" customHeight="1">
       <c r="A276" s="4"/>
@@ -16104,6 +18542,10 @@
       <c r="D276" s="5"/>
       <c r="E276" s="5"/>
       <c r="F276" s="5"/>
+      <c r="G276" s="5"/>
+      <c r="H276" s="5"/>
+      <c r="I276" s="5"/>
+      <c r="J276" s="5"/>
     </row>
     <row r="277" spans="1:10" ht="42" customHeight="1">
       <c r="A277" s="4"/>
@@ -16112,14 +18554,22 @@
       <c r="D277" s="5"/>
       <c r="E277" s="5"/>
       <c r="F277" s="5"/>
+      <c r="G277" s="5"/>
+      <c r="H277" s="5"/>
+      <c r="I277" s="5"/>
+      <c r="J277" s="5"/>
     </row>
     <row r="278" spans="1:10" ht="42" customHeight="1">
       <c r="A278" s="4"/>
-      <c r="B278" s="8"/>
+      <c r="B278" s="7"/>
       <c r="C278" s="8"/>
       <c r="D278" s="5"/>
       <c r="E278" s="5"/>
       <c r="F278" s="5"/>
+      <c r="G278" s="5"/>
+      <c r="H278" s="5"/>
+      <c r="I278" s="5"/>
+      <c r="J278" s="5"/>
     </row>
     <row r="279" spans="1:10" ht="42" customHeight="1">
       <c r="A279" s="4"/>
@@ -16128,6 +18578,10 @@
       <c r="D279" s="5"/>
       <c r="E279" s="5"/>
       <c r="F279" s="5"/>
+      <c r="G279" s="5"/>
+      <c r="H279" s="5"/>
+      <c r="I279" s="5"/>
+      <c r="J279" s="5"/>
     </row>
     <row r="280" spans="1:10" ht="42" customHeight="1">
       <c r="A280" s="4"/>
@@ -16136,6 +18590,10 @@
       <c r="D280" s="5"/>
       <c r="E280" s="5"/>
       <c r="F280" s="5"/>
+      <c r="G280" s="5"/>
+      <c r="H280" s="5"/>
+      <c r="I280" s="5"/>
+      <c r="J280" s="5"/>
     </row>
     <row r="281" spans="1:10" ht="42" customHeight="1">
       <c r="A281" s="4"/>
@@ -16144,14 +18602,22 @@
       <c r="D281" s="5"/>
       <c r="E281" s="5"/>
       <c r="F281" s="5"/>
+      <c r="G281" s="5"/>
+      <c r="H281" s="5"/>
+      <c r="I281" s="5"/>
+      <c r="J281" s="5"/>
     </row>
     <row r="282" spans="1:10" ht="42" customHeight="1">
       <c r="A282" s="4"/>
-      <c r="B282" s="8"/>
+      <c r="B282" s="7"/>
       <c r="C282" s="8"/>
       <c r="D282" s="5"/>
       <c r="E282" s="5"/>
       <c r="F282" s="5"/>
+      <c r="G282" s="5"/>
+      <c r="H282" s="5"/>
+      <c r="I282" s="5"/>
+      <c r="J282" s="5"/>
     </row>
     <row r="283" spans="1:10" ht="42" customHeight="1">
       <c r="A283" s="4"/>
@@ -16160,6 +18626,10 @@
       <c r="D283" s="5"/>
       <c r="E283" s="5"/>
       <c r="F283" s="5"/>
+      <c r="G283" s="5"/>
+      <c r="H283" s="5"/>
+      <c r="I283" s="5"/>
+      <c r="J283" s="5"/>
     </row>
     <row r="284" spans="1:10" ht="42" customHeight="1">
       <c r="A284" s="4"/>
@@ -16168,6 +18638,10 @@
       <c r="D284" s="5"/>
       <c r="E284" s="5"/>
       <c r="F284" s="5"/>
+      <c r="G284" s="5"/>
+      <c r="H284" s="5"/>
+      <c r="I284" s="5"/>
+      <c r="J284" s="5"/>
     </row>
     <row r="285" spans="1:10" ht="42" customHeight="1">
       <c r="A285" s="4"/>
@@ -16176,6 +18650,10 @@
       <c r="D285" s="5"/>
       <c r="E285" s="5"/>
       <c r="F285" s="5"/>
+      <c r="G285" s="5"/>
+      <c r="H285" s="5"/>
+      <c r="I285" s="5"/>
+      <c r="J285" s="5"/>
     </row>
     <row r="286" spans="1:10" ht="42" customHeight="1">
       <c r="A286" s="4"/>
@@ -16184,6 +18662,10 @@
       <c r="D286" s="5"/>
       <c r="E286" s="5"/>
       <c r="F286" s="5"/>
+      <c r="G286" s="5"/>
+      <c r="H286" s="5"/>
+      <c r="I286" s="5"/>
+      <c r="J286" s="5"/>
     </row>
     <row r="287" spans="1:10" ht="42" customHeight="1">
       <c r="A287" s="4"/>
@@ -16192,29 +18674,854 @@
       <c r="D287" s="5"/>
       <c r="E287" s="5"/>
       <c r="F287" s="5"/>
+      <c r="G287" s="5"/>
+      <c r="H287" s="5"/>
+      <c r="I287" s="5"/>
+      <c r="J287" s="5"/>
     </row>
     <row r="288" spans="1:10" ht="42" customHeight="1">
       <c r="A288" s="4"/>
       <c r="B288" s="8"/>
       <c r="C288" s="8"/>
-      <c r="D288" s="5"/>
+      <c r="D288" s="10"/>
       <c r="E288" s="5"/>
       <c r="F288" s="5"/>
-    </row>
-    <row r="289" spans="1:6" ht="42" customHeight="1">
+      <c r="G288" s="5"/>
+      <c r="H288" s="5"/>
+      <c r="I288" s="5"/>
+      <c r="J288" s="5"/>
+    </row>
+    <row r="289" spans="1:10" ht="42" customHeight="1">
       <c r="A289" s="4"/>
       <c r="B289" s="8"/>
       <c r="C289" s="8"/>
-      <c r="D289" s="5"/>
+      <c r="D289" s="10"/>
       <c r="E289" s="5"/>
       <c r="F289" s="5"/>
+      <c r="G289" s="5"/>
+      <c r="H289" s="5"/>
+      <c r="I289" s="5"/>
+      <c r="J289" s="5"/>
+    </row>
+    <row r="290" spans="1:10" ht="42" customHeight="1">
+      <c r="A290" s="4"/>
+      <c r="B290" s="8"/>
+      <c r="C290" s="8"/>
+      <c r="D290" s="10"/>
+      <c r="E290" s="5"/>
+      <c r="F290" s="5"/>
+      <c r="G290" s="5"/>
+      <c r="H290" s="5"/>
+      <c r="I290" s="5"/>
+      <c r="J290" s="5"/>
+    </row>
+    <row r="291" spans="1:10" ht="42" customHeight="1">
+      <c r="A291" s="4"/>
+      <c r="B291" s="8"/>
+      <c r="C291" s="8"/>
+      <c r="D291" s="10"/>
+      <c r="E291" s="5"/>
+      <c r="F291" s="5"/>
+      <c r="G291" s="5"/>
+      <c r="H291" s="5"/>
+      <c r="I291" s="5"/>
+      <c r="J291" s="5"/>
+    </row>
+    <row r="292" spans="1:10" ht="42" customHeight="1">
+      <c r="A292" s="4"/>
+      <c r="B292" s="8"/>
+      <c r="C292" s="8"/>
+      <c r="D292" s="10"/>
+      <c r="E292" s="5"/>
+      <c r="F292" s="5"/>
+      <c r="G292" s="5"/>
+      <c r="H292" s="5"/>
+      <c r="I292" s="5"/>
+      <c r="J292" s="5"/>
+    </row>
+    <row r="293" spans="1:10" ht="42" customHeight="1">
+      <c r="A293" s="4"/>
+      <c r="B293" s="8"/>
+      <c r="C293" s="8"/>
+      <c r="D293" s="5"/>
+      <c r="E293" s="5"/>
+      <c r="F293" s="5"/>
+      <c r="G293" s="5"/>
+      <c r="H293" s="5"/>
+      <c r="I293" s="5"/>
+      <c r="J293" s="5"/>
+    </row>
+    <row r="294" spans="1:10" ht="42" customHeight="1">
+      <c r="A294" s="4"/>
+      <c r="B294" s="8"/>
+      <c r="C294" s="8"/>
+      <c r="D294" s="5"/>
+      <c r="E294" s="5"/>
+      <c r="F294" s="5"/>
+      <c r="G294" s="5"/>
+      <c r="H294" s="5"/>
+      <c r="I294" s="5"/>
+      <c r="J294" s="5"/>
+    </row>
+    <row r="295" spans="1:10" ht="42" customHeight="1">
+      <c r="A295" s="4"/>
+      <c r="B295" s="7"/>
+      <c r="C295" s="8"/>
+      <c r="D295" s="5"/>
+      <c r="E295" s="5"/>
+      <c r="F295" s="5"/>
+      <c r="G295" s="5"/>
+      <c r="H295" s="5"/>
+      <c r="I295" s="5"/>
+      <c r="J295" s="5"/>
+    </row>
+    <row r="296" spans="1:10" ht="42" customHeight="1">
+      <c r="A296" s="4"/>
+      <c r="B296" s="8"/>
+      <c r="C296" s="8"/>
+      <c r="D296" s="5"/>
+      <c r="E296" s="5"/>
+      <c r="F296" s="5"/>
+      <c r="G296" s="5"/>
+      <c r="H296" s="5"/>
+      <c r="I296" s="5"/>
+      <c r="J296" s="5"/>
+    </row>
+    <row r="297" spans="1:10" ht="42" customHeight="1">
+      <c r="A297" s="4"/>
+      <c r="B297" s="8"/>
+      <c r="C297" s="8"/>
+      <c r="D297" s="5"/>
+      <c r="E297" s="5"/>
+      <c r="F297" s="5"/>
+      <c r="G297" s="5"/>
+      <c r="H297" s="5"/>
+      <c r="I297" s="5"/>
+      <c r="J297" s="5"/>
+    </row>
+    <row r="298" spans="1:10" ht="42" customHeight="1">
+      <c r="A298" s="4"/>
+      <c r="B298" s="8"/>
+      <c r="C298" s="8"/>
+      <c r="D298" s="5"/>
+      <c r="E298" s="5"/>
+      <c r="F298" s="5"/>
+      <c r="G298" s="5"/>
+      <c r="H298" s="5"/>
+      <c r="I298" s="5"/>
+      <c r="J298" s="5"/>
+    </row>
+    <row r="299" spans="1:10" ht="42" customHeight="1">
+      <c r="A299" s="4"/>
+      <c r="B299" s="7"/>
+      <c r="C299" s="8"/>
+      <c r="D299" s="5"/>
+      <c r="E299" s="5"/>
+      <c r="F299" s="5"/>
+      <c r="G299" s="5"/>
+      <c r="H299" s="5"/>
+      <c r="I299" s="5"/>
+      <c r="J299" s="5"/>
+    </row>
+    <row r="300" spans="1:10" ht="42" customHeight="1">
+      <c r="A300" s="4"/>
+      <c r="B300" s="8"/>
+      <c r="C300" s="8"/>
+      <c r="D300" s="5"/>
+      <c r="E300" s="5"/>
+      <c r="F300" s="5"/>
+      <c r="G300" s="5"/>
+      <c r="H300" s="5"/>
+      <c r="I300" s="5"/>
+      <c r="J300" s="5"/>
+    </row>
+    <row r="301" spans="1:10" ht="42" customHeight="1">
+      <c r="A301" s="4"/>
+      <c r="B301" s="8"/>
+      <c r="C301" s="8"/>
+      <c r="D301" s="5"/>
+      <c r="E301" s="5"/>
+      <c r="F301" s="5"/>
+      <c r="G301" s="5"/>
+      <c r="H301" s="5"/>
+      <c r="I301" s="5"/>
+      <c r="J301" s="5"/>
+    </row>
+    <row r="302" spans="1:10" ht="42" customHeight="1">
+      <c r="A302" s="4"/>
+      <c r="B302" s="8"/>
+      <c r="C302" s="8"/>
+      <c r="D302" s="5"/>
+      <c r="E302" s="5"/>
+      <c r="F302" s="5"/>
+      <c r="G302" s="5"/>
+      <c r="H302" s="5"/>
+      <c r="I302" s="5"/>
+      <c r="J302" s="5"/>
+    </row>
+    <row r="303" spans="1:10" ht="42" customHeight="1">
+      <c r="A303" s="4"/>
+      <c r="B303" s="7"/>
+      <c r="C303" s="8"/>
+      <c r="D303" s="5"/>
+      <c r="E303" s="5"/>
+      <c r="F303" s="5"/>
+      <c r="G303" s="5"/>
+      <c r="H303" s="5"/>
+      <c r="I303" s="5"/>
+      <c r="J303" s="5"/>
+    </row>
+    <row r="304" spans="1:10" ht="42" customHeight="1">
+      <c r="A304" s="4"/>
+      <c r="B304" s="8"/>
+      <c r="C304" s="8"/>
+      <c r="D304" s="5"/>
+      <c r="E304" s="5"/>
+      <c r="F304" s="5"/>
+      <c r="G304" s="5"/>
+      <c r="H304" s="5"/>
+      <c r="I304" s="5"/>
+      <c r="J304" s="5"/>
+    </row>
+    <row r="305" spans="1:10" ht="42" customHeight="1">
+      <c r="A305" s="4"/>
+      <c r="B305" s="8"/>
+      <c r="C305" s="8"/>
+      <c r="D305" s="5"/>
+      <c r="E305" s="5"/>
+      <c r="F305" s="5"/>
+      <c r="G305" s="5"/>
+      <c r="H305" s="5"/>
+      <c r="I305" s="5"/>
+      <c r="J305" s="5"/>
+    </row>
+    <row r="306" spans="1:10" ht="42" customHeight="1">
+      <c r="A306" s="4"/>
+      <c r="B306" s="8"/>
+      <c r="C306" s="8"/>
+      <c r="D306" s="5"/>
+      <c r="E306" s="5"/>
+      <c r="F306" s="5"/>
+      <c r="G306" s="5"/>
+      <c r="H306" s="5"/>
+      <c r="I306" s="5"/>
+      <c r="J306" s="5"/>
+    </row>
+    <row r="307" spans="1:10" ht="42" customHeight="1">
+      <c r="A307" s="4"/>
+      <c r="B307" s="7"/>
+      <c r="C307" s="8"/>
+      <c r="D307" s="5"/>
+      <c r="E307" s="5"/>
+      <c r="F307" s="5"/>
+      <c r="G307" s="5"/>
+      <c r="H307" s="5"/>
+      <c r="I307" s="5"/>
+      <c r="J307" s="5"/>
+    </row>
+    <row r="308" spans="1:10" ht="42" customHeight="1">
+      <c r="A308" s="4"/>
+      <c r="B308" s="7"/>
+      <c r="C308" s="8"/>
+      <c r="D308" s="5"/>
+      <c r="E308" s="5"/>
+      <c r="F308" s="5"/>
+      <c r="G308" s="5"/>
+      <c r="H308" s="5"/>
+      <c r="I308" s="5"/>
+      <c r="J308" s="5"/>
+    </row>
+    <row r="309" spans="1:10" ht="42" customHeight="1">
+      <c r="A309" s="4"/>
+      <c r="B309" s="8"/>
+      <c r="C309" s="8"/>
+      <c r="D309" s="5"/>
+      <c r="E309" s="5"/>
+      <c r="F309" s="5"/>
+      <c r="G309" s="5"/>
+      <c r="H309" s="5"/>
+      <c r="I309" s="5"/>
+      <c r="J309" s="5"/>
+    </row>
+    <row r="310" spans="1:10" ht="42" customHeight="1">
+      <c r="A310" s="4"/>
+      <c r="B310" s="8"/>
+      <c r="C310" s="8"/>
+      <c r="D310" s="5"/>
+      <c r="E310" s="5"/>
+      <c r="F310" s="5"/>
+      <c r="G310" s="5"/>
+      <c r="H310" s="5"/>
+      <c r="I310" s="5"/>
+      <c r="J310" s="5"/>
+    </row>
+    <row r="311" spans="1:10" ht="42" customHeight="1">
+      <c r="A311" s="4"/>
+      <c r="B311" s="8"/>
+      <c r="C311" s="8"/>
+      <c r="D311" s="5"/>
+      <c r="E311" s="5"/>
+      <c r="F311" s="5"/>
+      <c r="G311" s="5"/>
+      <c r="H311" s="5"/>
+      <c r="I311" s="5"/>
+      <c r="J311" s="5"/>
+    </row>
+    <row r="312" spans="1:10" ht="42" customHeight="1">
+      <c r="A312" s="4"/>
+      <c r="B312" s="7"/>
+      <c r="C312" s="8"/>
+      <c r="D312" s="5"/>
+      <c r="E312" s="5"/>
+      <c r="F312" s="5"/>
+      <c r="G312" s="5"/>
+      <c r="H312" s="5"/>
+      <c r="I312" s="5"/>
+      <c r="J312" s="5"/>
+    </row>
+    <row r="313" spans="1:10" ht="42" customHeight="1">
+      <c r="A313" s="4"/>
+      <c r="B313" s="8"/>
+      <c r="C313" s="8"/>
+      <c r="D313" s="5"/>
+      <c r="E313" s="5"/>
+      <c r="F313" s="5"/>
+      <c r="G313" s="5"/>
+      <c r="H313" s="5"/>
+      <c r="I313" s="5"/>
+      <c r="J313" s="5"/>
+    </row>
+    <row r="314" spans="1:10" ht="42" customHeight="1">
+      <c r="A314" s="4"/>
+      <c r="B314" s="8"/>
+      <c r="C314" s="8"/>
+      <c r="D314" s="5"/>
+      <c r="E314" s="5"/>
+      <c r="F314" s="5"/>
+      <c r="G314" s="5"/>
+      <c r="H314" s="5"/>
+      <c r="I314" s="5"/>
+      <c r="J314" s="5"/>
+    </row>
+    <row r="315" spans="1:10" ht="42" customHeight="1">
+      <c r="A315" s="4"/>
+      <c r="B315" s="8"/>
+      <c r="C315" s="8"/>
+      <c r="D315" s="5"/>
+      <c r="E315" s="5"/>
+      <c r="F315" s="5"/>
+      <c r="G315" s="5"/>
+      <c r="H315" s="5"/>
+      <c r="I315" s="5"/>
+      <c r="J315" s="5"/>
+    </row>
+    <row r="316" spans="1:10" ht="42" customHeight="1">
+      <c r="A316" s="4"/>
+      <c r="B316" s="7"/>
+      <c r="C316" s="8"/>
+      <c r="D316" s="5"/>
+      <c r="E316" s="5"/>
+      <c r="F316" s="5"/>
+      <c r="G316" s="5"/>
+      <c r="H316" s="5"/>
+      <c r="I316" s="5"/>
+      <c r="J316" s="5"/>
+    </row>
+    <row r="317" spans="1:10" ht="42" customHeight="1">
+      <c r="A317" s="4"/>
+      <c r="B317" s="8"/>
+      <c r="C317" s="8"/>
+      <c r="D317" s="5"/>
+      <c r="E317" s="5"/>
+      <c r="F317" s="5"/>
+      <c r="G317" s="5"/>
+      <c r="H317" s="5"/>
+      <c r="I317" s="5"/>
+      <c r="J317" s="5"/>
+    </row>
+    <row r="318" spans="1:10" ht="42" customHeight="1">
+      <c r="A318" s="4"/>
+      <c r="B318" s="8"/>
+      <c r="C318" s="8"/>
+      <c r="D318" s="5"/>
+      <c r="E318" s="5"/>
+      <c r="F318" s="5"/>
+      <c r="G318" s="5"/>
+      <c r="H318" s="5"/>
+      <c r="I318" s="5"/>
+      <c r="J318" s="5"/>
+    </row>
+    <row r="319" spans="1:10" ht="42" customHeight="1">
+      <c r="A319" s="4"/>
+      <c r="B319" s="8"/>
+      <c r="C319" s="8"/>
+      <c r="D319" s="5"/>
+      <c r="E319" s="5"/>
+      <c r="F319" s="5"/>
+      <c r="G319" s="5"/>
+      <c r="H319" s="5"/>
+      <c r="I319" s="5"/>
+      <c r="J319" s="5"/>
+    </row>
+    <row r="320" spans="1:10" ht="42" customHeight="1">
+      <c r="A320" s="4"/>
+      <c r="B320" s="7"/>
+      <c r="C320" s="8"/>
+      <c r="D320" s="5"/>
+      <c r="E320" s="5"/>
+      <c r="F320" s="5"/>
+      <c r="G320" s="5"/>
+      <c r="H320" s="5"/>
+      <c r="I320" s="5"/>
+      <c r="J320" s="5"/>
+    </row>
+    <row r="321" spans="1:10" ht="42" customHeight="1">
+      <c r="A321" s="4"/>
+      <c r="B321" s="8"/>
+      <c r="C321" s="8"/>
+      <c r="D321" s="5"/>
+      <c r="E321" s="5"/>
+      <c r="F321" s="5"/>
+      <c r="G321" s="5"/>
+      <c r="H321" s="5"/>
+      <c r="I321" s="5"/>
+      <c r="J321" s="5"/>
+    </row>
+    <row r="322" spans="1:10" ht="42" customHeight="1">
+      <c r="A322" s="4"/>
+      <c r="B322" s="8"/>
+      <c r="C322" s="8"/>
+      <c r="D322" s="5"/>
+      <c r="E322" s="5"/>
+      <c r="F322" s="5"/>
+      <c r="G322" s="5"/>
+      <c r="H322" s="5"/>
+      <c r="I322" s="5"/>
+      <c r="J322" s="5"/>
+    </row>
+    <row r="323" spans="1:10" ht="42" customHeight="1">
+      <c r="A323" s="4"/>
+      <c r="B323" s="8"/>
+      <c r="C323" s="8"/>
+      <c r="D323" s="5"/>
+      <c r="E323" s="5"/>
+      <c r="F323" s="5"/>
+      <c r="G323" s="5"/>
+      <c r="H323" s="5"/>
+      <c r="I323" s="5"/>
+      <c r="J323" s="5"/>
+    </row>
+    <row r="324" spans="1:10" ht="42" customHeight="1">
+      <c r="A324" s="4"/>
+      <c r="B324" s="8"/>
+      <c r="C324" s="8"/>
+      <c r="D324" s="5"/>
+      <c r="E324" s="5"/>
+      <c r="F324" s="5"/>
+      <c r="G324" s="5"/>
+      <c r="H324" s="5"/>
+      <c r="I324" s="5"/>
+      <c r="J324" s="5"/>
+    </row>
+    <row r="325" spans="1:10" ht="42" customHeight="1">
+      <c r="A325" s="4"/>
+      <c r="B325" s="8"/>
+      <c r="C325" s="8"/>
+      <c r="D325" s="5"/>
+      <c r="E325" s="5"/>
+      <c r="F325" s="5"/>
+      <c r="G325" s="5"/>
+      <c r="H325" s="5"/>
+      <c r="I325" s="5"/>
+      <c r="J325" s="5"/>
+    </row>
+    <row r="326" spans="1:10" ht="42" customHeight="1">
+      <c r="A326" s="4"/>
+      <c r="B326" s="8"/>
+      <c r="C326" s="8"/>
+      <c r="D326" s="5"/>
+      <c r="E326" s="5"/>
+      <c r="F326" s="5"/>
+      <c r="G326" s="5"/>
+      <c r="H326" s="5"/>
+      <c r="I326" s="5"/>
+      <c r="J326" s="5"/>
+    </row>
+    <row r="327" spans="1:10" ht="42" customHeight="1">
+      <c r="A327" s="4"/>
+      <c r="B327" s="8"/>
+      <c r="C327" s="8"/>
+      <c r="D327" s="5"/>
+      <c r="E327" s="5"/>
+      <c r="F327" s="5"/>
+      <c r="G327" s="5"/>
+      <c r="H327" s="5"/>
+      <c r="I327" s="5"/>
+      <c r="J327" s="5"/>
+    </row>
+    <row r="328" spans="1:10" ht="42" customHeight="1">
+      <c r="A328" s="4"/>
+      <c r="B328" s="8"/>
+      <c r="C328" s="8"/>
+      <c r="D328" s="5"/>
+      <c r="E328" s="5"/>
+      <c r="F328" s="5"/>
+      <c r="G328" s="5"/>
+      <c r="H328" s="5"/>
+      <c r="I328" s="5"/>
+      <c r="J328" s="5"/>
+    </row>
+    <row r="329" spans="1:10" ht="42" customHeight="1">
+      <c r="A329" s="4"/>
+      <c r="B329" s="8"/>
+      <c r="C329" s="8"/>
+      <c r="D329" s="5"/>
+      <c r="E329" s="5"/>
+      <c r="F329" s="5"/>
+      <c r="G329" s="5"/>
+      <c r="H329" s="5"/>
+      <c r="I329" s="5"/>
+      <c r="J329" s="5"/>
+    </row>
+    <row r="330" spans="1:10" ht="42" customHeight="1">
+      <c r="A330" s="4"/>
+      <c r="B330" s="8"/>
+      <c r="C330" s="8"/>
+      <c r="D330" s="5"/>
+      <c r="E330" s="5"/>
+      <c r="F330" s="5"/>
+      <c r="G330" s="5"/>
+      <c r="H330" s="5"/>
+      <c r="I330" s="5"/>
+      <c r="J330" s="5"/>
+    </row>
+    <row r="331" spans="1:10" ht="42" customHeight="1">
+      <c r="A331" s="4"/>
+      <c r="B331" s="8"/>
+      <c r="C331" s="8"/>
+      <c r="D331" s="5"/>
+      <c r="E331" s="5"/>
+      <c r="F331" s="5"/>
+      <c r="G331" s="5"/>
+      <c r="H331" s="5"/>
+      <c r="I331" s="5"/>
+      <c r="J331" s="5"/>
+    </row>
+    <row r="332" spans="1:10" ht="42" customHeight="1">
+      <c r="A332" s="4"/>
+      <c r="B332" s="8"/>
+      <c r="C332" s="8"/>
+      <c r="D332" s="5"/>
+      <c r="E332" s="5"/>
+      <c r="F332" s="5"/>
+      <c r="G332" s="5"/>
+      <c r="H332" s="5"/>
+      <c r="I332" s="5"/>
+      <c r="J332" s="5"/>
+    </row>
+    <row r="333" spans="1:10" ht="42" customHeight="1">
+      <c r="A333" s="4"/>
+      <c r="B333" s="8"/>
+      <c r="C333" s="8"/>
+      <c r="D333" s="5"/>
+      <c r="E333" s="5"/>
+      <c r="F333" s="5"/>
+      <c r="G333" s="5"/>
+      <c r="H333" s="5"/>
+      <c r="I333" s="5"/>
+      <c r="J333" s="5"/>
+    </row>
+    <row r="334" spans="1:10" ht="42" customHeight="1">
+      <c r="A334" s="4"/>
+      <c r="B334" s="8"/>
+      <c r="C334" s="8"/>
+      <c r="D334" s="5"/>
+      <c r="E334" s="5"/>
+      <c r="F334" s="5"/>
+      <c r="G334" s="5"/>
+      <c r="H334" s="5"/>
+      <c r="I334" s="5"/>
+      <c r="J334" s="5"/>
+    </row>
+    <row r="335" spans="1:10" ht="42" customHeight="1">
+      <c r="A335" s="4"/>
+      <c r="B335" s="8"/>
+      <c r="C335" s="8"/>
+      <c r="D335" s="5"/>
+      <c r="E335" s="5"/>
+      <c r="F335" s="5"/>
+      <c r="G335" s="5"/>
+      <c r="H335" s="5"/>
+      <c r="I335" s="5"/>
+      <c r="J335" s="5"/>
+    </row>
+    <row r="336" spans="1:10" ht="42" customHeight="1">
+      <c r="A336" s="4"/>
+      <c r="B336" s="8"/>
+      <c r="C336" s="8"/>
+      <c r="D336" s="5"/>
+      <c r="E336" s="5"/>
+      <c r="F336" s="5"/>
+      <c r="G336" s="5"/>
+      <c r="H336" s="5"/>
+      <c r="I336" s="5"/>
+      <c r="J336" s="5"/>
+    </row>
+    <row r="337" spans="1:10" ht="42" customHeight="1">
+      <c r="A337" s="4"/>
+      <c r="B337" s="8"/>
+      <c r="C337" s="8"/>
+      <c r="D337" s="5"/>
+      <c r="E337" s="5"/>
+      <c r="F337" s="5"/>
+      <c r="G337" s="5"/>
+      <c r="H337" s="5"/>
+      <c r="I337" s="5"/>
+      <c r="J337" s="5"/>
+    </row>
+    <row r="338" spans="1:10" ht="42" customHeight="1">
+      <c r="A338" s="4"/>
+      <c r="B338" s="8"/>
+      <c r="C338" s="8"/>
+      <c r="D338" s="5"/>
+      <c r="E338" s="5"/>
+      <c r="F338" s="5"/>
+      <c r="G338" s="5"/>
+      <c r="H338" s="5"/>
+      <c r="I338" s="5"/>
+      <c r="J338" s="5"/>
+    </row>
+    <row r="339" spans="1:10" ht="42" customHeight="1">
+      <c r="A339" s="4"/>
+      <c r="B339" s="8"/>
+      <c r="C339" s="8"/>
+      <c r="D339" s="5"/>
+      <c r="E339" s="5"/>
+      <c r="F339" s="5"/>
+      <c r="G339" s="5"/>
+      <c r="H339" s="5"/>
+      <c r="I339" s="5"/>
+      <c r="J339" s="5"/>
+    </row>
+    <row r="340" spans="1:10" ht="42" customHeight="1">
+      <c r="A340" s="4"/>
+      <c r="B340" s="8"/>
+      <c r="C340" s="8"/>
+      <c r="D340" s="5"/>
+      <c r="E340" s="5"/>
+      <c r="F340" s="5"/>
+      <c r="G340" s="5"/>
+      <c r="H340" s="5"/>
+      <c r="I340" s="5"/>
+      <c r="J340" s="5"/>
+    </row>
+    <row r="341" spans="1:10" ht="42" customHeight="1">
+      <c r="A341" s="4"/>
+      <c r="B341" s="8"/>
+      <c r="C341" s="8"/>
+      <c r="D341" s="5"/>
+      <c r="E341" s="5"/>
+      <c r="F341" s="5"/>
+      <c r="G341" s="5"/>
+      <c r="H341" s="5"/>
+      <c r="I341" s="5"/>
+      <c r="J341" s="5"/>
+    </row>
+    <row r="342" spans="1:10" ht="42" customHeight="1">
+      <c r="A342" s="4"/>
+      <c r="B342" s="8"/>
+      <c r="C342" s="8"/>
+      <c r="D342" s="5"/>
+      <c r="E342" s="5"/>
+      <c r="F342" s="5"/>
+      <c r="G342" s="5"/>
+      <c r="H342" s="5"/>
+      <c r="I342" s="5"/>
+      <c r="J342" s="5"/>
+    </row>
+    <row r="343" spans="1:10" ht="42" customHeight="1">
+      <c r="A343" s="4"/>
+      <c r="B343" s="8"/>
+      <c r="C343" s="8"/>
+      <c r="D343" s="5"/>
+      <c r="E343" s="5"/>
+      <c r="F343" s="5"/>
+      <c r="G343" s="5"/>
+      <c r="H343" s="5"/>
+      <c r="I343" s="5"/>
+      <c r="J343" s="5"/>
+    </row>
+    <row r="344" spans="1:10" ht="42" customHeight="1">
+      <c r="A344" s="4"/>
+      <c r="B344" s="8"/>
+      <c r="C344" s="8"/>
+      <c r="D344" s="5"/>
+      <c r="E344" s="5"/>
+      <c r="F344" s="5"/>
+      <c r="G344" s="5"/>
+      <c r="H344" s="5"/>
+      <c r="I344" s="5"/>
+      <c r="J344" s="5"/>
+    </row>
+    <row r="345" spans="1:10" ht="42" customHeight="1">
+      <c r="A345" s="4"/>
+      <c r="B345" s="8"/>
+      <c r="C345" s="8"/>
+      <c r="D345" s="5"/>
+      <c r="E345" s="5"/>
+      <c r="F345" s="5"/>
+      <c r="G345" s="5"/>
+      <c r="H345" s="5"/>
+      <c r="I345" s="5"/>
+      <c r="J345" s="5"/>
+    </row>
+    <row r="346" spans="1:10" ht="42" customHeight="1">
+      <c r="A346" s="4"/>
+      <c r="B346" s="8"/>
+      <c r="C346" s="8"/>
+      <c r="D346" s="5"/>
+      <c r="E346" s="5"/>
+      <c r="F346" s="5"/>
+      <c r="G346" s="5"/>
+      <c r="H346" s="5"/>
+      <c r="I346" s="5"/>
+      <c r="J346" s="5"/>
+    </row>
+    <row r="347" spans="1:10" ht="42" customHeight="1">
+      <c r="A347" s="4"/>
+      <c r="B347" s="8"/>
+      <c r="C347" s="8"/>
+      <c r="D347" s="5"/>
+      <c r="E347" s="5"/>
+      <c r="F347" s="5"/>
+    </row>
+    <row r="348" spans="1:10" ht="42" customHeight="1">
+      <c r="A348" s="4"/>
+      <c r="B348" s="8"/>
+      <c r="C348" s="8"/>
+      <c r="D348" s="5"/>
+      <c r="E348" s="5"/>
+      <c r="F348" s="5"/>
+    </row>
+    <row r="349" spans="1:10" ht="42" customHeight="1">
+      <c r="A349" s="4"/>
+      <c r="B349" s="8"/>
+      <c r="C349" s="8"/>
+      <c r="D349" s="5"/>
+      <c r="E349" s="5"/>
+      <c r="F349" s="5"/>
+    </row>
+    <row r="350" spans="1:10" ht="42" customHeight="1">
+      <c r="A350" s="4"/>
+      <c r="B350" s="8"/>
+      <c r="C350" s="8"/>
+      <c r="D350" s="5"/>
+      <c r="E350" s="5"/>
+      <c r="F350" s="5"/>
+    </row>
+    <row r="351" spans="1:10" ht="42" customHeight="1">
+      <c r="A351" s="4"/>
+      <c r="B351" s="8"/>
+      <c r="C351" s="8"/>
+      <c r="D351" s="5"/>
+      <c r="E351" s="5"/>
+      <c r="F351" s="5"/>
+    </row>
+    <row r="352" spans="1:10" ht="42" customHeight="1">
+      <c r="A352" s="4"/>
+      <c r="B352" s="8"/>
+      <c r="C352" s="8"/>
+      <c r="D352" s="5"/>
+      <c r="E352" s="5"/>
+      <c r="F352" s="5"/>
+    </row>
+    <row r="353" spans="1:6" ht="42" customHeight="1">
+      <c r="A353" s="4"/>
+      <c r="B353" s="8"/>
+      <c r="C353" s="8"/>
+      <c r="D353" s="5"/>
+      <c r="E353" s="5"/>
+      <c r="F353" s="5"/>
+    </row>
+    <row r="354" spans="1:6" ht="42" customHeight="1">
+      <c r="A354" s="4"/>
+      <c r="B354" s="8"/>
+      <c r="C354" s="8"/>
+      <c r="D354" s="5"/>
+      <c r="E354" s="5"/>
+      <c r="F354" s="5"/>
+    </row>
+    <row r="355" spans="1:6" ht="42" customHeight="1">
+      <c r="A355" s="4"/>
+      <c r="B355" s="8"/>
+      <c r="C355" s="8"/>
+      <c r="D355" s="5"/>
+      <c r="E355" s="5"/>
+      <c r="F355" s="5"/>
+    </row>
+    <row r="356" spans="1:6" ht="42" customHeight="1">
+      <c r="A356" s="4"/>
+      <c r="B356" s="8"/>
+      <c r="C356" s="8"/>
+      <c r="D356" s="5"/>
+      <c r="E356" s="5"/>
+      <c r="F356" s="5"/>
+    </row>
+    <row r="357" spans="1:6" ht="42" customHeight="1">
+      <c r="A357" s="4"/>
+      <c r="B357" s="8"/>
+      <c r="C357" s="8"/>
+      <c r="D357" s="5"/>
+      <c r="E357" s="5"/>
+      <c r="F357" s="5"/>
+    </row>
+    <row r="358" spans="1:6" ht="42" customHeight="1">
+      <c r="A358" s="4"/>
+      <c r="B358" s="8"/>
+      <c r="C358" s="8"/>
+      <c r="D358" s="5"/>
+      <c r="E358" s="5"/>
+      <c r="F358" s="5"/>
+    </row>
+    <row r="359" spans="1:6" ht="42" customHeight="1">
+      <c r="A359" s="4"/>
+      <c r="B359" s="8"/>
+      <c r="C359" s="8"/>
+      <c r="D359" s="5"/>
+      <c r="E359" s="5"/>
+      <c r="F359" s="5"/>
+    </row>
+    <row r="360" spans="1:6" ht="42" customHeight="1">
+      <c r="A360" s="4"/>
+      <c r="B360" s="8"/>
+      <c r="C360" s="8"/>
+      <c r="D360" s="5"/>
+      <c r="E360" s="5"/>
+      <c r="F360" s="5"/>
+    </row>
+    <row r="361" spans="1:6" ht="42" customHeight="1">
+      <c r="A361" s="4"/>
+      <c r="B361" s="8"/>
+      <c r="C361" s="8"/>
+      <c r="D361" s="5"/>
+      <c r="E361" s="5"/>
+      <c r="F361" s="5"/>
+    </row>
+    <row r="362" spans="1:6" ht="42" customHeight="1">
+      <c r="A362" s="4"/>
+      <c r="B362" s="8"/>
+      <c r="C362" s="8"/>
+      <c r="D362" s="5"/>
+      <c r="E362" s="5"/>
+      <c r="F362" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="I2:I189 I191:I247">
+  <conditionalFormatting sqref="I2:I262 I264:I320">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="yes"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
